--- a/research/traditional_assets/database/data/malta/malta_air_transport.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="mtse_mia" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.153</v>
+        <v>0.00335</v>
+      </c>
+      <c r="E2">
+        <v>0.00758</v>
       </c>
       <c r="G2">
-        <v>0.1098870056497175</v>
+        <v>0.2634207240948814</v>
       </c>
       <c r="H2">
-        <v>0.1098870056497175</v>
+        <v>0.2634207240948814</v>
       </c>
       <c r="I2">
-        <v>-0.1779661016949153</v>
+        <v>0.4594257178526842</v>
       </c>
       <c r="J2">
-        <v>-0.1779661016949153</v>
+        <v>0.295778034712546</v>
       </c>
       <c r="K2">
-        <v>-5.85</v>
+        <v>24.4</v>
       </c>
       <c r="L2">
-        <v>-0.1652542372881356</v>
+        <v>0.3046192259675406</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>17.7</v>
+        <v>36</v>
       </c>
       <c r="V2">
-        <v>0.01925587467362924</v>
+        <v>0.04292357219506378</v>
       </c>
       <c r="W2">
-        <v>-0.04090909090909091</v>
+        <v>0.1685082872928177</v>
       </c>
       <c r="X2">
-        <v>0.06267120432634792</v>
+        <v>0.09775638893287353</v>
       </c>
       <c r="Y2">
-        <v>-0.1035802952354388</v>
+        <v>0.07075189835994414</v>
       </c>
       <c r="Z2">
-        <v>0.2161172161172161</v>
+        <v>0.4206932773109243</v>
       </c>
       <c r="AA2">
-        <v>-0.03846153846153846</v>
+        <v>0.1244318307798053</v>
       </c>
       <c r="AB2">
-        <v>0.05991331436025689</v>
+        <v>0.09417981225260548</v>
       </c>
       <c r="AC2">
-        <v>-0.09837485282179534</v>
+        <v>0.03025201852719982</v>
       </c>
       <c r="AD2">
-        <v>63.3</v>
+        <v>52.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>63.3</v>
+        <v>52.9</v>
       </c>
       <c r="AG2">
-        <v>45.59999999999999</v>
+        <v>16.9</v>
       </c>
       <c r="AH2">
-        <v>0.06442748091603054</v>
+        <v>0.05933153880663974</v>
       </c>
       <c r="AI2">
-        <v>0.3041806823642479</v>
+        <v>0.26007866273353</v>
       </c>
       <c r="AJ2">
-        <v>0.04726368159203979</v>
+        <v>0.01975222066386162</v>
       </c>
       <c r="AK2">
-        <v>0.2394957983193277</v>
+        <v>0.1009557945041816</v>
       </c>
       <c r="AL2">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="AM2">
-        <v>2.475</v>
+        <v>1.952</v>
       </c>
       <c r="AN2">
-        <v>21.90311418685121</v>
+        <v>1.157549234135667</v>
       </c>
       <c r="AO2">
-        <v>-2.52</v>
+        <v>18.68020304568528</v>
       </c>
       <c r="AP2">
-        <v>15.77854671280276</v>
+        <v>0.3698030634573304</v>
       </c>
       <c r="AQ2">
-        <v>-2.545454545454545</v>
+        <v>18.85245901639344</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.153</v>
+        <v>0.00335</v>
+      </c>
+      <c r="E3">
+        <v>0.00758</v>
       </c>
       <c r="G3">
-        <v>0.1098870056497175</v>
+        <v>0.2634207240948814</v>
       </c>
       <c r="H3">
-        <v>0.1098870056497175</v>
+        <v>0.2634207240948814</v>
       </c>
       <c r="I3">
-        <v>-0.1779661016949153</v>
+        <v>0.4594257178526842</v>
       </c>
       <c r="J3">
-        <v>-0.1779661016949153</v>
+        <v>0.295778034712546</v>
       </c>
       <c r="K3">
-        <v>-5.85</v>
+        <v>24.4</v>
       </c>
       <c r="L3">
-        <v>-0.1652542372881356</v>
+        <v>0.3046192259675406</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>17.7</v>
+        <v>36</v>
       </c>
       <c r="V3">
-        <v>0.01925587467362924</v>
+        <v>0.04292357219506378</v>
       </c>
       <c r="W3">
-        <v>-0.04090909090909091</v>
+        <v>0.1685082872928177</v>
       </c>
       <c r="X3">
-        <v>0.06267120432634792</v>
+        <v>0.09775638893287353</v>
       </c>
       <c r="Y3">
-        <v>-0.1035802952354388</v>
+        <v>0.07075189835994414</v>
       </c>
       <c r="Z3">
-        <v>0.2161172161172161</v>
+        <v>0.4206932773109243</v>
       </c>
       <c r="AA3">
-        <v>-0.03846153846153846</v>
+        <v>0.1244318307798053</v>
       </c>
       <c r="AB3">
-        <v>0.05991331436025689</v>
+        <v>0.09417981225260548</v>
       </c>
       <c r="AC3">
-        <v>-0.09837485282179534</v>
+        <v>0.03025201852719982</v>
       </c>
       <c r="AD3">
-        <v>63.3</v>
+        <v>52.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>63.3</v>
+        <v>52.9</v>
       </c>
       <c r="AG3">
-        <v>45.59999999999999</v>
+        <v>16.9</v>
       </c>
       <c r="AH3">
-        <v>0.06442748091603054</v>
+        <v>0.05933153880663974</v>
       </c>
       <c r="AI3">
-        <v>0.3041806823642479</v>
+        <v>0.26007866273353</v>
       </c>
       <c r="AJ3">
-        <v>0.04726368159203979</v>
+        <v>0.01975222066386162</v>
       </c>
       <c r="AK3">
-        <v>0.2394957983193277</v>
+        <v>0.1009557945041816</v>
       </c>
       <c r="AL3">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="AM3">
-        <v>2.475</v>
+        <v>1.952</v>
       </c>
       <c r="AN3">
-        <v>21.90311418685121</v>
+        <v>1.157549234135667</v>
       </c>
       <c r="AO3">
-        <v>-2.52</v>
+        <v>18.68020304568528</v>
       </c>
       <c r="AP3">
-        <v>15.77854671280276</v>
+        <v>0.3698030634573304</v>
       </c>
       <c r="AQ3">
-        <v>-2.545454545454545</v>
+        <v>18.85245901639344</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Malta International Airport p.l.c. (MTSE:MIA)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MTSE:MIA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0593315388066397</v>
+      </c>
+      <c r="F2">
+        <v>0.15</v>
+      </c>
+      <c r="G2">
+        <v>838.7</v>
+      </c>
+      <c r="H2">
+        <v>792.8556938033011</v>
+      </c>
+      <c r="I2">
+        <v>855.6</v>
+      </c>
+      <c r="J2">
+        <v>890.5956938033009</v>
+      </c>
+      <c r="K2">
+        <v>52.9</v>
+      </c>
+      <c r="L2">
+        <v>133.74</v>
+      </c>
+      <c r="M2">
+        <v>0.09417981225260549</v>
+      </c>
+      <c r="N2">
+        <v>0.0920036789454703</v>
+      </c>
+      <c r="O2">
+        <v>0.0374751834862385</v>
+      </c>
+      <c r="P2">
+        <v>0.03575</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.0977563889328735</v>
+      </c>
+      <c r="T2">
+        <v>0.101930798759377</v>
+      </c>
+      <c r="U2">
+        <v>0.799428268291632</v>
+      </c>
+      <c r="V2">
+        <v>0.856031823549074</v>
+      </c>
+      <c r="W2">
+        <v>4.676645322674933</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>838.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.07374819139040771</v>
+      </c>
+      <c r="AC2">
+        <v>0.05765412844036698</v>
+      </c>
+      <c r="AD2">
+        <v>0.35</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>45.7</v>
+      </c>
+      <c r="AH2">
+        <v>11.3</v>
+      </c>
+      <c r="AI2">
+        <v>-3.552713678800501e-15</v>
+      </c>
+      <c r="AJ2">
+        <v>52.9</v>
+      </c>
+      <c r="AK2">
+        <v>52.9</v>
+      </c>
+      <c r="AL2">
+        <v>1.97</v>
+      </c>
+      <c r="AM2">
+        <v>52.9</v>
+      </c>
+      <c r="AN2">
+        <v>36</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09543448965221143</v>
+      </c>
+      <c r="C2">
+        <v>872.6450841934808</v>
+      </c>
+      <c r="D2">
+        <v>836.6450841934808</v>
+      </c>
+      <c r="E2">
+        <v>-52.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>36</v>
+      </c>
+      <c r="H2">
+        <v>838.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>45.7</v>
+      </c>
+      <c r="K2">
+        <v>11.3</v>
+      </c>
+      <c r="L2">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="O2">
+        <v>12.04</v>
+      </c>
+      <c r="P2">
+        <v>22.36000000000001</v>
+      </c>
+      <c r="Q2">
+        <v>33.66000000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09543448965221143</v>
+      </c>
+      <c r="T2">
+        <v>0.7679441161126261</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.35</v>
+      </c>
+      <c r="W2">
+        <v>0.029705</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09514531893842869</v>
+      </c>
+      <c r="C3">
+        <v>868.022843830256</v>
+      </c>
+      <c r="D3">
+        <v>840.938843830256</v>
+      </c>
+      <c r="E3">
+        <v>-43.98399999999999</v>
+      </c>
+      <c r="F3">
+        <v>8.916</v>
+      </c>
+      <c r="G3">
+        <v>36</v>
+      </c>
+      <c r="H3">
+        <v>838.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>45.7</v>
+      </c>
+      <c r="K3">
+        <v>11.3</v>
+      </c>
+      <c r="L3">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M3">
+        <v>0.4074612000000001</v>
+      </c>
+      <c r="N3">
+        <v>33.99253880000001</v>
+      </c>
+      <c r="O3">
+        <v>11.89738858</v>
+      </c>
+      <c r="P3">
+        <v>22.09515022</v>
+      </c>
+      <c r="Q3">
+        <v>33.39515022</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09580633226103909</v>
+      </c>
+      <c r="T3">
+        <v>0.7729861734406384</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.35</v>
+      </c>
+      <c r="W3">
+        <v>0.029705</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>84.42521643778598</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09485614822464596</v>
+      </c>
+      <c r="C4">
+        <v>863.4449029623871</v>
+      </c>
+      <c r="D4">
+        <v>845.2769029623871</v>
+      </c>
+      <c r="E4">
+        <v>-35.068</v>
+      </c>
+      <c r="F4">
+        <v>17.832</v>
+      </c>
+      <c r="G4">
+        <v>36</v>
+      </c>
+      <c r="H4">
+        <v>838.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>45.7</v>
+      </c>
+      <c r="K4">
+        <v>11.3</v>
+      </c>
+      <c r="L4">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M4">
+        <v>0.8149224000000002</v>
+      </c>
+      <c r="N4">
+        <v>33.58507760000001</v>
+      </c>
+      <c r="O4">
+        <v>11.75477716</v>
+      </c>
+      <c r="P4">
+        <v>21.83030044</v>
+      </c>
+      <c r="Q4">
+        <v>33.13030044</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.0961857634945367</v>
+      </c>
+      <c r="T4">
+        <v>0.7781311298977936</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.35</v>
+      </c>
+      <c r="W4">
+        <v>0.029705</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>42.21260821889299</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09456697751086321</v>
+      </c>
+      <c r="C5">
+        <v>858.9119507136497</v>
+      </c>
+      <c r="D5">
+        <v>849.6599507136498</v>
+      </c>
+      <c r="E5">
+        <v>-26.152</v>
+      </c>
+      <c r="F5">
+        <v>26.748</v>
+      </c>
+      <c r="G5">
+        <v>36</v>
+      </c>
+      <c r="H5">
+        <v>838.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>45.7</v>
+      </c>
+      <c r="K5">
+        <v>11.3</v>
+      </c>
+      <c r="L5">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M5">
+        <v>1.2223836</v>
+      </c>
+      <c r="N5">
+        <v>33.17761640000001</v>
+      </c>
+      <c r="O5">
+        <v>11.61216574</v>
+      </c>
+      <c r="P5">
+        <v>21.56545066</v>
+      </c>
+      <c r="Q5">
+        <v>32.86545066000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.0965730180524363</v>
+      </c>
+      <c r="T5">
+        <v>0.783382167931385</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.35</v>
+      </c>
+      <c r="W5">
+        <v>0.029705</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>28.14173881259533</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09427780679708048</v>
+      </c>
+      <c r="C6">
+        <v>854.4246905756841</v>
+      </c>
+      <c r="D6">
+        <v>854.088690575684</v>
+      </c>
+      <c r="E6">
+        <v>-17.236</v>
+      </c>
+      <c r="F6">
+        <v>35.664</v>
+      </c>
+      <c r="G6">
+        <v>36</v>
+      </c>
+      <c r="H6">
+        <v>838.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>45.7</v>
+      </c>
+      <c r="K6">
+        <v>11.3</v>
+      </c>
+      <c r="L6">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M6">
+        <v>1.6298448</v>
+      </c>
+      <c r="N6">
+        <v>32.7701552</v>
+      </c>
+      <c r="O6">
+        <v>11.46955432</v>
+      </c>
+      <c r="P6">
+        <v>21.30060088</v>
+      </c>
+      <c r="Q6">
+        <v>32.60060088</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0969683404136255</v>
+      </c>
+      <c r="T6">
+        <v>0.7887426025906764</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.35</v>
+      </c>
+      <c r="W6">
+        <v>0.029705</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>21.10630410944649</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09398863608329772</v>
+      </c>
+      <c r="C7">
+        <v>849.9838407844115</v>
+      </c>
+      <c r="D7">
+        <v>858.5638407844116</v>
+      </c>
+      <c r="E7">
+        <v>-8.319999999999993</v>
+      </c>
+      <c r="F7">
+        <v>44.58000000000001</v>
+      </c>
+      <c r="G7">
+        <v>36</v>
+      </c>
+      <c r="H7">
+        <v>838.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>45.7</v>
+      </c>
+      <c r="K7">
+        <v>11.3</v>
+      </c>
+      <c r="L7">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M7">
+        <v>2.037306000000001</v>
+      </c>
+      <c r="N7">
+        <v>32.362694</v>
+      </c>
+      <c r="O7">
+        <v>11.3269429</v>
+      </c>
+      <c r="P7">
+        <v>21.03575110000001</v>
+      </c>
+      <c r="Q7">
+        <v>32.33575110000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09737198535083971</v>
+      </c>
+      <c r="T7">
+        <v>0.7942158885059528</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.35</v>
+      </c>
+      <c r="W7">
+        <v>0.029705</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>16.8850432875572</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.093699465369515</v>
+      </c>
+      <c r="C8">
+        <v>845.5901347083434</v>
+      </c>
+      <c r="D8">
+        <v>863.0861347083434</v>
+      </c>
+      <c r="E8">
+        <v>0.5960000000000036</v>
+      </c>
+      <c r="F8">
+        <v>53.496</v>
+      </c>
+      <c r="G8">
+        <v>36</v>
+      </c>
+      <c r="H8">
+        <v>838.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>45.7</v>
+      </c>
+      <c r="K8">
+        <v>11.3</v>
+      </c>
+      <c r="L8">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M8">
+        <v>2.4447672</v>
+      </c>
+      <c r="N8">
+        <v>31.9552328</v>
+      </c>
+      <c r="O8">
+        <v>11.18433148</v>
+      </c>
+      <c r="P8">
+        <v>20.77090132</v>
+      </c>
+      <c r="Q8">
+        <v>32.07090132</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09778421847820745</v>
+      </c>
+      <c r="T8">
+        <v>0.7998056273130436</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.35</v>
+      </c>
+      <c r="W8">
+        <v>0.029705</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>14.07086940629766</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09348309465573225</v>
+      </c>
+      <c r="C9">
+        <v>840.0892041040777</v>
+      </c>
+      <c r="D9">
+        <v>866.5012041040777</v>
+      </c>
+      <c r="E9">
+        <v>9.512000000000008</v>
+      </c>
+      <c r="F9">
+        <v>62.41200000000001</v>
+      </c>
+      <c r="G9">
+        <v>36</v>
+      </c>
+      <c r="H9">
+        <v>838.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>45.7</v>
+      </c>
+      <c r="K9">
+        <v>11.3</v>
+      </c>
+      <c r="L9">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M9">
+        <v>2.9520876</v>
+      </c>
+      <c r="N9">
+        <v>31.44791240000001</v>
+      </c>
+      <c r="O9">
+        <v>11.00676934</v>
+      </c>
+      <c r="P9">
+        <v>20.44114306000001</v>
+      </c>
+      <c r="Q9">
+        <v>31.74114306000001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.0982053168341207</v>
+      </c>
+      <c r="T9">
+        <v>0.8055155755568459</v>
+      </c>
+      <c r="U9">
+        <v>0.0473</v>
+      </c>
+      <c r="V9">
+        <v>0.35</v>
+      </c>
+      <c r="W9">
+        <v>0.030745</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>11.65277073756212</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09340192394194952</v>
+      </c>
+      <c r="C10">
+        <v>832.461336758625</v>
+      </c>
+      <c r="D10">
+        <v>867.7893367586249</v>
+      </c>
+      <c r="E10">
+        <v>18.428</v>
+      </c>
+      <c r="F10">
+        <v>71.328</v>
+      </c>
+      <c r="G10">
+        <v>36</v>
+      </c>
+      <c r="H10">
+        <v>838.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>45.7</v>
+      </c>
+      <c r="K10">
+        <v>11.3</v>
+      </c>
+      <c r="L10">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M10">
+        <v>3.6448608</v>
+      </c>
+      <c r="N10">
+        <v>30.75513920000001</v>
+      </c>
+      <c r="O10">
+        <v>10.76429872</v>
+      </c>
+      <c r="P10">
+        <v>19.99084048</v>
+      </c>
+      <c r="Q10">
+        <v>31.29084048</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09863556950211903</v>
+      </c>
+      <c r="T10">
+        <v>0.8113496531102963</v>
+      </c>
+      <c r="U10">
+        <v>0.0511</v>
+      </c>
+      <c r="V10">
+        <v>0.35</v>
+      </c>
+      <c r="W10">
+        <v>0.033215</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>9.437946162443296</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09314785322816677</v>
+      </c>
+      <c r="C11">
+        <v>827.6021640867934</v>
+      </c>
+      <c r="D11">
+        <v>871.8461640867935</v>
+      </c>
+      <c r="E11">
+        <v>27.344</v>
+      </c>
+      <c r="F11">
+        <v>80.244</v>
+      </c>
+      <c r="G11">
+        <v>36</v>
+      </c>
+      <c r="H11">
+        <v>838.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>45.7</v>
+      </c>
+      <c r="K11">
+        <v>11.3</v>
+      </c>
+      <c r="L11">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M11">
+        <v>4.1004684</v>
+      </c>
+      <c r="N11">
+        <v>30.29953160000001</v>
+      </c>
+      <c r="O11">
+        <v>10.60483606</v>
+      </c>
+      <c r="P11">
+        <v>19.69469554</v>
+      </c>
+      <c r="Q11">
+        <v>30.99469554000001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09907527827271073</v>
+      </c>
+      <c r="T11">
+        <v>0.8173119521484378</v>
+      </c>
+      <c r="U11">
+        <v>0.0511</v>
+      </c>
+      <c r="V11">
+        <v>0.35</v>
+      </c>
+      <c r="W11">
+        <v>0.033215</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>8.389285477727377</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09301728251438404</v>
+      </c>
+      <c r="C12">
+        <v>820.7858188587445</v>
+      </c>
+      <c r="D12">
+        <v>873.9458188587445</v>
+      </c>
+      <c r="E12">
+        <v>36.26000000000001</v>
+      </c>
+      <c r="F12">
+        <v>89.16000000000001</v>
+      </c>
+      <c r="G12">
+        <v>36</v>
+      </c>
+      <c r="H12">
+        <v>838.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>45.7</v>
+      </c>
+      <c r="K12">
+        <v>11.3</v>
+      </c>
+      <c r="L12">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M12">
+        <v>4.725480000000001</v>
+      </c>
+      <c r="N12">
+        <v>29.67452</v>
+      </c>
+      <c r="O12">
+        <v>10.386082</v>
+      </c>
+      <c r="P12">
+        <v>19.288438</v>
+      </c>
+      <c r="Q12">
+        <v>30.588438</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.0995247583493156</v>
+      </c>
+      <c r="T12">
+        <v>0.8234067467207602</v>
+      </c>
+      <c r="U12">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.35</v>
+      </c>
+      <c r="W12">
+        <v>0.03445</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>7.279683756993999</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.0927755618006013</v>
+      </c>
+      <c r="C13">
+        <v>815.7836420797494</v>
+      </c>
+      <c r="D13">
+        <v>877.8596420797494</v>
+      </c>
+      <c r="E13">
+        <v>45.17600000000001</v>
+      </c>
+      <c r="F13">
+        <v>98.07600000000001</v>
+      </c>
+      <c r="G13">
+        <v>36</v>
+      </c>
+      <c r="H13">
+        <v>838.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>45.7</v>
+      </c>
+      <c r="K13">
+        <v>11.3</v>
+      </c>
+      <c r="L13">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M13">
+        <v>5.198028000000001</v>
+      </c>
+      <c r="N13">
+        <v>29.201972</v>
+      </c>
+      <c r="O13">
+        <v>10.2206902</v>
+      </c>
+      <c r="P13">
+        <v>18.9812818</v>
+      </c>
+      <c r="Q13">
+        <v>30.28128180000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09998433910179921</v>
+      </c>
+      <c r="T13">
+        <v>0.8296385029688653</v>
+      </c>
+      <c r="U13">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.35</v>
+      </c>
+      <c r="W13">
+        <v>0.03445</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>6.617894324539999</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09268984108681856</v>
+      </c>
+      <c r="C14">
+        <v>808.264023171297</v>
+      </c>
+      <c r="D14">
+        <v>879.256023171297</v>
+      </c>
+      <c r="E14">
+        <v>54.09200000000001</v>
+      </c>
+      <c r="F14">
+        <v>106.992</v>
+      </c>
+      <c r="G14">
+        <v>36</v>
+      </c>
+      <c r="H14">
+        <v>838.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>45.7</v>
+      </c>
+      <c r="K14">
+        <v>11.3</v>
+      </c>
+      <c r="L14">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M14">
+        <v>5.88456</v>
+      </c>
+      <c r="N14">
+        <v>28.51544000000001</v>
+      </c>
+      <c r="O14">
+        <v>9.980404000000002</v>
+      </c>
+      <c r="P14">
+        <v>18.53503600000001</v>
+      </c>
+      <c r="Q14">
+        <v>29.83503600000001</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1004543648713847</v>
+      </c>
+      <c r="T14">
+        <v>0.8360118900407907</v>
+      </c>
+      <c r="U14">
+        <v>0.055</v>
+      </c>
+      <c r="V14">
+        <v>0.35</v>
+      </c>
+      <c r="W14">
+        <v>0.03575</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.845806653343666</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.0924611203730358</v>
+      </c>
+      <c r="C15">
+        <v>803.0956912002071</v>
+      </c>
+      <c r="D15">
+        <v>883.0036912002071</v>
+      </c>
+      <c r="E15">
+        <v>63.008</v>
+      </c>
+      <c r="F15">
+        <v>115.908</v>
+      </c>
+      <c r="G15">
+        <v>36</v>
+      </c>
+      <c r="H15">
+        <v>838.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>45.7</v>
+      </c>
+      <c r="K15">
+        <v>11.3</v>
+      </c>
+      <c r="L15">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M15">
+        <v>6.37494</v>
+      </c>
+      <c r="N15">
+        <v>28.02506</v>
+      </c>
+      <c r="O15">
+        <v>9.808771</v>
+      </c>
+      <c r="P15">
+        <v>18.216289</v>
+      </c>
+      <c r="Q15">
+        <v>29.516289</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1009351958310756</v>
+      </c>
+      <c r="T15">
+        <v>0.8425317917580478</v>
+      </c>
+      <c r="U15">
+        <v>0.055</v>
+      </c>
+      <c r="V15">
+        <v>0.35</v>
+      </c>
+      <c r="W15">
+        <v>0.03575</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.396129218471076</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09223239965925308</v>
+      </c>
+      <c r="C16">
+        <v>797.9594434818196</v>
+      </c>
+      <c r="D16">
+        <v>886.7834434818196</v>
+      </c>
+      <c r="E16">
+        <v>71.92400000000001</v>
+      </c>
+      <c r="F16">
+        <v>124.824</v>
+      </c>
+      <c r="G16">
+        <v>36</v>
+      </c>
+      <c r="H16">
+        <v>838.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>45.7</v>
+      </c>
+      <c r="K16">
+        <v>11.3</v>
+      </c>
+      <c r="L16">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M16">
+        <v>6.865320000000001</v>
+      </c>
+      <c r="N16">
+        <v>27.53468000000001</v>
+      </c>
+      <c r="O16">
+        <v>9.637138000000002</v>
+      </c>
+      <c r="P16">
+        <v>17.897542</v>
+      </c>
+      <c r="Q16">
+        <v>29.197542</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1014272089061082</v>
+      </c>
+      <c r="T16">
+        <v>0.8492033190966367</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0.35</v>
+      </c>
+      <c r="W16">
+        <v>0.03575</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.010691417151714</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09200367894547035</v>
+      </c>
+      <c r="C17">
+        <v>792.8556938033011</v>
+      </c>
+      <c r="D17">
+        <v>890.5956938033011</v>
+      </c>
+      <c r="E17">
+        <v>80.84</v>
+      </c>
+      <c r="F17">
+        <v>133.74</v>
+      </c>
+      <c r="G17">
+        <v>36</v>
+      </c>
+      <c r="H17">
+        <v>838.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>45.7</v>
+      </c>
+      <c r="K17">
+        <v>11.3</v>
+      </c>
+      <c r="L17">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M17">
+        <v>7.355700000000001</v>
+      </c>
+      <c r="N17">
+        <v>27.04430000000001</v>
+      </c>
+      <c r="O17">
+        <v>9.465505000000002</v>
+      </c>
+      <c r="P17">
+        <v>17.57879500000001</v>
+      </c>
+      <c r="Q17">
+        <v>28.87879500000001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1019307987593769</v>
+      </c>
+      <c r="T17">
+        <v>0.8560318235490745</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.35</v>
+      </c>
+      <c r="W17">
+        <v>0.03575</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.676645322674933</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09217015823168759</v>
+      </c>
+      <c r="C18">
+        <v>781.1616294256601</v>
+      </c>
+      <c r="D18">
+        <v>887.8176294256601</v>
+      </c>
+      <c r="E18">
+        <v>89.756</v>
+      </c>
+      <c r="F18">
+        <v>142.656</v>
+      </c>
+      <c r="G18">
+        <v>36</v>
+      </c>
+      <c r="H18">
+        <v>838.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>45.7</v>
+      </c>
+      <c r="K18">
+        <v>11.3</v>
+      </c>
+      <c r="L18">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M18">
+        <v>8.388172800000001</v>
+      </c>
+      <c r="N18">
+        <v>26.01182720000001</v>
+      </c>
+      <c r="O18">
+        <v>9.104139520000002</v>
+      </c>
+      <c r="P18">
+        <v>16.90768768</v>
+      </c>
+      <c r="Q18">
+        <v>28.20768768</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1024463788472471</v>
+      </c>
+      <c r="T18">
+        <v>0.8630229114408561</v>
+      </c>
+      <c r="U18">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.35</v>
+      </c>
+      <c r="W18">
+        <v>0.03822</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.10101232058548</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09243023751790484</v>
+      </c>
+      <c r="C19">
+        <v>767.9401669470531</v>
+      </c>
+      <c r="D19">
+        <v>883.5121669470531</v>
+      </c>
+      <c r="E19">
+        <v>98.672</v>
+      </c>
+      <c r="F19">
+        <v>151.572</v>
+      </c>
+      <c r="G19">
+        <v>36</v>
+      </c>
+      <c r="H19">
+        <v>838.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>45.7</v>
+      </c>
+      <c r="K19">
+        <v>11.3</v>
+      </c>
+      <c r="L19">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M19">
+        <v>9.549036000000001</v>
+      </c>
+      <c r="N19">
+        <v>24.850964</v>
+      </c>
+      <c r="O19">
+        <v>8.697837400000001</v>
+      </c>
+      <c r="P19">
+        <v>16.1531266</v>
+      </c>
+      <c r="Q19">
+        <v>27.4531266</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1029743825516926</v>
+      </c>
+      <c r="T19">
+        <v>0.8701824592818372</v>
+      </c>
+      <c r="U19">
+        <v>0.063</v>
+      </c>
+      <c r="V19">
+        <v>0.35</v>
+      </c>
+      <c r="W19">
+        <v>0.04095</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>3.602457881612343</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09308421680412213</v>
+      </c>
+      <c r="C20">
+        <v>748.3802138733772</v>
+      </c>
+      <c r="D20">
+        <v>872.8682138733773</v>
+      </c>
+      <c r="E20">
+        <v>107.588</v>
+      </c>
+      <c r="F20">
+        <v>160.488</v>
+      </c>
+      <c r="G20">
+        <v>36</v>
+      </c>
+      <c r="H20">
+        <v>838.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>45.7</v>
+      </c>
+      <c r="K20">
+        <v>11.3</v>
+      </c>
+      <c r="L20">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M20">
+        <v>11.2502088</v>
+      </c>
+      <c r="N20">
+        <v>23.14979120000001</v>
+      </c>
+      <c r="O20">
+        <v>8.102426920000001</v>
+      </c>
+      <c r="P20">
+        <v>15.04736428000001</v>
+      </c>
+      <c r="Q20">
+        <v>26.34736428000001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1035152643952709</v>
+      </c>
+      <c r="T20">
+        <v>0.877516630240891</v>
+      </c>
+      <c r="U20">
+        <v>0.0701</v>
+      </c>
+      <c r="V20">
+        <v>0.35</v>
+      </c>
+      <c r="W20">
+        <v>0.045565</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.057721026475527</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.0955841960903394</v>
+      </c>
+      <c r="C21">
+        <v>701.0353444955442</v>
+      </c>
+      <c r="D21">
+        <v>834.4393444955442</v>
+      </c>
+      <c r="E21">
+        <v>116.504</v>
+      </c>
+      <c r="F21">
+        <v>169.404</v>
+      </c>
+      <c r="G21">
+        <v>36</v>
+      </c>
+      <c r="H21">
+        <v>838.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>45.7</v>
+      </c>
+      <c r="K21">
+        <v>11.3</v>
+      </c>
+      <c r="L21">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M21">
+        <v>15.4835256</v>
+      </c>
+      <c r="N21">
+        <v>18.91647440000001</v>
+      </c>
+      <c r="O21">
+        <v>6.620766040000001</v>
+      </c>
+      <c r="P21">
+        <v>12.29570836</v>
+      </c>
+      <c r="Q21">
+        <v>23.59570836</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.104069501346098</v>
+      </c>
+      <c r="T21">
+        <v>0.8850318918409094</v>
+      </c>
+      <c r="U21">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.35</v>
+      </c>
+      <c r="W21">
+        <v>0.05941</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.221716222047</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09559207537655665</v>
+      </c>
+      <c r="C22">
+        <v>692.0035750614704</v>
+      </c>
+      <c r="D22">
+        <v>834.3235750614705</v>
+      </c>
+      <c r="E22">
+        <v>125.42</v>
+      </c>
+      <c r="F22">
+        <v>178.32</v>
+      </c>
+      <c r="G22">
+        <v>36</v>
+      </c>
+      <c r="H22">
+        <v>838.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>45.7</v>
+      </c>
+      <c r="K22">
+        <v>11.3</v>
+      </c>
+      <c r="L22">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M22">
+        <v>16.298448</v>
+      </c>
+      <c r="N22">
+        <v>18.101552</v>
+      </c>
+      <c r="O22">
+        <v>6.3355432</v>
+      </c>
+      <c r="P22">
+        <v>11.7660088</v>
+      </c>
+      <c r="Q22">
+        <v>23.0660088</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1046375942206958</v>
+      </c>
+      <c r="T22">
+        <v>0.892735034980928</v>
+      </c>
+      <c r="U22">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V22">
+        <v>0.35</v>
+      </c>
+      <c r="W22">
+        <v>0.05941</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.110630410944649</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09559995466277391</v>
+      </c>
+      <c r="C23">
+        <v>682.9718377464542</v>
+      </c>
+      <c r="D23">
+        <v>834.2078377464542</v>
+      </c>
+      <c r="E23">
+        <v>134.336</v>
+      </c>
+      <c r="F23">
+        <v>187.236</v>
+      </c>
+      <c r="G23">
+        <v>36</v>
+      </c>
+      <c r="H23">
+        <v>838.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>45.7</v>
+      </c>
+      <c r="K23">
+        <v>11.3</v>
+      </c>
+      <c r="L23">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M23">
+        <v>17.1133704</v>
+      </c>
+      <c r="N23">
+        <v>17.2866296</v>
+      </c>
+      <c r="O23">
+        <v>6.050320360000002</v>
+      </c>
+      <c r="P23">
+        <v>11.23630924</v>
+      </c>
+      <c r="Q23">
+        <v>22.53630924</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1052200691933847</v>
+      </c>
+      <c r="T23">
+        <v>0.9006331944029723</v>
+      </c>
+      <c r="U23">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.35</v>
+      </c>
+      <c r="W23">
+        <v>0.05941</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.010124200899666</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09862513394899117</v>
+      </c>
+      <c r="C24">
+        <v>631.8724257828071</v>
+      </c>
+      <c r="D24">
+        <v>792.0244257828072</v>
+      </c>
+      <c r="E24">
+        <v>143.252</v>
+      </c>
+      <c r="F24">
+        <v>196.152</v>
+      </c>
+      <c r="G24">
+        <v>36</v>
+      </c>
+      <c r="H24">
+        <v>838.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>45.7</v>
+      </c>
+      <c r="K24">
+        <v>11.3</v>
+      </c>
+      <c r="L24">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M24">
+        <v>22.0671</v>
+      </c>
+      <c r="N24">
+        <v>12.3329</v>
+      </c>
+      <c r="O24">
+        <v>4.316515000000001</v>
+      </c>
+      <c r="P24">
+        <v>8.016385000000001</v>
+      </c>
+      <c r="Q24">
+        <v>19.316385</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1058174794217835</v>
+      </c>
+      <c r="T24">
+        <v>0.9087338707332743</v>
+      </c>
+      <c r="U24">
+        <v>0.1125</v>
+      </c>
+      <c r="V24">
+        <v>0.35</v>
+      </c>
+      <c r="W24">
+        <v>0.07312500000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>1.558881774224977</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1143346377350491</v>
+      </c>
+      <c r="C25">
+        <v>458.2331797519075</v>
+      </c>
+      <c r="D25">
+        <v>627.3011797519075</v>
+      </c>
+      <c r="E25">
+        <v>152.168</v>
+      </c>
+      <c r="F25">
+        <v>205.068</v>
+      </c>
+      <c r="G25">
+        <v>36</v>
+      </c>
+      <c r="H25">
+        <v>838.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>45.7</v>
+      </c>
+      <c r="K25">
+        <v>11.3</v>
+      </c>
+      <c r="L25">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M25">
+        <v>40.3163688</v>
+      </c>
+      <c r="N25">
+        <v>-5.916368799999994</v>
+      </c>
+      <c r="O25">
+        <v>-2.070729079999998</v>
+      </c>
+      <c r="P25">
+        <v>-3.845639719999996</v>
+      </c>
+      <c r="Q25">
+        <v>7.454360280000005</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1072992871484064</v>
+      </c>
+      <c r="T25">
+        <v>0.9288266716370758</v>
+      </c>
+      <c r="U25">
+        <v>0.1966</v>
+      </c>
+      <c r="V25">
+        <v>0.2986380063077507</v>
+      </c>
+      <c r="W25">
+        <v>0.1378877679598962</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.8532514465935733</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1159126377350491</v>
+      </c>
+      <c r="C26">
+        <v>436.4803570115204</v>
+      </c>
+      <c r="D26">
+        <v>614.4643570115204</v>
+      </c>
+      <c r="E26">
+        <v>161.084</v>
+      </c>
+      <c r="F26">
+        <v>213.984</v>
+      </c>
+      <c r="G26">
+        <v>36</v>
+      </c>
+      <c r="H26">
+        <v>838.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>45.7</v>
+      </c>
+      <c r="K26">
+        <v>11.3</v>
+      </c>
+      <c r="L26">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M26">
+        <v>42.0692544</v>
+      </c>
+      <c r="N26">
+        <v>-7.669254399999993</v>
+      </c>
+      <c r="O26">
+        <v>-2.684239039999997</v>
+      </c>
+      <c r="P26">
+        <v>-4.985015359999995</v>
+      </c>
+      <c r="Q26">
+        <v>6.314984640000006</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1082005935582539</v>
+      </c>
+      <c r="T26">
+        <v>0.9410480752112479</v>
+      </c>
+      <c r="U26">
+        <v>0.1966</v>
+      </c>
+      <c r="V26">
+        <v>0.2861947560449277</v>
+      </c>
+      <c r="W26">
+        <v>0.1403341109615672</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.8176993029855077</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1221035875153323</v>
+      </c>
+      <c r="C27">
+        <v>381.8986409301795</v>
+      </c>
+      <c r="D27">
+        <v>568.7986409301794</v>
+      </c>
+      <c r="E27">
+        <v>170</v>
+      </c>
+      <c r="F27">
+        <v>222.9</v>
+      </c>
+      <c r="G27">
+        <v>36</v>
+      </c>
+      <c r="H27">
+        <v>838.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>45.7</v>
+      </c>
+      <c r="K27">
+        <v>11.3</v>
+      </c>
+      <c r="L27">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M27">
+        <v>47.65602</v>
+      </c>
+      <c r="N27">
+        <v>-13.25601999999999</v>
+      </c>
+      <c r="O27">
+        <v>-4.639606999999997</v>
+      </c>
+      <c r="P27">
+        <v>-8.616412999999994</v>
+      </c>
+      <c r="Q27">
+        <v>2.683587000000006</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1095432011794082</v>
+      </c>
+      <c r="T27">
+        <v>0.9592533707695726</v>
+      </c>
+      <c r="U27">
+        <v>0.2138</v>
+      </c>
+      <c r="V27">
+        <v>0.2526438422679863</v>
+      </c>
+      <c r="W27">
+        <v>0.1597847465231045</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.7218395493371038</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1238535875153323</v>
+      </c>
+      <c r="C28">
+        <v>361.2794588457273</v>
+      </c>
+      <c r="D28">
+        <v>557.0954588457273</v>
+      </c>
+      <c r="E28">
+        <v>178.916</v>
+      </c>
+      <c r="F28">
+        <v>231.816</v>
+      </c>
+      <c r="G28">
+        <v>36</v>
+      </c>
+      <c r="H28">
+        <v>838.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>45.7</v>
+      </c>
+      <c r="K28">
+        <v>11.3</v>
+      </c>
+      <c r="L28">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M28">
+        <v>49.5622608</v>
+      </c>
+      <c r="N28">
+        <v>-15.16226079999999</v>
+      </c>
+      <c r="O28">
+        <v>-5.306791279999997</v>
+      </c>
+      <c r="P28">
+        <v>-9.855469519999994</v>
+      </c>
+      <c r="Q28">
+        <v>1.444530480000006</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1104991903845353</v>
+      </c>
+      <c r="T28">
+        <v>0.9722162541583507</v>
+      </c>
+      <c r="U28">
+        <v>0.2138</v>
+      </c>
+      <c r="V28">
+        <v>0.2429267714115253</v>
+      </c>
+      <c r="W28">
+        <v>0.1618622562722159</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.6940764897472153</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1256035875153323</v>
+      </c>
+      <c r="C29">
+        <v>341.1321597613682</v>
+      </c>
+      <c r="D29">
+        <v>545.8641597613682</v>
+      </c>
+      <c r="E29">
+        <v>187.832</v>
+      </c>
+      <c r="F29">
+        <v>240.732</v>
+      </c>
+      <c r="G29">
+        <v>36</v>
+      </c>
+      <c r="H29">
+        <v>838.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>45.7</v>
+      </c>
+      <c r="K29">
+        <v>11.3</v>
+      </c>
+      <c r="L29">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M29">
+        <v>51.4685016</v>
+      </c>
+      <c r="N29">
+        <v>-17.0685016</v>
+      </c>
+      <c r="O29">
+        <v>-5.973975559999999</v>
+      </c>
+      <c r="P29">
+        <v>-11.09452604</v>
+      </c>
+      <c r="Q29">
+        <v>0.2054739600000026</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1114813710747344</v>
+      </c>
+      <c r="T29">
+        <v>0.9855342850372323</v>
+      </c>
+      <c r="U29">
+        <v>0.2138</v>
+      </c>
+      <c r="V29">
+        <v>0.2339294835814688</v>
+      </c>
+      <c r="W29">
+        <v>0.163785876410282</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.6683699530899109</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1273535875153323</v>
+      </c>
+      <c r="C30">
+        <v>321.4287675575572</v>
+      </c>
+      <c r="D30">
+        <v>535.0767675575572</v>
+      </c>
+      <c r="E30">
+        <v>196.748</v>
+      </c>
+      <c r="F30">
+        <v>249.648</v>
+      </c>
+      <c r="G30">
+        <v>36</v>
+      </c>
+      <c r="H30">
+        <v>838.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>45.7</v>
+      </c>
+      <c r="K30">
+        <v>11.3</v>
+      </c>
+      <c r="L30">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M30">
+        <v>53.3747424</v>
+      </c>
+      <c r="N30">
+        <v>-18.9747424</v>
+      </c>
+      <c r="O30">
+        <v>-6.641159839999998</v>
+      </c>
+      <c r="P30">
+        <v>-12.33358256</v>
+      </c>
+      <c r="Q30">
+        <v>-1.033582559999997</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1124908345618835</v>
+      </c>
+      <c r="T30">
+        <v>0.9992222612183049</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.2255748591678449</v>
+      </c>
+      <c r="W30">
+        <v>0.1655720951099147</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.6444995976224142</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1291035875153322</v>
+      </c>
+      <c r="C31">
+        <v>302.1434747200304</v>
+      </c>
+      <c r="D31">
+        <v>524.7074747200304</v>
+      </c>
+      <c r="E31">
+        <v>205.664</v>
+      </c>
+      <c r="F31">
+        <v>258.564</v>
+      </c>
+      <c r="G31">
+        <v>36</v>
+      </c>
+      <c r="H31">
+        <v>838.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>45.7</v>
+      </c>
+      <c r="K31">
+        <v>11.3</v>
+      </c>
+      <c r="L31">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M31">
+        <v>55.28098319999999</v>
+      </c>
+      <c r="N31">
+        <v>-20.88098319999998</v>
+      </c>
+      <c r="O31">
+        <v>-7.308344119999993</v>
+      </c>
+      <c r="P31">
+        <v>-13.57263907999999</v>
+      </c>
+      <c r="Q31">
+        <v>-2.272639079999987</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1135287336402199</v>
+      </c>
+      <c r="T31">
+        <v>1.013295814193211</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.2177964157482641</v>
+      </c>
+      <c r="W31">
+        <v>0.1672351263130211</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.622275473566469</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1308535875153323</v>
+      </c>
+      <c r="C32">
+        <v>283.2524362066523</v>
+      </c>
+      <c r="D32">
+        <v>514.7324362066523</v>
+      </c>
+      <c r="E32">
+        <v>214.58</v>
+      </c>
+      <c r="F32">
+        <v>267.48</v>
+      </c>
+      <c r="G32">
+        <v>36</v>
+      </c>
+      <c r="H32">
+        <v>838.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>45.7</v>
+      </c>
+      <c r="K32">
+        <v>11.3</v>
+      </c>
+      <c r="L32">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M32">
+        <v>57.187224</v>
+      </c>
+      <c r="N32">
+        <v>-22.78722399999999</v>
+      </c>
+      <c r="O32">
+        <v>-7.975528399999997</v>
+      </c>
+      <c r="P32">
+        <v>-14.8116956</v>
+      </c>
+      <c r="Q32">
+        <v>-3.511695599999996</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1145962869779373</v>
+      </c>
+      <c r="T32">
+        <v>1.027771468681685</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.2105365352233219</v>
+      </c>
+      <c r="W32">
+        <v>0.1687872887692538</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.6015329577809199</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1326035875153322</v>
+      </c>
+      <c r="C33">
+        <v>264.7335863879884</v>
+      </c>
+      <c r="D33">
+        <v>505.1295863879885</v>
+      </c>
+      <c r="E33">
+        <v>223.496</v>
+      </c>
+      <c r="F33">
+        <v>276.396</v>
+      </c>
+      <c r="G33">
+        <v>36</v>
+      </c>
+      <c r="H33">
+        <v>838.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>45.7</v>
+      </c>
+      <c r="K33">
+        <v>11.3</v>
+      </c>
+      <c r="L33">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M33">
+        <v>59.0934648</v>
+      </c>
+      <c r="N33">
+        <v>-24.69346479999999</v>
+      </c>
+      <c r="O33">
+        <v>-8.642712679999997</v>
+      </c>
+      <c r="P33">
+        <v>-16.05075212</v>
+      </c>
+      <c r="Q33">
+        <v>-4.750752119999998</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1156947838906611</v>
+      </c>
+      <c r="T33">
+        <v>1.042666707358231</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.2037450340870857</v>
+      </c>
+      <c r="W33">
+        <v>0.170239311712181</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5821286688202449</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1343535875153323</v>
+      </c>
+      <c r="C34">
+        <v>246.5664761035404</v>
+      </c>
+      <c r="D34">
+        <v>495.8784761035403</v>
+      </c>
+      <c r="E34">
+        <v>232.412</v>
+      </c>
+      <c r="F34">
+        <v>285.312</v>
+      </c>
+      <c r="G34">
+        <v>36</v>
+      </c>
+      <c r="H34">
+        <v>838.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>45.7</v>
+      </c>
+      <c r="K34">
+        <v>11.3</v>
+      </c>
+      <c r="L34">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M34">
+        <v>60.9997056</v>
+      </c>
+      <c r="N34">
+        <v>-26.59970559999999</v>
+      </c>
+      <c r="O34">
+        <v>-9.309896959999996</v>
+      </c>
+      <c r="P34">
+        <v>-17.28980864</v>
+      </c>
+      <c r="Q34">
+        <v>-5.989808639999996</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.116825589536112</v>
+      </c>
+      <c r="T34">
+        <v>1.05800004128997</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1973780017718643</v>
+      </c>
+      <c r="W34">
+        <v>0.1716005832211754</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.5639371479196124</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1361035875153322</v>
+      </c>
+      <c r="C35">
+        <v>228.7321273011958</v>
+      </c>
+      <c r="D35">
+        <v>486.9601273011959</v>
+      </c>
+      <c r="E35">
+        <v>241.328</v>
+      </c>
+      <c r="F35">
+        <v>294.228</v>
+      </c>
+      <c r="G35">
+        <v>36</v>
+      </c>
+      <c r="H35">
+        <v>838.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>45.7</v>
+      </c>
+      <c r="K35">
+        <v>11.3</v>
+      </c>
+      <c r="L35">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M35">
+        <v>62.9059464</v>
+      </c>
+      <c r="N35">
+        <v>-28.50594639999999</v>
+      </c>
+      <c r="O35">
+        <v>-9.977081239999997</v>
+      </c>
+      <c r="P35">
+        <v>-18.52886516</v>
+      </c>
+      <c r="Q35">
+        <v>-7.228865159999994</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1179901505739644</v>
+      </c>
+      <c r="T35">
+        <v>1.073791086682358</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1913968502030199</v>
+      </c>
+      <c r="W35">
+        <v>0.1728793534265943</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.5468481434371999</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1378535875153322</v>
+      </c>
+      <c r="C36">
+        <v>211.2129030853624</v>
+      </c>
+      <c r="D36">
+        <v>478.3569030853624</v>
+      </c>
+      <c r="E36">
+        <v>250.244</v>
+      </c>
+      <c r="F36">
+        <v>303.144</v>
+      </c>
+      <c r="G36">
+        <v>36</v>
+      </c>
+      <c r="H36">
+        <v>838.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>45.7</v>
+      </c>
+      <c r="K36">
+        <v>11.3</v>
+      </c>
+      <c r="L36">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M36">
+        <v>64.8121872</v>
+      </c>
+      <c r="N36">
+        <v>-30.41218719999999</v>
+      </c>
+      <c r="O36">
+        <v>-10.64426552</v>
+      </c>
+      <c r="P36">
+        <v>-19.76792167999999</v>
+      </c>
+      <c r="Q36">
+        <v>-8.467921679999993</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1191900013402366</v>
+      </c>
+      <c r="T36">
+        <v>1.090060648601787</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1857675310794017</v>
+      </c>
+      <c r="W36">
+        <v>0.1740829018552239</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.5307643745125763</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1396035875153323</v>
+      </c>
+      <c r="C37">
+        <v>193.9923913012747</v>
+      </c>
+      <c r="D37">
+        <v>470.0523913012747</v>
+      </c>
+      <c r="E37">
+        <v>259.1600000000001</v>
+      </c>
+      <c r="F37">
+        <v>312.0600000000001</v>
+      </c>
+      <c r="G37">
+        <v>36</v>
+      </c>
+      <c r="H37">
+        <v>838.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>45.7</v>
+      </c>
+      <c r="K37">
+        <v>11.3</v>
+      </c>
+      <c r="L37">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M37">
+        <v>66.718428</v>
+      </c>
+      <c r="N37">
+        <v>-32.318428</v>
+      </c>
+      <c r="O37">
+        <v>-11.3114498</v>
+      </c>
+      <c r="P37">
+        <v>-21.0069782</v>
+      </c>
+      <c r="Q37">
+        <v>-9.706978199999998</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1204267705916248</v>
+      </c>
+      <c r="T37">
+        <v>1.10683081242643</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1804598873342759</v>
+      </c>
+      <c r="W37">
+        <v>0.1752176760879318</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5155996780979313</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1413535875153323</v>
+      </c>
+      <c r="C38">
+        <v>177.0553000385799</v>
+      </c>
+      <c r="D38">
+        <v>462.0313000385799</v>
+      </c>
+      <c r="E38">
+        <v>268.076</v>
+      </c>
+      <c r="F38">
+        <v>320.976</v>
+      </c>
+      <c r="G38">
+        <v>36</v>
+      </c>
+      <c r="H38">
+        <v>838.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>45.7</v>
+      </c>
+      <c r="K38">
+        <v>11.3</v>
+      </c>
+      <c r="L38">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M38">
+        <v>68.62466879999999</v>
+      </c>
+      <c r="N38">
+        <v>-34.22466879999999</v>
+      </c>
+      <c r="O38">
+        <v>-11.97863408</v>
+      </c>
+      <c r="P38">
+        <v>-22.24603471999999</v>
+      </c>
+      <c r="Q38">
+        <v>-10.94603471999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.121702188882119</v>
+      </c>
+      <c r="T38">
+        <v>1.124125043870593</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1754471126861016</v>
+      </c>
+      <c r="W38">
+        <v>0.1762894073077115</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5012774648174332</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1527280733578422</v>
+      </c>
+      <c r="C39">
+        <v>122.0104722071949</v>
+      </c>
+      <c r="D39">
+        <v>415.9024722071949</v>
+      </c>
+      <c r="E39">
+        <v>276.992</v>
+      </c>
+      <c r="F39">
+        <v>329.892</v>
+      </c>
+      <c r="G39">
+        <v>36</v>
+      </c>
+      <c r="H39">
+        <v>838.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>45.7</v>
+      </c>
+      <c r="K39">
+        <v>11.3</v>
+      </c>
+      <c r="L39">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M39">
+        <v>78.7782096</v>
+      </c>
+      <c r="N39">
+        <v>-44.37820959999999</v>
+      </c>
+      <c r="O39">
+        <v>-15.53237336</v>
+      </c>
+      <c r="P39">
+        <v>-28.84583624</v>
+      </c>
+      <c r="Q39">
+        <v>-17.54583624</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1236125186143906</v>
+      </c>
+      <c r="T39">
+        <v>1.150028455144217</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.1528341410795404</v>
+      </c>
+      <c r="W39">
+        <v>0.2023032071102058</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.4366689745129725</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1547280733578423</v>
+      </c>
+      <c r="C40">
+        <v>105.919290904502</v>
+      </c>
+      <c r="D40">
+        <v>408.727290904502</v>
+      </c>
+      <c r="E40">
+        <v>285.908</v>
+      </c>
+      <c r="F40">
+        <v>338.808</v>
+      </c>
+      <c r="G40">
+        <v>36</v>
+      </c>
+      <c r="H40">
+        <v>838.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>45.7</v>
+      </c>
+      <c r="K40">
+        <v>11.3</v>
+      </c>
+      <c r="L40">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M40">
+        <v>80.9073504</v>
+      </c>
+      <c r="N40">
+        <v>-46.50735039999999</v>
+      </c>
+      <c r="O40">
+        <v>-16.27757264</v>
+      </c>
+      <c r="P40">
+        <v>-30.22977776</v>
+      </c>
+      <c r="Q40">
+        <v>-18.92977776</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1249804624630099</v>
+      </c>
+      <c r="T40">
+        <v>1.168577301194931</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.1488121899984998</v>
+      </c>
+      <c r="W40">
+        <v>0.2032636490283583</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.4251776857099996</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1567280733578423</v>
+      </c>
+      <c r="C41">
+        <v>90.07148443524409</v>
+      </c>
+      <c r="D41">
+        <v>401.7954844352441</v>
+      </c>
+      <c r="E41">
+        <v>294.8240000000001</v>
+      </c>
+      <c r="F41">
+        <v>347.724</v>
+      </c>
+      <c r="G41">
+        <v>36</v>
+      </c>
+      <c r="H41">
+        <v>838.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>45.7</v>
+      </c>
+      <c r="K41">
+        <v>11.3</v>
+      </c>
+      <c r="L41">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M41">
+        <v>83.03649120000001</v>
+      </c>
+      <c r="N41">
+        <v>-48.63649120000001</v>
+      </c>
+      <c r="O41">
+        <v>-17.02277192</v>
+      </c>
+      <c r="P41">
+        <v>-31.61371928000001</v>
+      </c>
+      <c r="Q41">
+        <v>-20.31371928000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1263932569296166</v>
+      </c>
+      <c r="T41">
+        <v>1.187734306132552</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.1449964928190511</v>
+      </c>
+      <c r="W41">
+        <v>0.2041748375148106</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.4142756937687174</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1587280733578423</v>
+      </c>
+      <c r="C42">
+        <v>74.454876759569</v>
+      </c>
+      <c r="D42">
+        <v>395.094876759569</v>
+      </c>
+      <c r="E42">
+        <v>303.7400000000001</v>
+      </c>
+      <c r="F42">
+        <v>356.64</v>
+      </c>
+      <c r="G42">
+        <v>36</v>
+      </c>
+      <c r="H42">
+        <v>838.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>45.7</v>
+      </c>
+      <c r="K42">
+        <v>11.3</v>
+      </c>
+      <c r="L42">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M42">
+        <v>85.16563200000002</v>
+      </c>
+      <c r="N42">
+        <v>-50.76563200000001</v>
+      </c>
+      <c r="O42">
+        <v>-17.7679712</v>
+      </c>
+      <c r="P42">
+        <v>-32.99766080000001</v>
+      </c>
+      <c r="Q42">
+        <v>-21.6976608</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1278531445451102</v>
+      </c>
+      <c r="T42">
+        <v>1.207529877901429</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.1413715804985748</v>
+      </c>
+      <c r="W42">
+        <v>0.2050404665769404</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.4039188014244995</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1607280733578423</v>
+      </c>
+      <c r="C43">
+        <v>59.05809073746866</v>
+      </c>
+      <c r="D43">
+        <v>388.6140907374687</v>
+      </c>
+      <c r="E43">
+        <v>312.6560000000001</v>
+      </c>
+      <c r="F43">
+        <v>365.556</v>
+      </c>
+      <c r="G43">
+        <v>36</v>
+      </c>
+      <c r="H43">
+        <v>838.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>45.7</v>
+      </c>
+      <c r="K43">
+        <v>11.3</v>
+      </c>
+      <c r="L43">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M43">
+        <v>87.29477280000002</v>
+      </c>
+      <c r="N43">
+        <v>-52.89477280000001</v>
+      </c>
+      <c r="O43">
+        <v>-18.51317048</v>
+      </c>
+      <c r="P43">
+        <v>-34.38160232000001</v>
+      </c>
+      <c r="Q43">
+        <v>-23.08160232000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1293625198763833</v>
+      </c>
+      <c r="T43">
+        <v>1.227996486001453</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.1379234931693413</v>
+      </c>
+      <c r="W43">
+        <v>0.2058638698311613</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3940671233409752</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1627280733578423</v>
+      </c>
+      <c r="C44">
+        <v>43.87048366397948</v>
+      </c>
+      <c r="D44">
+        <v>382.3424836639795</v>
+      </c>
+      <c r="E44">
+        <v>321.572</v>
+      </c>
+      <c r="F44">
+        <v>374.472</v>
+      </c>
+      <c r="G44">
+        <v>36</v>
+      </c>
+      <c r="H44">
+        <v>838.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>45.7</v>
+      </c>
+      <c r="K44">
+        <v>11.3</v>
+      </c>
+      <c r="L44">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M44">
+        <v>89.42391360000001</v>
+      </c>
+      <c r="N44">
+        <v>-55.0239136</v>
+      </c>
+      <c r="O44">
+        <v>-19.25836976</v>
+      </c>
+      <c r="P44">
+        <v>-35.76554384000001</v>
+      </c>
+      <c r="Q44">
+        <v>-24.46554384000001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1309239426328726</v>
+      </c>
+      <c r="T44">
+        <v>1.249168839208374</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.1346396004748332</v>
+      </c>
+      <c r="W44">
+        <v>0.2066480634066098</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3846845727852376</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1647280733578422</v>
+      </c>
+      <c r="C45">
+        <v>28.88208894739404</v>
+      </c>
+      <c r="D45">
+        <v>376.270088947394</v>
+      </c>
+      <c r="E45">
+        <v>330.488</v>
+      </c>
+      <c r="F45">
+        <v>383.388</v>
+      </c>
+      <c r="G45">
+        <v>36</v>
+      </c>
+      <c r="H45">
+        <v>838.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>45.7</v>
+      </c>
+      <c r="K45">
+        <v>11.3</v>
+      </c>
+      <c r="L45">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M45">
+        <v>91.55305439999999</v>
+      </c>
+      <c r="N45">
+        <v>-57.15305439999999</v>
+      </c>
+      <c r="O45">
+        <v>-20.00356904</v>
+      </c>
+      <c r="P45">
+        <v>-37.14948535999999</v>
+      </c>
+      <c r="Q45">
+        <v>-25.84948535999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1325401521527476</v>
+      </c>
+      <c r="T45">
+        <v>1.271084082001503</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.1315084469754185</v>
+      </c>
+      <c r="W45">
+        <v>0.2073957828622701</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3757384199297671</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1667280733578423</v>
+      </c>
+      <c r="C46">
+        <v>14.08356325821404</v>
+      </c>
+      <c r="D46">
+        <v>370.3875632582141</v>
+      </c>
+      <c r="E46">
+        <v>339.4040000000001</v>
+      </c>
+      <c r="F46">
+        <v>392.304</v>
+      </c>
+      <c r="G46">
+        <v>36</v>
+      </c>
+      <c r="H46">
+        <v>838.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>45.7</v>
+      </c>
+      <c r="K46">
+        <v>11.3</v>
+      </c>
+      <c r="L46">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M46">
+        <v>93.68219520000001</v>
+      </c>
+      <c r="N46">
+        <v>-59.2821952</v>
+      </c>
+      <c r="O46">
+        <v>-20.74876832</v>
+      </c>
+      <c r="P46">
+        <v>-38.53342688000001</v>
+      </c>
+      <c r="Q46">
+        <v>-27.23342688000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1342140834411895</v>
+      </c>
+      <c r="T46">
+        <v>1.293782012037245</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.128519618635068</v>
+      </c>
+      <c r="W46">
+        <v>0.2081095150699458</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3671989103859087</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1687280733578422</v>
+      </c>
+      <c r="C47">
+        <v>-0.5338614406361444</v>
+      </c>
+      <c r="D47">
+        <v>364.6861385593639</v>
+      </c>
+      <c r="E47">
+        <v>348.3200000000001</v>
+      </c>
+      <c r="F47">
+        <v>401.22</v>
+      </c>
+      <c r="G47">
+        <v>36</v>
+      </c>
+      <c r="H47">
+        <v>838.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>45.7</v>
+      </c>
+      <c r="K47">
+        <v>11.3</v>
+      </c>
+      <c r="L47">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M47">
+        <v>95.81133600000001</v>
+      </c>
+      <c r="N47">
+        <v>-61.41133600000001</v>
+      </c>
+      <c r="O47">
+        <v>-21.4939676</v>
+      </c>
+      <c r="P47">
+        <v>-39.9173684</v>
+      </c>
+      <c r="Q47">
+        <v>-28.6173684</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.135948884958302</v>
+      </c>
+      <c r="T47">
+        <v>1.317305321347013</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.1256636271098443</v>
+      </c>
+      <c r="W47">
+        <v>0.2087915258461692</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3590389345995552</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1707280733578423</v>
+      </c>
+      <c r="C48">
+        <v>-14.97842150033159</v>
+      </c>
+      <c r="D48">
+        <v>359.1575784996684</v>
+      </c>
+      <c r="E48">
+        <v>357.236</v>
+      </c>
+      <c r="F48">
+        <v>410.136</v>
+      </c>
+      <c r="G48">
+        <v>36</v>
+      </c>
+      <c r="H48">
+        <v>838.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>45.7</v>
+      </c>
+      <c r="K48">
+        <v>11.3</v>
+      </c>
+      <c r="L48">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M48">
+        <v>97.94047680000001</v>
+      </c>
+      <c r="N48">
+        <v>-63.54047680000001</v>
+      </c>
+      <c r="O48">
+        <v>-22.23916688</v>
+      </c>
+      <c r="P48">
+        <v>-41.30130992000001</v>
+      </c>
+      <c r="Q48">
+        <v>-30.00130992000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1377479383834558</v>
+      </c>
+      <c r="T48">
+        <v>1.34169986433492</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.1229318091291955</v>
+      </c>
+      <c r="W48">
+        <v>0.2094438839799481</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.35123374036913</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1727280733578423</v>
+      </c>
+      <c r="C49">
+        <v>-29.25786128550692</v>
+      </c>
+      <c r="D49">
+        <v>353.7941387144931</v>
+      </c>
+      <c r="E49">
+        <v>366.152</v>
+      </c>
+      <c r="F49">
+        <v>419.052</v>
+      </c>
+      <c r="G49">
+        <v>36</v>
+      </c>
+      <c r="H49">
+        <v>838.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>45.7</v>
+      </c>
+      <c r="K49">
+        <v>11.3</v>
+      </c>
+      <c r="L49">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M49">
+        <v>100.0696176</v>
+      </c>
+      <c r="N49">
+        <v>-65.66961760000001</v>
+      </c>
+      <c r="O49">
+        <v>-22.98436616</v>
+      </c>
+      <c r="P49">
+        <v>-42.68525144000001</v>
+      </c>
+      <c r="Q49">
+        <v>-31.38525144000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1396148806171059</v>
+      </c>
+      <c r="T49">
+        <v>1.367014956114825</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.1203162387221913</v>
+      </c>
+      <c r="W49">
+        <v>0.2100684821931407</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3437606820634038</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1747280733578422</v>
+      </c>
+      <c r="C50">
+        <v>-43.37946936888051</v>
+      </c>
+      <c r="D50">
+        <v>348.5885306311195</v>
+      </c>
+      <c r="E50">
+        <v>375.068</v>
+      </c>
+      <c r="F50">
+        <v>427.968</v>
+      </c>
+      <c r="G50">
+        <v>36</v>
+      </c>
+      <c r="H50">
+        <v>838.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>45.7</v>
+      </c>
+      <c r="K50">
+        <v>11.3</v>
+      </c>
+      <c r="L50">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M50">
+        <v>102.1987584</v>
+      </c>
+      <c r="N50">
+        <v>-67.7987584</v>
+      </c>
+      <c r="O50">
+        <v>-23.72956544</v>
+      </c>
+      <c r="P50">
+        <v>-44.06919296</v>
+      </c>
+      <c r="Q50">
+        <v>-32.76919296</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.141553628321281</v>
+      </c>
+      <c r="T50">
+        <v>1.393303705270879</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.117809650415479</v>
+      </c>
+      <c r="W50">
+        <v>0.2106670554807836</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.336599001187083</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1767280733578422</v>
+      </c>
+      <c r="C51">
+        <v>-57.35011157687734</v>
+      </c>
+      <c r="D51">
+        <v>343.5338884231227</v>
+      </c>
+      <c r="E51">
+        <v>383.984</v>
+      </c>
+      <c r="F51">
+        <v>436.884</v>
+      </c>
+      <c r="G51">
+        <v>36</v>
+      </c>
+      <c r="H51">
+        <v>838.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>45.7</v>
+      </c>
+      <c r="K51">
+        <v>11.3</v>
+      </c>
+      <c r="L51">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M51">
+        <v>104.3278992</v>
+      </c>
+      <c r="N51">
+        <v>-69.9278992</v>
+      </c>
+      <c r="O51">
+        <v>-24.47476472</v>
+      </c>
+      <c r="P51">
+        <v>-45.45313448</v>
+      </c>
+      <c r="Q51">
+        <v>-34.15313448000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1435684053471885</v>
+      </c>
+      <c r="T51">
+        <v>1.420623385766386</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.1154053718355713</v>
+      </c>
+      <c r="W51">
+        <v>0.2112411972056656</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.329729633815918</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1787280733578422</v>
+      </c>
+      <c r="C52">
+        <v>-71.17626120131473</v>
+      </c>
+      <c r="D52">
+        <v>338.6237387986853</v>
+      </c>
+      <c r="E52">
+        <v>392.9</v>
+      </c>
+      <c r="F52">
+        <v>445.8</v>
+      </c>
+      <c r="G52">
+        <v>36</v>
+      </c>
+      <c r="H52">
+        <v>838.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>45.7</v>
+      </c>
+      <c r="K52">
+        <v>11.3</v>
+      </c>
+      <c r="L52">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M52">
+        <v>106.45704</v>
+      </c>
+      <c r="N52">
+        <v>-72.05704</v>
+      </c>
+      <c r="O52">
+        <v>-25.219964</v>
+      </c>
+      <c r="P52">
+        <v>-46.837076</v>
+      </c>
+      <c r="Q52">
+        <v>-35.537076</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1456637734541322</v>
+      </c>
+      <c r="T52">
+        <v>1.449035853481714</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.1130972643988599</v>
+      </c>
+      <c r="W52">
+        <v>0.2117923732615523</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3231350411395997</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1807280733578422</v>
+      </c>
+      <c r="C53">
+        <v>-84.86402665669311</v>
+      </c>
+      <c r="D53">
+        <v>333.8519733433069</v>
+      </c>
+      <c r="E53">
+        <v>401.816</v>
+      </c>
+      <c r="F53">
+        <v>454.716</v>
+      </c>
+      <c r="G53">
+        <v>36</v>
+      </c>
+      <c r="H53">
+        <v>838.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>45.7</v>
+      </c>
+      <c r="K53">
+        <v>11.3</v>
+      </c>
+      <c r="L53">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M53">
+        <v>108.5861808</v>
+      </c>
+      <c r="N53">
+        <v>-74.1861808</v>
+      </c>
+      <c r="O53">
+        <v>-25.96516328</v>
+      </c>
+      <c r="P53">
+        <v>-48.22101752</v>
+      </c>
+      <c r="Q53">
+        <v>-36.92101752000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1478446667899309</v>
+      </c>
+      <c r="T53">
+        <v>1.478608013756851</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.1108796709792744</v>
+      </c>
+      <c r="W53">
+        <v>0.2123219345701493</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3167990599407839</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1827280733578422</v>
+      </c>
+      <c r="C54">
+        <v>-98.41917683156231</v>
+      </c>
+      <c r="D54">
+        <v>329.2128231684377</v>
+      </c>
+      <c r="E54">
+        <v>410.732</v>
+      </c>
+      <c r="F54">
+        <v>463.632</v>
+      </c>
+      <c r="G54">
+        <v>36</v>
+      </c>
+      <c r="H54">
+        <v>838.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>45.7</v>
+      </c>
+      <c r="K54">
+        <v>11.3</v>
+      </c>
+      <c r="L54">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M54">
+        <v>110.7153216</v>
+      </c>
+      <c r="N54">
+        <v>-76.3153216</v>
+      </c>
+      <c r="O54">
+        <v>-26.71036256</v>
+      </c>
+      <c r="P54">
+        <v>-49.60495904</v>
+      </c>
+      <c r="Q54">
+        <v>-38.30495904</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1501164306813877</v>
+      </c>
+      <c r="T54">
+        <v>1.509412347376785</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.1087473696142883</v>
+      </c>
+      <c r="W54">
+        <v>0.212831128136108</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3107067703265382</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1847280733578422</v>
+      </c>
+      <c r="C55">
+        <v>-111.847164355185</v>
+      </c>
+      <c r="D55">
+        <v>324.700835644815</v>
+      </c>
+      <c r="E55">
+        <v>419.6480000000001</v>
+      </c>
+      <c r="F55">
+        <v>472.5480000000001</v>
+      </c>
+      <c r="G55">
+        <v>36</v>
+      </c>
+      <c r="H55">
+        <v>838.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>45.7</v>
+      </c>
+      <c r="K55">
+        <v>11.3</v>
+      </c>
+      <c r="L55">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M55">
+        <v>112.8444624</v>
+      </c>
+      <c r="N55">
+        <v>-78.44446240000002</v>
+      </c>
+      <c r="O55">
+        <v>-27.45556184</v>
+      </c>
+      <c r="P55">
+        <v>-50.98890056000002</v>
+      </c>
+      <c r="Q55">
+        <v>-39.68890056000002</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1524848653767364</v>
+      </c>
+      <c r="T55">
+        <v>1.541527503703951</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.1066955324517546</v>
+      </c>
+      <c r="W55">
+        <v>0.213321106850521</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3048443784335845</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1867280733578423</v>
+      </c>
+      <c r="C56">
+        <v>-125.153146976798</v>
+      </c>
+      <c r="D56">
+        <v>320.310853023202</v>
+      </c>
+      <c r="E56">
+        <v>428.5640000000001</v>
+      </c>
+      <c r="F56">
+        <v>481.4640000000001</v>
+      </c>
+      <c r="G56">
+        <v>36</v>
+      </c>
+      <c r="H56">
+        <v>838.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>45.7</v>
+      </c>
+      <c r="K56">
+        <v>11.3</v>
+      </c>
+      <c r="L56">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M56">
+        <v>114.9736032</v>
+      </c>
+      <c r="N56">
+        <v>-80.57360320000001</v>
+      </c>
+      <c r="O56">
+        <v>-28.20076112</v>
+      </c>
+      <c r="P56">
+        <v>-52.37284208000001</v>
+      </c>
+      <c r="Q56">
+        <v>-41.07284208000002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.154956275493622</v>
+      </c>
+      <c r="T56">
+        <v>1.575038971175776</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.1047196892582036</v>
+      </c>
+      <c r="W56">
+        <v>0.213792938205141</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2991991121662959</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1887280733578423</v>
+      </c>
+      <c r="C57">
+        <v>-138.342007233712</v>
+      </c>
+      <c r="D57">
+        <v>316.037992766288</v>
+      </c>
+      <c r="E57">
+        <v>437.4800000000001</v>
+      </c>
+      <c r="F57">
+        <v>490.3800000000001</v>
+      </c>
+      <c r="G57">
+        <v>36</v>
+      </c>
+      <c r="H57">
+        <v>838.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>45.7</v>
+      </c>
+      <c r="K57">
+        <v>11.3</v>
+      </c>
+      <c r="L57">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M57">
+        <v>117.102744</v>
+      </c>
+      <c r="N57">
+        <v>-82.70274400000001</v>
+      </c>
+      <c r="O57">
+        <v>-28.9459604</v>
+      </c>
+      <c r="P57">
+        <v>-53.75678360000001</v>
+      </c>
+      <c r="Q57">
+        <v>-42.45678360000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1575375260601469</v>
+      </c>
+      <c r="T57">
+        <v>1.610039837201904</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.1028156949080544</v>
+      </c>
+      <c r="W57">
+        <v>0.2142476120559566</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.293759128308727</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1907280733578423</v>
+      </c>
+      <c r="C58">
+        <v>-151.4183705659306</v>
+      </c>
+      <c r="D58">
+        <v>311.8776294340695</v>
+      </c>
+      <c r="E58">
+        <v>446.3960000000001</v>
+      </c>
+      <c r="F58">
+        <v>499.296</v>
+      </c>
+      <c r="G58">
+        <v>36</v>
+      </c>
+      <c r="H58">
+        <v>838.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>45.7</v>
+      </c>
+      <c r="K58">
+        <v>11.3</v>
+      </c>
+      <c r="L58">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M58">
+        <v>119.2318848</v>
+      </c>
+      <c r="N58">
+        <v>-84.83188480000001</v>
+      </c>
+      <c r="O58">
+        <v>-29.69115968</v>
+      </c>
+      <c r="P58">
+        <v>-55.14072512000001</v>
+      </c>
+      <c r="Q58">
+        <v>-43.84072512000002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1602361061978775</v>
+      </c>
+      <c r="T58">
+        <v>1.646631651683766</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.1009797003561249</v>
+      </c>
+      <c r="W58">
+        <v>0.2146860475549574</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2885134295889282</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1927280733578423</v>
+      </c>
+      <c r="C59">
+        <v>-164.3866220185819</v>
+      </c>
+      <c r="D59">
+        <v>307.8253779814182</v>
+      </c>
+      <c r="E59">
+        <v>455.3120000000001</v>
+      </c>
+      <c r="F59">
+        <v>508.212</v>
+      </c>
+      <c r="G59">
+        <v>36</v>
+      </c>
+      <c r="H59">
+        <v>838.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>45.7</v>
+      </c>
+      <c r="K59">
+        <v>11.3</v>
+      </c>
+      <c r="L59">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M59">
+        <v>121.3610256</v>
+      </c>
+      <c r="N59">
+        <v>-86.96102560000001</v>
+      </c>
+      <c r="O59">
+        <v>-30.43635896</v>
+      </c>
+      <c r="P59">
+        <v>-56.52466664000001</v>
+      </c>
+      <c r="Q59">
+        <v>-45.22466664000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1630602016908514</v>
+      </c>
+      <c r="T59">
+        <v>1.684925411025249</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.09920812666566653</v>
+      </c>
+      <c r="W59">
+        <v>0.2151090993522388</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.283451790473333</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1947280733578423</v>
+      </c>
+      <c r="C60">
+        <v>-177.2509216589549</v>
+      </c>
+      <c r="D60">
+        <v>303.877078341045</v>
+      </c>
+      <c r="E60">
+        <v>464.228</v>
+      </c>
+      <c r="F60">
+        <v>517.1279999999999</v>
+      </c>
+      <c r="G60">
+        <v>36</v>
+      </c>
+      <c r="H60">
+        <v>838.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>45.7</v>
+      </c>
+      <c r="K60">
+        <v>11.3</v>
+      </c>
+      <c r="L60">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M60">
+        <v>123.4901664</v>
+      </c>
+      <c r="N60">
+        <v>-89.09016639999999</v>
+      </c>
+      <c r="O60">
+        <v>-31.18155823999999</v>
+      </c>
+      <c r="P60">
+        <v>-57.90860815999999</v>
+      </c>
+      <c r="Q60">
+        <v>-46.60860815999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.166018777921586</v>
+      </c>
+      <c r="T60">
+        <v>1.725042682716326</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.09749764172315507</v>
+      </c>
+      <c r="W60">
+        <v>0.2155175631565106</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2785646906375859</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1967280733578423</v>
+      </c>
+      <c r="C61">
+        <v>-190.0152188220882</v>
+      </c>
+      <c r="D61">
+        <v>300.0287811779118</v>
+      </c>
+      <c r="E61">
+        <v>473.144</v>
+      </c>
+      <c r="F61">
+        <v>526.044</v>
+      </c>
+      <c r="G61">
+        <v>36</v>
+      </c>
+      <c r="H61">
+        <v>838.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>45.7</v>
+      </c>
+      <c r="K61">
+        <v>11.3</v>
+      </c>
+      <c r="L61">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M61">
+        <v>125.6193072</v>
+      </c>
+      <c r="N61">
+        <v>-91.2193072</v>
+      </c>
+      <c r="O61">
+        <v>-31.92675752</v>
+      </c>
+      <c r="P61">
+        <v>-59.29254968000001</v>
+      </c>
+      <c r="Q61">
+        <v>-47.99254968000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1691216749440637</v>
+      </c>
+      <c r="T61">
+        <v>1.767116894489895</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.09584513932106768</v>
+      </c>
+      <c r="W61">
+        <v>0.215912180730129</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2738432552030505</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1987280733578423</v>
+      </c>
+      <c r="C62">
+        <v>-202.6832652874589</v>
+      </c>
+      <c r="D62">
+        <v>296.2767347125411</v>
+      </c>
+      <c r="E62">
+        <v>482.0600000000001</v>
+      </c>
+      <c r="F62">
+        <v>534.96</v>
+      </c>
+      <c r="G62">
+        <v>36</v>
+      </c>
+      <c r="H62">
+        <v>838.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>45.7</v>
+      </c>
+      <c r="K62">
+        <v>11.3</v>
+      </c>
+      <c r="L62">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M62">
+        <v>127.748448</v>
+      </c>
+      <c r="N62">
+        <v>-93.348448</v>
+      </c>
+      <c r="O62">
+        <v>-32.6719568</v>
+      </c>
+      <c r="P62">
+        <v>-60.67649120000001</v>
+      </c>
+      <c r="Q62">
+        <v>-49.3764912</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1723797168176653</v>
+      </c>
+      <c r="T62">
+        <v>1.811294816852142</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.09424772033238321</v>
+      </c>
+      <c r="W62">
+        <v>0.2162936443846269</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2692792009496664</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2007280733578423</v>
+      </c>
+      <c r="C63">
+        <v>-215.2586274791871</v>
+      </c>
+      <c r="D63">
+        <v>292.6173725208129</v>
+      </c>
+      <c r="E63">
+        <v>490.976</v>
+      </c>
+      <c r="F63">
+        <v>543.876</v>
+      </c>
+      <c r="G63">
+        <v>36</v>
+      </c>
+      <c r="H63">
+        <v>838.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>45.7</v>
+      </c>
+      <c r="K63">
+        <v>11.3</v>
+      </c>
+      <c r="L63">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M63">
+        <v>129.8775888</v>
+      </c>
+      <c r="N63">
+        <v>-95.47758880000001</v>
+      </c>
+      <c r="O63">
+        <v>-33.41715608</v>
+      </c>
+      <c r="P63">
+        <v>-62.06043272000001</v>
+      </c>
+      <c r="Q63">
+        <v>-50.76043272000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.175804837761708</v>
+      </c>
+      <c r="T63">
+        <v>1.857738273694505</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.09270267573677038</v>
+      </c>
+      <c r="W63">
+        <v>0.2166626010340592</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.264864787819344</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2027280733578423</v>
+      </c>
+      <c r="C64">
+        <v>-227.7446977731514</v>
+      </c>
+      <c r="D64">
+        <v>289.0473022268487</v>
+      </c>
+      <c r="E64">
+        <v>499.8920000000001</v>
+      </c>
+      <c r="F64">
+        <v>552.792</v>
+      </c>
+      <c r="G64">
+        <v>36</v>
+      </c>
+      <c r="H64">
+        <v>838.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>45.7</v>
+      </c>
+      <c r="K64">
+        <v>11.3</v>
+      </c>
+      <c r="L64">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M64">
+        <v>132.0067296</v>
+      </c>
+      <c r="N64">
+        <v>-97.60672959999999</v>
+      </c>
+      <c r="O64">
+        <v>-34.16235535999999</v>
+      </c>
+      <c r="P64">
+        <v>-63.44437424</v>
+      </c>
+      <c r="Q64">
+        <v>-52.14437424</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1794102282291213</v>
+      </c>
+      <c r="T64">
+        <v>1.906626123002255</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.09120747128940312</v>
+      </c>
+      <c r="W64">
+        <v>0.2170196558560906</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2605927751125804</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2047280733578423</v>
+      </c>
+      <c r="C65">
+        <v>-240.144704986367</v>
+      </c>
+      <c r="D65">
+        <v>285.563295013633</v>
+      </c>
+      <c r="E65">
+        <v>508.808</v>
+      </c>
+      <c r="F65">
+        <v>561.708</v>
+      </c>
+      <c r="G65">
+        <v>36</v>
+      </c>
+      <c r="H65">
+        <v>838.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>45.7</v>
+      </c>
+      <c r="K65">
+        <v>11.3</v>
+      </c>
+      <c r="L65">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M65">
+        <v>134.1358704</v>
+      </c>
+      <c r="N65">
+        <v>-99.73587039999998</v>
+      </c>
+      <c r="O65">
+        <v>-34.90755463999999</v>
+      </c>
+      <c r="P65">
+        <v>-64.82831575999998</v>
+      </c>
+      <c r="Q65">
+        <v>-53.52831575999998</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1832105046677462</v>
+      </c>
+      <c r="T65">
+        <v>1.958156558759073</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.08975973364988879</v>
+      </c>
+      <c r="W65">
+        <v>0.2173653756044066</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2564563818568252</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2067280733578423</v>
+      </c>
+      <c r="C66">
+        <v>-252.4617241168029</v>
+      </c>
+      <c r="D66">
+        <v>282.1622758831971</v>
+      </c>
+      <c r="E66">
+        <v>517.724</v>
+      </c>
+      <c r="F66">
+        <v>570.624</v>
+      </c>
+      <c r="G66">
+        <v>36</v>
+      </c>
+      <c r="H66">
+        <v>838.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>45.7</v>
+      </c>
+      <c r="K66">
+        <v>11.3</v>
+      </c>
+      <c r="L66">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M66">
+        <v>136.2650112</v>
+      </c>
+      <c r="N66">
+        <v>-101.8650112</v>
+      </c>
+      <c r="O66">
+        <v>-35.65275391999999</v>
+      </c>
+      <c r="P66">
+        <v>-66.21225728</v>
+      </c>
+      <c r="Q66">
+        <v>-54.91225728000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1872219075751836</v>
+      </c>
+      <c r="T66">
+        <v>2.01254979650238</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.08835723781160927</v>
+      </c>
+      <c r="W66">
+        <v>0.2177002916105877</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2524492508903122</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2087280733578423</v>
+      </c>
+      <c r="C67">
+        <v>-264.6986853953906</v>
+      </c>
+      <c r="D67">
+        <v>278.8413146046095</v>
+      </c>
+      <c r="E67">
+        <v>526.6400000000001</v>
+      </c>
+      <c r="F67">
+        <v>579.5400000000001</v>
+      </c>
+      <c r="G67">
+        <v>36</v>
+      </c>
+      <c r="H67">
+        <v>838.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>45.7</v>
+      </c>
+      <c r="K67">
+        <v>11.3</v>
+      </c>
+      <c r="L67">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M67">
+        <v>138.394152</v>
+      </c>
+      <c r="N67">
+        <v>-103.994152</v>
+      </c>
+      <c r="O67">
+        <v>-36.3979532</v>
+      </c>
+      <c r="P67">
+        <v>-67.59619880000001</v>
+      </c>
+      <c r="Q67">
+        <v>-56.29619880000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1914625335059032</v>
+      </c>
+      <c r="T67">
+        <v>2.070051219259591</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.08699789569143065</v>
+      </c>
+      <c r="W67">
+        <v>0.2180249025088864</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2485654162612305</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2107280733578423</v>
+      </c>
+      <c r="C68">
+        <v>-276.8583827062334</v>
+      </c>
+      <c r="D68">
+        <v>275.5976172937666</v>
+      </c>
+      <c r="E68">
+        <v>535.556</v>
+      </c>
+      <c r="F68">
+        <v>588.456</v>
+      </c>
+      <c r="G68">
+        <v>36</v>
+      </c>
+      <c r="H68">
+        <v>838.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>45.7</v>
+      </c>
+      <c r="K68">
+        <v>11.3</v>
+      </c>
+      <c r="L68">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M68">
+        <v>140.5232928</v>
+      </c>
+      <c r="N68">
+        <v>-106.1232928</v>
+      </c>
+      <c r="O68">
+        <v>-37.14315248</v>
+      </c>
+      <c r="P68">
+        <v>-68.98014032</v>
+      </c>
+      <c r="Q68">
+        <v>-57.68014032000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1959526080207827</v>
+      </c>
+      <c r="T68">
+        <v>2.130935078649579</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.08567974575671201</v>
+      </c>
+      <c r="W68">
+        <v>0.2183396767132972</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2447992735906058</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2127280733578423</v>
+      </c>
+      <c r="C69">
+        <v>-288.943481425872</v>
+      </c>
+      <c r="D69">
+        <v>272.4285185741281</v>
+      </c>
+      <c r="E69">
+        <v>544.4720000000001</v>
+      </c>
+      <c r="F69">
+        <v>597.3720000000001</v>
+      </c>
+      <c r="G69">
+        <v>36</v>
+      </c>
+      <c r="H69">
+        <v>838.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>45.7</v>
+      </c>
+      <c r="K69">
+        <v>11.3</v>
+      </c>
+      <c r="L69">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M69">
+        <v>142.6524336</v>
+      </c>
+      <c r="N69">
+        <v>-108.2524336</v>
+      </c>
+      <c r="O69">
+        <v>-37.88835176000001</v>
+      </c>
+      <c r="P69">
+        <v>-70.36408184000001</v>
+      </c>
+      <c r="Q69">
+        <v>-59.06408184000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2007148082638367</v>
+      </c>
+      <c r="T69">
+        <v>2.195508868911688</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.08440094358123869</v>
+      </c>
+      <c r="W69">
+        <v>0.2186450546728002</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2411455530892535</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2147280733578422</v>
+      </c>
+      <c r="C70">
+        <v>-300.956525727835</v>
+      </c>
+      <c r="D70">
+        <v>269.3314742721651</v>
+      </c>
+      <c r="E70">
+        <v>553.388</v>
+      </c>
+      <c r="F70">
+        <v>606.288</v>
+      </c>
+      <c r="G70">
+        <v>36</v>
+      </c>
+      <c r="H70">
+        <v>838.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>45.7</v>
+      </c>
+      <c r="K70">
+        <v>11.3</v>
+      </c>
+      <c r="L70">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M70">
+        <v>144.7815744</v>
+      </c>
+      <c r="N70">
+        <v>-110.3815744</v>
+      </c>
+      <c r="O70">
+        <v>-38.63355104</v>
+      </c>
+      <c r="P70">
+        <v>-71.74802336</v>
+      </c>
+      <c r="Q70">
+        <v>-60.44802336000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2057746460220816</v>
+      </c>
+      <c r="T70">
+        <v>2.264118521065178</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.08315975323445578</v>
+      </c>
+      <c r="W70">
+        <v>0.218941450927612</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.237599294955588</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2167280733578423</v>
+      </c>
+      <c r="C71">
+        <v>-312.8999453945506</v>
+      </c>
+      <c r="D71">
+        <v>266.3040546054494</v>
+      </c>
+      <c r="E71">
+        <v>562.3040000000001</v>
+      </c>
+      <c r="F71">
+        <v>615.2040000000001</v>
+      </c>
+      <c r="G71">
+        <v>36</v>
+      </c>
+      <c r="H71">
+        <v>838.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>45.7</v>
+      </c>
+      <c r="K71">
+        <v>11.3</v>
+      </c>
+      <c r="L71">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M71">
+        <v>146.9107152</v>
+      </c>
+      <c r="N71">
+        <v>-112.5107152</v>
+      </c>
+      <c r="O71">
+        <v>-39.37875032</v>
+      </c>
+      <c r="P71">
+        <v>-73.13196488000003</v>
+      </c>
+      <c r="Q71">
+        <v>-61.83196488000003</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2111609249260197</v>
+      </c>
+      <c r="T71">
+        <v>2.337154602389862</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.08195453941946367</v>
+      </c>
+      <c r="W71">
+        <v>0.2192292559866321</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2341558269127533</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2187280733578423</v>
+      </c>
+      <c r="C72">
+        <v>-324.7760621749468</v>
+      </c>
+      <c r="D72">
+        <v>263.3439378250533</v>
+      </c>
+      <c r="E72">
+        <v>571.2200000000001</v>
+      </c>
+      <c r="F72">
+        <v>624.1200000000001</v>
+      </c>
+      <c r="G72">
+        <v>36</v>
+      </c>
+      <c r="H72">
+        <v>838.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>45.7</v>
+      </c>
+      <c r="K72">
+        <v>11.3</v>
+      </c>
+      <c r="L72">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M72">
+        <v>149.039856</v>
+      </c>
+      <c r="N72">
+        <v>-114.639856</v>
+      </c>
+      <c r="O72">
+        <v>-40.12394960000001</v>
+      </c>
+      <c r="P72">
+        <v>-74.51590640000003</v>
+      </c>
+      <c r="Q72">
+        <v>-63.21590640000004</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2169062890902204</v>
+      </c>
+      <c r="T72">
+        <v>2.415059755802857</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.08078376028489989</v>
+      </c>
+      <c r="W72">
+        <v>0.2195088380439659</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2308107436711425</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2207280733578422</v>
+      </c>
+      <c r="C73">
+        <v>-336.5870957227056</v>
+      </c>
+      <c r="D73">
+        <v>260.4489042772944</v>
+      </c>
+      <c r="E73">
+        <v>580.136</v>
+      </c>
+      <c r="F73">
+        <v>633.0359999999999</v>
+      </c>
+      <c r="G73">
+        <v>36</v>
+      </c>
+      <c r="H73">
+        <v>838.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>45.7</v>
+      </c>
+      <c r="K73">
+        <v>11.3</v>
+      </c>
+      <c r="L73">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M73">
+        <v>151.1689968</v>
+      </c>
+      <c r="N73">
+        <v>-116.7689968</v>
+      </c>
+      <c r="O73">
+        <v>-40.86914888</v>
+      </c>
+      <c r="P73">
+        <v>-75.89984792</v>
+      </c>
+      <c r="Q73">
+        <v>-64.59984792</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2230478852657452</v>
+      </c>
+      <c r="T73">
+        <v>2.498337678416748</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.07964596084426752</v>
+      </c>
+      <c r="W73">
+        <v>0.2197805445503889</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2275598881264786</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2227280733578422</v>
+      </c>
+      <c r="C74">
+        <v>-348.335169147088</v>
+      </c>
+      <c r="D74">
+        <v>257.616830852912</v>
+      </c>
+      <c r="E74">
+        <v>589.052</v>
+      </c>
+      <c r="F74">
+        <v>641.952</v>
+      </c>
+      <c r="G74">
+        <v>36</v>
+      </c>
+      <c r="H74">
+        <v>838.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>45.7</v>
+      </c>
+      <c r="K74">
+        <v>11.3</v>
+      </c>
+      <c r="L74">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M74">
+        <v>153.2981376</v>
+      </c>
+      <c r="N74">
+        <v>-118.8981376</v>
+      </c>
+      <c r="O74">
+        <v>-41.61434816</v>
+      </c>
+      <c r="P74">
+        <v>-77.28378944000002</v>
+      </c>
+      <c r="Q74">
+        <v>-65.98378944000002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2296281668823789</v>
+      </c>
+      <c r="T74">
+        <v>2.587564024074489</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.07853976694365268</v>
+      </c>
+      <c r="W74">
+        <v>0.2200447036538557</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2243993341247219</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2247280733578422</v>
+      </c>
+      <c r="C75">
+        <v>-360.022314205501</v>
+      </c>
+      <c r="D75">
+        <v>254.845685794499</v>
+      </c>
+      <c r="E75">
+        <v>597.9680000000001</v>
+      </c>
+      <c r="F75">
+        <v>650.8680000000001</v>
+      </c>
+      <c r="G75">
+        <v>36</v>
+      </c>
+      <c r="H75">
+        <v>838.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>45.7</v>
+      </c>
+      <c r="K75">
+        <v>11.3</v>
+      </c>
+      <c r="L75">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M75">
+        <v>155.4272784</v>
+      </c>
+      <c r="N75">
+        <v>-121.0272784</v>
+      </c>
+      <c r="O75">
+        <v>-42.35954744000001</v>
+      </c>
+      <c r="P75">
+        <v>-78.66773096000003</v>
+      </c>
+      <c r="Q75">
+        <v>-67.36773096000003</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2366958767669115</v>
+      </c>
+      <c r="T75">
+        <v>2.68339972866984</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.07746387972524647</v>
+      </c>
+      <c r="W75">
+        <v>0.2203016255216111</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2213253706435614</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2267280733578422</v>
+      </c>
+      <c r="C76">
+        <v>-371.6504761644993</v>
+      </c>
+      <c r="D76">
+        <v>252.1335238355007</v>
+      </c>
+      <c r="E76">
+        <v>606.884</v>
+      </c>
+      <c r="F76">
+        <v>659.784</v>
+      </c>
+      <c r="G76">
+        <v>36</v>
+      </c>
+      <c r="H76">
+        <v>838.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>45.7</v>
+      </c>
+      <c r="K76">
+        <v>11.3</v>
+      </c>
+      <c r="L76">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M76">
+        <v>157.5564192</v>
+      </c>
+      <c r="N76">
+        <v>-123.1564192</v>
+      </c>
+      <c r="O76">
+        <v>-43.10474671999999</v>
+      </c>
+      <c r="P76">
+        <v>-80.05167247999999</v>
+      </c>
+      <c r="Q76">
+        <v>-68.75167248</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2443072566425619</v>
+      </c>
+      <c r="T76">
+        <v>2.786607410541757</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.07641707053977019</v>
+      </c>
+      <c r="W76">
+        <v>0.2205516035551029</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2183344872564863</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2287280733578422</v>
+      </c>
+      <c r="C77">
+        <v>-383.2215183536597</v>
+      </c>
+      <c r="D77">
+        <v>249.4784816463404</v>
+      </c>
+      <c r="E77">
+        <v>615.8000000000001</v>
+      </c>
+      <c r="F77">
+        <v>668.7</v>
+      </c>
+      <c r="G77">
+        <v>36</v>
+      </c>
+      <c r="H77">
+        <v>838.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>45.7</v>
+      </c>
+      <c r="K77">
+        <v>11.3</v>
+      </c>
+      <c r="L77">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M77">
+        <v>159.68556</v>
+      </c>
+      <c r="N77">
+        <v>-125.28556</v>
+      </c>
+      <c r="O77">
+        <v>-43.849946</v>
+      </c>
+      <c r="P77">
+        <v>-81.43561400000002</v>
+      </c>
+      <c r="Q77">
+        <v>-70.13561400000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2525275469082644</v>
+      </c>
+      <c r="T77">
+        <v>2.898071706963428</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.07539817626590657</v>
+      </c>
+      <c r="W77">
+        <v>0.2207949155077015</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2154233607597331</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2307280733578422</v>
+      </c>
+      <c r="C78">
+        <v>-394.7372264347301</v>
+      </c>
+      <c r="D78">
+        <v>246.8787735652699</v>
+      </c>
+      <c r="E78">
+        <v>624.716</v>
+      </c>
+      <c r="F78">
+        <v>677.616</v>
+      </c>
+      <c r="G78">
+        <v>36</v>
+      </c>
+      <c r="H78">
+        <v>838.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>45.7</v>
+      </c>
+      <c r="K78">
+        <v>11.3</v>
+      </c>
+      <c r="L78">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M78">
+        <v>161.8147008</v>
+      </c>
+      <c r="N78">
+        <v>-127.4147008</v>
+      </c>
+      <c r="O78">
+        <v>-44.59514528</v>
+      </c>
+      <c r="P78">
+        <v>-82.81955551999999</v>
+      </c>
+      <c r="Q78">
+        <v>-71.51955552</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2614328613627754</v>
+      </c>
+      <c r="T78">
+        <v>3.018824694753571</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.07440609499924991</v>
+      </c>
+      <c r="W78">
+        <v>0.2210318245141791</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2125888428549998</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2327280733578422</v>
+      </c>
+      <c r="C79">
+        <v>-406.1993124066123</v>
+      </c>
+      <c r="D79">
+        <v>244.3326875933877</v>
+      </c>
+      <c r="E79">
+        <v>633.6320000000001</v>
+      </c>
+      <c r="F79">
+        <v>686.532</v>
+      </c>
+      <c r="G79">
+        <v>36</v>
+      </c>
+      <c r="H79">
+        <v>838.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>45.7</v>
+      </c>
+      <c r="K79">
+        <v>11.3</v>
+      </c>
+      <c r="L79">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M79">
+        <v>163.9438416</v>
+      </c>
+      <c r="N79">
+        <v>-129.5438416</v>
+      </c>
+      <c r="O79">
+        <v>-45.34034456</v>
+      </c>
+      <c r="P79">
+        <v>-84.20349704</v>
+      </c>
+      <c r="Q79">
+        <v>-72.90349704</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.271112550987244</v>
+      </c>
+      <c r="T79">
+        <v>3.150077942351552</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.07343978207718173</v>
+      </c>
+      <c r="W79">
+        <v>0.221262580039969</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2098279487919478</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2347280733578423</v>
+      </c>
+      <c r="C80">
+        <v>-417.6094183650488</v>
+      </c>
+      <c r="D80">
+        <v>241.8385816349513</v>
+      </c>
+      <c r="E80">
+        <v>642.5480000000001</v>
+      </c>
+      <c r="F80">
+        <v>695.4480000000001</v>
+      </c>
+      <c r="G80">
+        <v>36</v>
+      </c>
+      <c r="H80">
+        <v>838.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>45.7</v>
+      </c>
+      <c r="K80">
+        <v>11.3</v>
+      </c>
+      <c r="L80">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M80">
+        <v>166.0729824</v>
+      </c>
+      <c r="N80">
+        <v>-131.6729824</v>
+      </c>
+      <c r="O80">
+        <v>-46.08554384000001</v>
+      </c>
+      <c r="P80">
+        <v>-85.58743856000001</v>
+      </c>
+      <c r="Q80">
+        <v>-74.28743856000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2816722123957551</v>
+      </c>
+      <c r="T80">
+        <v>3.293263303367532</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.07249824640952554</v>
+      </c>
+      <c r="W80">
+        <v>0.2214874187574053</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2071378468843588</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2367280733578422</v>
+      </c>
+      <c r="C81">
+        <v>-428.9691200343691</v>
+      </c>
+      <c r="D81">
+        <v>239.3948799656309</v>
+      </c>
+      <c r="E81">
+        <v>651.4640000000001</v>
+      </c>
+      <c r="F81">
+        <v>704.364</v>
+      </c>
+      <c r="G81">
+        <v>36</v>
+      </c>
+      <c r="H81">
+        <v>838.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>45.7</v>
+      </c>
+      <c r="K81">
+        <v>11.3</v>
+      </c>
+      <c r="L81">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M81">
+        <v>168.2021232</v>
+      </c>
+      <c r="N81">
+        <v>-133.8021232</v>
+      </c>
+      <c r="O81">
+        <v>-46.83074312</v>
+      </c>
+      <c r="P81">
+        <v>-86.97138008000002</v>
+      </c>
+      <c r="Q81">
+        <v>-75.67138008000002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.293237555843172</v>
+      </c>
+      <c r="T81">
+        <v>3.450085365432652</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.07158054708788598</v>
+      </c>
+      <c r="W81">
+        <v>0.2217065653554128</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2045158488225314</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2387280733578422</v>
+      </c>
+      <c r="C82">
+        <v>-440.279930087254</v>
+      </c>
+      <c r="D82">
+        <v>237.0000699127461</v>
+      </c>
+      <c r="E82">
+        <v>660.3800000000001</v>
+      </c>
+      <c r="F82">
+        <v>713.2800000000001</v>
+      </c>
+      <c r="G82">
+        <v>36</v>
+      </c>
+      <c r="H82">
+        <v>838.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>45.7</v>
+      </c>
+      <c r="K82">
+        <v>11.3</v>
+      </c>
+      <c r="L82">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M82">
+        <v>170.331264</v>
+      </c>
+      <c r="N82">
+        <v>-135.931264</v>
+      </c>
+      <c r="O82">
+        <v>-47.57594240000001</v>
+      </c>
+      <c r="P82">
+        <v>-88.35532160000002</v>
+      </c>
+      <c r="Q82">
+        <v>-77.05532160000003</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3059594336353306</v>
+      </c>
+      <c r="T82">
+        <v>3.622589633704285</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.07068579024928741</v>
+      </c>
+      <c r="W82">
+        <v>0.2219202332884702</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2019594007122497</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2407280733578422</v>
+      </c>
+      <c r="C83">
+        <v>-451.5433012672161</v>
+      </c>
+      <c r="D83">
+        <v>234.6526987327839</v>
+      </c>
+      <c r="E83">
+        <v>669.296</v>
+      </c>
+      <c r="F83">
+        <v>722.196</v>
+      </c>
+      <c r="G83">
+        <v>36</v>
+      </c>
+      <c r="H83">
+        <v>838.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>45.7</v>
+      </c>
+      <c r="K83">
+        <v>11.3</v>
+      </c>
+      <c r="L83">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M83">
+        <v>172.4604048</v>
+      </c>
+      <c r="N83">
+        <v>-138.0604048</v>
+      </c>
+      <c r="O83">
+        <v>-48.32114168</v>
+      </c>
+      <c r="P83">
+        <v>-89.73926312</v>
+      </c>
+      <c r="Q83">
+        <v>-78.43926312000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3200204564582427</v>
+      </c>
+      <c r="T83">
+        <v>3.813252246004511</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.06981312617213571</v>
+      </c>
+      <c r="W83">
+        <v>0.222128625470094</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1994660747775306</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2427280733578423</v>
+      </c>
+      <c r="C84">
+        <v>-462.7606293273408</v>
+      </c>
+      <c r="D84">
+        <v>232.3513706726592</v>
+      </c>
+      <c r="E84">
+        <v>678.2120000000001</v>
+      </c>
+      <c r="F84">
+        <v>731.1120000000001</v>
+      </c>
+      <c r="G84">
+        <v>36</v>
+      </c>
+      <c r="H84">
+        <v>838.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>45.7</v>
+      </c>
+      <c r="K84">
+        <v>11.3</v>
+      </c>
+      <c r="L84">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M84">
+        <v>174.5895456</v>
+      </c>
+      <c r="N84">
+        <v>-140.1895456</v>
+      </c>
+      <c r="O84">
+        <v>-49.06634096000001</v>
+      </c>
+      <c r="P84">
+        <v>-91.12320464000003</v>
+      </c>
+      <c r="Q84">
+        <v>-79.82320464000003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3356438151503673</v>
+      </c>
+      <c r="T84">
+        <v>4.025099593004762</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06896174658467064</v>
+      </c>
+      <c r="W84">
+        <v>0.2223319349155807</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1970335616704876</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2447280733578423</v>
+      </c>
+      <c r="C85">
+        <v>-473.9332557977774</v>
+      </c>
+      <c r="D85">
+        <v>230.0947442022227</v>
+      </c>
+      <c r="E85">
+        <v>687.1280000000002</v>
+      </c>
+      <c r="F85">
+        <v>740.0280000000001</v>
+      </c>
+      <c r="G85">
+        <v>36</v>
+      </c>
+      <c r="H85">
+        <v>838.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>45.7</v>
+      </c>
+      <c r="K85">
+        <v>11.3</v>
+      </c>
+      <c r="L85">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M85">
+        <v>176.7186864000001</v>
+      </c>
+      <c r="N85">
+        <v>-142.3186864</v>
+      </c>
+      <c r="O85">
+        <v>-49.81154024000001</v>
+      </c>
+      <c r="P85">
+        <v>-92.50714616000003</v>
+      </c>
+      <c r="Q85">
+        <v>-81.20714616000004</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3531052160415655</v>
+      </c>
+      <c r="T85">
+        <v>4.26187015729916</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06813088216798785</v>
+      </c>
+      <c r="W85">
+        <v>0.2225303453382845</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1946596633371082</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2467280733578422</v>
+      </c>
+      <c r="C86">
+        <v>-485.0624705935133</v>
+      </c>
+      <c r="D86">
+        <v>227.8815294064867</v>
+      </c>
+      <c r="E86">
+        <v>696.044</v>
+      </c>
+      <c r="F86">
+        <v>748.944</v>
+      </c>
+      <c r="G86">
+        <v>36</v>
+      </c>
+      <c r="H86">
+        <v>838.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>45.7</v>
+      </c>
+      <c r="K86">
+        <v>11.3</v>
+      </c>
+      <c r="L86">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M86">
+        <v>178.8478272</v>
+      </c>
+      <c r="N86">
+        <v>-144.4478272</v>
+      </c>
+      <c r="O86">
+        <v>-50.55673952</v>
+      </c>
+      <c r="P86">
+        <v>-93.89108768</v>
+      </c>
+      <c r="Q86">
+        <v>-82.59108768</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3727492920441631</v>
+      </c>
+      <c r="T86">
+        <v>4.528237042130355</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.06731980023741659</v>
+      </c>
+      <c r="W86">
+        <v>0.2227240317033049</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1923422863926189</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2487280733578422</v>
+      </c>
+      <c r="C87">
+        <v>-496.1495144730811</v>
+      </c>
+      <c r="D87">
+        <v>225.7104855269189</v>
+      </c>
+      <c r="E87">
+        <v>704.96</v>
+      </c>
+      <c r="F87">
+        <v>757.86</v>
+      </c>
+      <c r="G87">
+        <v>36</v>
+      </c>
+      <c r="H87">
+        <v>838.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>45.7</v>
+      </c>
+      <c r="K87">
+        <v>11.3</v>
+      </c>
+      <c r="L87">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M87">
+        <v>180.976968</v>
+      </c>
+      <c r="N87">
+        <v>-146.576968</v>
+      </c>
+      <c r="O87">
+        <v>-51.30193879999999</v>
+      </c>
+      <c r="P87">
+        <v>-95.27502920000001</v>
+      </c>
+      <c r="Q87">
+        <v>-83.97502920000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3950125781804407</v>
+      </c>
+      <c r="T87">
+        <v>4.830119511605712</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.06652780258756463</v>
+      </c>
+      <c r="W87">
+        <v>0.2229131607420896</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1900794359644704</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2507280733578423</v>
+      </c>
+      <c r="C88">
+        <v>-507.1955813580454</v>
+      </c>
+      <c r="D88">
+        <v>223.5804186419546</v>
+      </c>
+      <c r="E88">
+        <v>713.876</v>
+      </c>
+      <c r="F88">
+        <v>766.776</v>
+      </c>
+      <c r="G88">
+        <v>36</v>
+      </c>
+      <c r="H88">
+        <v>838.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>45.7</v>
+      </c>
+      <c r="K88">
+        <v>11.3</v>
+      </c>
+      <c r="L88">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M88">
+        <v>183.1061088</v>
+      </c>
+      <c r="N88">
+        <v>-148.7061088</v>
+      </c>
+      <c r="O88">
+        <v>-52.04713807999999</v>
+      </c>
+      <c r="P88">
+        <v>-96.65897071999999</v>
+      </c>
+      <c r="Q88">
+        <v>-85.35897071999999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4204563337647579</v>
+      </c>
+      <c r="T88">
+        <v>5.175128048148978</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.06575422348770923</v>
+      </c>
+      <c r="W88">
+        <v>0.2230978914311351</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1878692099648835</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2527280733578422</v>
+      </c>
+      <c r="C89">
+        <v>-518.2018205223832</v>
+      </c>
+      <c r="D89">
+        <v>221.4901794776168</v>
+      </c>
+      <c r="E89">
+        <v>722.792</v>
+      </c>
+      <c r="F89">
+        <v>775.692</v>
+      </c>
+      <c r="G89">
+        <v>36</v>
+      </c>
+      <c r="H89">
+        <v>838.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>45.7</v>
+      </c>
+      <c r="K89">
+        <v>11.3</v>
+      </c>
+      <c r="L89">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M89">
+        <v>185.2352496</v>
+      </c>
+      <c r="N89">
+        <v>-150.8352496</v>
+      </c>
+      <c r="O89">
+        <v>-52.79233736</v>
+      </c>
+      <c r="P89">
+        <v>-98.04291223999999</v>
+      </c>
+      <c r="Q89">
+        <v>-86.74291224</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4498145132851239</v>
+      </c>
+      <c r="T89">
+        <v>5.573214821083514</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06499842781543672</v>
+      </c>
+      <c r="W89">
+        <v>0.2232783754376737</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1857097937583906</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2547280733578422</v>
+      </c>
+      <c r="C90">
+        <v>-529.1693386601899</v>
+      </c>
+      <c r="D90">
+        <v>219.4386613398102</v>
+      </c>
+      <c r="E90">
+        <v>731.7080000000001</v>
+      </c>
+      <c r="F90">
+        <v>784.6080000000001</v>
+      </c>
+      <c r="G90">
+        <v>36</v>
+      </c>
+      <c r="H90">
+        <v>838.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>45.7</v>
+      </c>
+      <c r="K90">
+        <v>11.3</v>
+      </c>
+      <c r="L90">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M90">
+        <v>187.3643904</v>
+      </c>
+      <c r="N90">
+        <v>-152.9643904</v>
+      </c>
+      <c r="O90">
+        <v>-53.53753664</v>
+      </c>
+      <c r="P90">
+        <v>-99.42685376000001</v>
+      </c>
+      <c r="Q90">
+        <v>-88.12685376000002</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4840657227255509</v>
+      </c>
+      <c r="T90">
+        <v>6.037649389507141</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06425980931753401</v>
+      </c>
+      <c r="W90">
+        <v>0.2234547575349729</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1835994551929543</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2567280733578423</v>
+      </c>
+      <c r="C91">
+        <v>-540.0992018395287</v>
+      </c>
+      <c r="D91">
+        <v>217.4247981604713</v>
+      </c>
+      <c r="E91">
+        <v>740.624</v>
+      </c>
+      <c r="F91">
+        <v>793.524</v>
+      </c>
+      <c r="G91">
+        <v>36</v>
+      </c>
+      <c r="H91">
+        <v>838.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>45.7</v>
+      </c>
+      <c r="K91">
+        <v>11.3</v>
+      </c>
+      <c r="L91">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M91">
+        <v>189.4935312</v>
+      </c>
+      <c r="N91">
+        <v>-155.0935312</v>
+      </c>
+      <c r="O91">
+        <v>-54.28273592</v>
+      </c>
+      <c r="P91">
+        <v>-100.81079528</v>
+      </c>
+      <c r="Q91">
+        <v>-89.51079528000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5245444247915101</v>
+      </c>
+      <c r="T91">
+        <v>6.586526606735064</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06353778898812353</v>
+      </c>
+      <c r="W91">
+        <v>0.2236271759896361</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1815365399660672</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2587280733578422</v>
+      </c>
+      <c r="C92">
+        <v>-550.9924373496739</v>
+      </c>
+      <c r="D92">
+        <v>215.4475626503261</v>
+      </c>
+      <c r="E92">
+        <v>749.5400000000001</v>
+      </c>
+      <c r="F92">
+        <v>802.4400000000001</v>
+      </c>
+      <c r="G92">
+        <v>36</v>
+      </c>
+      <c r="H92">
+        <v>838.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>45.7</v>
+      </c>
+      <c r="K92">
+        <v>11.3</v>
+      </c>
+      <c r="L92">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M92">
+        <v>191.622672</v>
+      </c>
+      <c r="N92">
+        <v>-157.222672</v>
+      </c>
+      <c r="O92">
+        <v>-55.0279352</v>
+      </c>
+      <c r="P92">
+        <v>-102.1947368</v>
+      </c>
+      <c r="Q92">
+        <v>-90.89473680000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5731188672706611</v>
+      </c>
+      <c r="T92">
+        <v>7.24517926740857</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06283181355492214</v>
+      </c>
+      <c r="W92">
+        <v>0.2237957629230846</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1795194672997775</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2607280733578422</v>
+      </c>
+      <c r="C93">
+        <v>-561.8500354484681</v>
+      </c>
+      <c r="D93">
+        <v>213.5059645515319</v>
+      </c>
+      <c r="E93">
+        <v>758.456</v>
+      </c>
+      <c r="F93">
+        <v>811.356</v>
+      </c>
+      <c r="G93">
+        <v>36</v>
+      </c>
+      <c r="H93">
+        <v>838.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>45.7</v>
+      </c>
+      <c r="K93">
+        <v>11.3</v>
+      </c>
+      <c r="L93">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M93">
+        <v>193.7518128</v>
+      </c>
+      <c r="N93">
+        <v>-159.3518128</v>
+      </c>
+      <c r="O93">
+        <v>-55.77313448</v>
+      </c>
+      <c r="P93">
+        <v>-103.57867832</v>
+      </c>
+      <c r="Q93">
+        <v>-92.27867832000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6324876303007347</v>
+      </c>
+      <c r="T93">
+        <v>8.050199186009523</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06214135406530762</v>
+      </c>
+      <c r="W93">
+        <v>0.2239606446492045</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1775467259008789</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2627280733578423</v>
+      </c>
+      <c r="C94">
+        <v>-572.6729510160428</v>
+      </c>
+      <c r="D94">
+        <v>211.5990489839572</v>
+      </c>
+      <c r="E94">
+        <v>767.3720000000001</v>
+      </c>
+      <c r="F94">
+        <v>820.272</v>
+      </c>
+      <c r="G94">
+        <v>36</v>
+      </c>
+      <c r="H94">
+        <v>838.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>45.7</v>
+      </c>
+      <c r="K94">
+        <v>11.3</v>
+      </c>
+      <c r="L94">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M94">
+        <v>195.8809536</v>
+      </c>
+      <c r="N94">
+        <v>-161.4809536</v>
+      </c>
+      <c r="O94">
+        <v>-56.51833376</v>
+      </c>
+      <c r="P94">
+        <v>-104.96261984</v>
+      </c>
+      <c r="Q94">
+        <v>-93.66261984000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.7066985840883269</v>
+      </c>
+      <c r="T94">
+        <v>9.056474084260717</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.06146590456459775</v>
+      </c>
+      <c r="W94">
+        <v>0.2241219419899741</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.175616870184565</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2647280733578423</v>
+      </c>
+      <c r="C95">
+        <v>-583.4621051207017</v>
+      </c>
+      <c r="D95">
+        <v>209.7258948792984</v>
+      </c>
+      <c r="E95">
+        <v>776.2880000000001</v>
+      </c>
+      <c r="F95">
+        <v>829.1880000000001</v>
+      </c>
+      <c r="G95">
+        <v>36</v>
+      </c>
+      <c r="H95">
+        <v>838.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>45.7</v>
+      </c>
+      <c r="K95">
+        <v>11.3</v>
+      </c>
+      <c r="L95">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M95">
+        <v>198.0100944</v>
+      </c>
+      <c r="N95">
+        <v>-163.6100944</v>
+      </c>
+      <c r="O95">
+        <v>-57.26353304000001</v>
+      </c>
+      <c r="P95">
+        <v>-106.34656136</v>
+      </c>
+      <c r="Q95">
+        <v>-95.04656136000004</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8021126675295165</v>
+      </c>
+      <c r="T95">
+        <v>10.35025609629796</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.06080498085960207</v>
+      </c>
+      <c r="W95">
+        <v>0.224279770570727</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1737285167417202</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2667280733578423</v>
+      </c>
+      <c r="C96">
+        <v>-594.218386502364</v>
+      </c>
+      <c r="D96">
+        <v>207.8856134976361</v>
+      </c>
+      <c r="E96">
+        <v>785.2040000000001</v>
+      </c>
+      <c r="F96">
+        <v>838.104</v>
+      </c>
+      <c r="G96">
+        <v>36</v>
+      </c>
+      <c r="H96">
+        <v>838.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>45.7</v>
+      </c>
+      <c r="K96">
+        <v>11.3</v>
+      </c>
+      <c r="L96">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M96">
+        <v>200.1392352</v>
+      </c>
+      <c r="N96">
+        <v>-165.7392352</v>
+      </c>
+      <c r="O96">
+        <v>-58.00873232000001</v>
+      </c>
+      <c r="P96">
+        <v>-107.73050288</v>
+      </c>
+      <c r="Q96">
+        <v>-96.43050288000002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9293314454511026</v>
+      </c>
+      <c r="T96">
+        <v>12.07529877901429</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.06015811936109566</v>
+      </c>
+      <c r="W96">
+        <v>0.2244342410965704</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1718803410317019</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2687280733578423</v>
+      </c>
+      <c r="C97">
+        <v>-604.9426529785859</v>
+      </c>
+      <c r="D97">
+        <v>206.0773470214142</v>
+      </c>
+      <c r="E97">
+        <v>794.1200000000001</v>
+      </c>
+      <c r="F97">
+        <v>847.0200000000001</v>
+      </c>
+      <c r="G97">
+        <v>36</v>
+      </c>
+      <c r="H97">
+        <v>838.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>45.7</v>
+      </c>
+      <c r="K97">
+        <v>11.3</v>
+      </c>
+      <c r="L97">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M97">
+        <v>202.268376</v>
+      </c>
+      <c r="N97">
+        <v>-167.868376</v>
+      </c>
+      <c r="O97">
+        <v>-58.75393160000001</v>
+      </c>
+      <c r="P97">
+        <v>-109.1144444</v>
+      </c>
+      <c r="Q97">
+        <v>-97.81444440000003</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.107437734541324</v>
+      </c>
+      <c r="T97">
+        <v>14.49035853481716</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05952487599939992</v>
+      </c>
+      <c r="W97">
+        <v>0.2245854596113433</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1700710742839998</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2707280733578422</v>
+      </c>
+      <c r="C98">
+        <v>-615.6357327778343</v>
+      </c>
+      <c r="D98">
+        <v>204.3002672221658</v>
+      </c>
+      <c r="E98">
+        <v>803.0360000000001</v>
+      </c>
+      <c r="F98">
+        <v>855.936</v>
+      </c>
+      <c r="G98">
+        <v>36</v>
+      </c>
+      <c r="H98">
+        <v>838.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>45.7</v>
+      </c>
+      <c r="K98">
+        <v>11.3</v>
+      </c>
+      <c r="L98">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M98">
+        <v>204.3975168</v>
+      </c>
+      <c r="N98">
+        <v>-169.9975168</v>
+      </c>
+      <c r="O98">
+        <v>-59.49913088</v>
+      </c>
+      <c r="P98">
+        <v>-110.49838592</v>
+      </c>
+      <c r="Q98">
+        <v>-99.19838592000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.374597168176651</v>
+      </c>
+      <c r="T98">
+        <v>18.11294816852141</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05890482520773951</v>
+      </c>
+      <c r="W98">
+        <v>0.2247335277403918</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1682995005935415</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2727280733578423</v>
+      </c>
+      <c r="C99">
+        <v>-626.2984258043667</v>
+      </c>
+      <c r="D99">
+        <v>202.5535741956332</v>
+      </c>
+      <c r="E99">
+        <v>811.952</v>
+      </c>
+      <c r="F99">
+        <v>864.852</v>
+      </c>
+      <c r="G99">
+        <v>36</v>
+      </c>
+      <c r="H99">
+        <v>838.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>45.7</v>
+      </c>
+      <c r="K99">
+        <v>11.3</v>
+      </c>
+      <c r="L99">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M99">
+        <v>206.5266576</v>
+      </c>
+      <c r="N99">
+        <v>-172.1266576</v>
+      </c>
+      <c r="O99">
+        <v>-60.24433015999999</v>
+      </c>
+      <c r="P99">
+        <v>-111.88232744</v>
+      </c>
+      <c r="Q99">
+        <v>-100.58232744</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.819862890902202</v>
+      </c>
+      <c r="T99">
+        <v>24.15059755802855</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05829755896848447</v>
+      </c>
+      <c r="W99">
+        <v>0.2248785429183259</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1665644541956699</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2747280733578423</v>
+      </c>
+      <c r="C100">
+        <v>-636.9315048387758</v>
+      </c>
+      <c r="D100">
+        <v>200.8364951612242</v>
+      </c>
+      <c r="E100">
+        <v>820.8680000000001</v>
+      </c>
+      <c r="F100">
+        <v>873.768</v>
+      </c>
+      <c r="G100">
+        <v>36</v>
+      </c>
+      <c r="H100">
+        <v>838.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>45.7</v>
+      </c>
+      <c r="K100">
+        <v>11.3</v>
+      </c>
+      <c r="L100">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M100">
+        <v>208.6557984</v>
+      </c>
+      <c r="N100">
+        <v>-174.2557984</v>
+      </c>
+      <c r="O100">
+        <v>-60.98952944</v>
+      </c>
+      <c r="P100">
+        <v>-113.26626896</v>
+      </c>
+      <c r="Q100">
+        <v>-101.96626896</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.710394336353304</v>
+      </c>
+      <c r="T100">
+        <v>36.22589633704282</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05770268591778565</v>
+      </c>
+      <c r="W100">
+        <v>0.2250205986028328</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.164864816907959</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2767280733578423</v>
+      </c>
+      <c r="C101">
+        <v>-647.5357166779829</v>
+      </c>
+      <c r="D101">
+        <v>199.1482833220171</v>
+      </c>
+      <c r="E101">
+        <v>829.784</v>
+      </c>
+      <c r="F101">
+        <v>882.684</v>
+      </c>
+      <c r="G101">
+        <v>36</v>
+      </c>
+      <c r="H101">
+        <v>838.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>45.7</v>
+      </c>
+      <c r="K101">
+        <v>11.3</v>
+      </c>
+      <c r="L101">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="M101">
+        <v>210.7849392</v>
+      </c>
+      <c r="N101">
+        <v>-176.3849392</v>
+      </c>
+      <c r="O101">
+        <v>-61.73472871999999</v>
+      </c>
+      <c r="P101">
+        <v>-114.65021048</v>
+      </c>
+      <c r="Q101">
+        <v>-103.35021048</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.381988672706608</v>
+      </c>
+      <c r="T101">
+        <v>72.45179267408564</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05711983050447468</v>
+      </c>
+      <c r="W101">
+        <v>0.2251597844755314</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1631995157270706</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malta/malta_air_transport.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_air_transport.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08970954743829634</v>
+        <v>0.08942481402226234</v>
       </c>
       <c r="C2">
-        <v>847.0698348031702</v>
+        <v>843.7939504106921</v>
       </c>
       <c r="D2">
-        <v>832.2698348031703</v>
+        <v>837.7019504106921</v>
       </c>
       <c r="E2">
-        <v>-58.4</v>
+        <v>-49.692</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.708</v>
       </c>
       <c r="G2">
         <v>14.8</v>
@@ -1451,28 +1451,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4380124</v>
       </c>
       <c r="N2">
-        <v>71.59999999999999</v>
+        <v>71.16198759999999</v>
       </c>
       <c r="O2">
-        <v>25.06</v>
+        <v>24.90669565999999</v>
       </c>
       <c r="P2">
-        <v>46.54</v>
+        <v>46.25529193999999</v>
       </c>
       <c r="Q2">
-        <v>60.73999999999999</v>
+        <v>60.45529194</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08970954743829634</v>
+        <v>0.08999784244672962</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8094990060529977</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>163.4656918388612</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08942481402226234</v>
+        <v>0.08914008060622827</v>
       </c>
       <c r="C3">
-        <v>843.7939504106921</v>
+        <v>840.5894412815547</v>
       </c>
       <c r="D3">
-        <v>837.7019504106921</v>
+        <v>843.2054412815548</v>
       </c>
       <c r="E3">
-        <v>-49.692</v>
+        <v>-40.98399999999999</v>
       </c>
       <c r="F3">
-        <v>8.708</v>
+        <v>17.416</v>
       </c>
       <c r="G3">
         <v>14.8</v>
@@ -1533,28 +1533,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M3">
-        <v>0.4380124</v>
+        <v>0.8760247999999999</v>
       </c>
       <c r="N3">
-        <v>71.16198759999999</v>
+        <v>70.7239752</v>
       </c>
       <c r="O3">
-        <v>24.90669565999999</v>
+        <v>24.75339132</v>
       </c>
       <c r="P3">
-        <v>46.25529193999999</v>
+        <v>45.97058388</v>
       </c>
       <c r="Q3">
-        <v>60.45529194</v>
+        <v>60.17058388</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08999784244672962</v>
+        <v>0.09029202102676355</v>
       </c>
       <c r="T3">
-        <v>0.8094990060529977</v>
+        <v>0.8148869900575693</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>163.4656918388612</v>
+        <v>81.7328459194306</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08914008060622827</v>
+        <v>0.08885534719019424</v>
       </c>
       <c r="C4">
-        <v>840.5894412815547</v>
+        <v>837.457723471407</v>
       </c>
       <c r="D4">
-        <v>843.2054412815548</v>
+        <v>848.7817234714071</v>
       </c>
       <c r="E4">
-        <v>-40.98399999999999</v>
+        <v>-32.276</v>
       </c>
       <c r="F4">
-        <v>17.416</v>
+        <v>26.124</v>
       </c>
       <c r="G4">
         <v>14.8</v>
@@ -1615,28 +1615,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M4">
-        <v>0.8760247999999999</v>
+        <v>1.3140372</v>
       </c>
       <c r="N4">
-        <v>70.7239752</v>
+        <v>70.28596279999999</v>
       </c>
       <c r="O4">
-        <v>24.75339132</v>
+        <v>24.60008698</v>
       </c>
       <c r="P4">
-        <v>45.97058388</v>
+        <v>45.68587581999999</v>
       </c>
       <c r="Q4">
-        <v>60.17058388</v>
+        <v>59.88587582</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09029202102676355</v>
+        <v>0.09059226514453014</v>
       </c>
       <c r="T4">
-        <v>0.8148869900575693</v>
+        <v>0.8203860665158432</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>81.7328459194306</v>
+        <v>54.48856394628707</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08885534719019424</v>
+        <v>0.0885706137741602</v>
       </c>
       <c r="C5">
-        <v>837.457723471407</v>
+        <v>834.4002507438793</v>
       </c>
       <c r="D5">
-        <v>848.7817234714071</v>
+        <v>854.4322507438793</v>
       </c>
       <c r="E5">
-        <v>-32.276</v>
+        <v>-23.568</v>
       </c>
       <c r="F5">
-        <v>26.124</v>
+        <v>34.832</v>
       </c>
       <c r="G5">
         <v>14.8</v>
@@ -1697,28 +1697,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M5">
-        <v>1.3140372</v>
+        <v>1.7520496</v>
       </c>
       <c r="N5">
-        <v>70.28596279999999</v>
+        <v>69.84795039999999</v>
       </c>
       <c r="O5">
-        <v>24.60008698</v>
+        <v>24.44678264</v>
       </c>
       <c r="P5">
-        <v>45.68587581999999</v>
+        <v>45.40116775999999</v>
       </c>
       <c r="Q5">
-        <v>59.88587582</v>
+        <v>59.60116776</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09059226514453014</v>
+        <v>0.09089876434808354</v>
       </c>
       <c r="T5">
-        <v>0.8203860665158432</v>
+        <v>0.8259997070669981</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>54.48856394628707</v>
+        <v>40.86642295971529</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0885706137741602</v>
+        <v>0.08828588035812616</v>
       </c>
       <c r="C6">
-        <v>834.4002507438793</v>
+        <v>831.4185158341453</v>
       </c>
       <c r="D6">
-        <v>854.4322507438793</v>
+        <v>860.1585158341453</v>
       </c>
       <c r="E6">
-        <v>-23.568</v>
+        <v>-14.86</v>
       </c>
       <c r="F6">
-        <v>34.832</v>
+        <v>43.54</v>
       </c>
       <c r="G6">
         <v>14.8</v>
@@ -1779,28 +1779,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M6">
-        <v>1.7520496</v>
+        <v>2.190062</v>
       </c>
       <c r="N6">
-        <v>69.84795039999999</v>
+        <v>69.409938</v>
       </c>
       <c r="O6">
-        <v>24.44678264</v>
+        <v>24.2934783</v>
       </c>
       <c r="P6">
-        <v>45.40116775999999</v>
+        <v>45.1164597</v>
       </c>
       <c r="Q6">
-        <v>59.60116776</v>
+        <v>59.3164597</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09089876434808354</v>
+        <v>0.09121171616644859</v>
       </c>
       <c r="T6">
-        <v>0.8259997070669981</v>
+        <v>0.831731529524493</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>40.86642295971529</v>
+        <v>32.69313836777224</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08828588035812616</v>
+        <v>0.08800114694209211</v>
       </c>
       <c r="C7">
-        <v>831.4185158341453</v>
+        <v>828.514051763638</v>
       </c>
       <c r="D7">
-        <v>860.1585158341453</v>
+        <v>865.9620517636381</v>
       </c>
       <c r="E7">
-        <v>-14.86</v>
+        <v>-6.151999999999994</v>
       </c>
       <c r="F7">
-        <v>43.54</v>
+        <v>52.248</v>
       </c>
       <c r="G7">
         <v>14.8</v>
@@ -1861,28 +1861,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M7">
-        <v>2.190062</v>
+        <v>2.6280744</v>
       </c>
       <c r="N7">
-        <v>69.409938</v>
+        <v>68.97192559999999</v>
       </c>
       <c r="O7">
-        <v>24.2934783</v>
+        <v>24.14017395999999</v>
       </c>
       <c r="P7">
-        <v>45.1164597</v>
+        <v>44.83175163999999</v>
       </c>
       <c r="Q7">
-        <v>59.3164597</v>
+        <v>59.03175164</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09121171616644859</v>
+        <v>0.09153132653414056</v>
       </c>
       <c r="T7">
-        <v>0.831731529524493</v>
+        <v>0.8375853056512964</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>32.69313836777224</v>
+        <v>27.24428197314353</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08800114694209211</v>
+        <v>0.08771641352605809</v>
       </c>
       <c r="C8">
-        <v>828.514051763638</v>
+        <v>825.6884332083484</v>
       </c>
       <c r="D8">
-        <v>865.9620517636381</v>
+        <v>871.8444332083485</v>
       </c>
       <c r="E8">
-        <v>-6.152000000000001</v>
+        <v>2.55599999999999</v>
       </c>
       <c r="F8">
-        <v>52.248</v>
+        <v>60.95599999999999</v>
       </c>
       <c r="G8">
         <v>14.8</v>
@@ -1943,28 +1943,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M8">
-        <v>2.6280744</v>
+        <v>3.066086799999999</v>
       </c>
       <c r="N8">
-        <v>68.97192559999999</v>
+        <v>68.5339132</v>
       </c>
       <c r="O8">
-        <v>24.14017395999999</v>
+        <v>23.98686962</v>
       </c>
       <c r="P8">
-        <v>44.83175163999999</v>
+        <v>44.54704358</v>
       </c>
       <c r="Q8">
-        <v>59.03175164</v>
+        <v>58.74704358</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09153132653414056</v>
+        <v>0.09185781024307321</v>
       </c>
       <c r="T8">
-        <v>0.8375853056512964</v>
+        <v>0.8435649694367405</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.24428197314353</v>
+        <v>23.35224169126589</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08771641352605808</v>
+        <v>0.08743168011002404</v>
       </c>
       <c r="C9">
-        <v>825.6884332083488</v>
+        <v>822.9432779232776</v>
       </c>
       <c r="D9">
-        <v>871.8444332083488</v>
+        <v>877.8072779232776</v>
       </c>
       <c r="E9">
-        <v>2.556000000000004</v>
+        <v>11.264</v>
       </c>
       <c r="F9">
-        <v>60.956</v>
+        <v>69.664</v>
       </c>
       <c r="G9">
         <v>14.8</v>
@@ -2025,28 +2025,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M9">
-        <v>3.0660868</v>
+        <v>3.5040992</v>
       </c>
       <c r="N9">
-        <v>68.5339132</v>
+        <v>68.0959008</v>
       </c>
       <c r="O9">
-        <v>23.98686962</v>
+        <v>23.83356528</v>
       </c>
       <c r="P9">
-        <v>44.54704358</v>
+        <v>44.26233551999999</v>
       </c>
       <c r="Q9">
-        <v>58.74704358</v>
+        <v>58.46233552</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09185781024307321</v>
+        <v>0.09219139142393917</v>
       </c>
       <c r="T9">
-        <v>0.8435649694367405</v>
+        <v>0.8496746259131727</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.35224169126588</v>
+        <v>20.43321147985765</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08743168011002404</v>
+        <v>0.08714694669399002</v>
       </c>
       <c r="C10">
-        <v>822.9432779232776</v>
+        <v>820.2802482257391</v>
       </c>
       <c r="D10">
-        <v>877.8072779232776</v>
+        <v>883.8522482257391</v>
       </c>
       <c r="E10">
-        <v>11.264</v>
+        <v>19.972</v>
       </c>
       <c r="F10">
-        <v>69.664</v>
+        <v>78.372</v>
       </c>
       <c r="G10">
         <v>14.8</v>
@@ -2107,28 +2107,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M10">
-        <v>3.5040992</v>
+        <v>3.9421116</v>
       </c>
       <c r="N10">
-        <v>68.0959008</v>
+        <v>67.65788839999999</v>
       </c>
       <c r="O10">
-        <v>23.83356528</v>
+        <v>23.68026094</v>
       </c>
       <c r="P10">
-        <v>44.26233551999999</v>
+        <v>43.97762745999999</v>
       </c>
       <c r="Q10">
-        <v>58.46233552</v>
+        <v>58.17762746</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09219139142393917</v>
+        <v>0.09253230405932969</v>
       </c>
       <c r="T10">
-        <v>0.8496746259131727</v>
+        <v>0.8559185605539221</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.43321147985765</v>
+        <v>18.16285464876235</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08714694669399002</v>
+        <v>0.08686221327795597</v>
       </c>
       <c r="C11">
-        <v>820.2802482257391</v>
+        <v>817.7010525403812</v>
       </c>
       <c r="D11">
-        <v>883.8522482257391</v>
+        <v>889.9810525403811</v>
       </c>
       <c r="E11">
-        <v>19.972</v>
+        <v>28.67999999999999</v>
       </c>
       <c r="F11">
-        <v>78.372</v>
+        <v>87.07999999999998</v>
       </c>
       <c r="G11">
         <v>14.8</v>
@@ -2189,28 +2189,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M11">
-        <v>3.9421116</v>
+        <v>4.380123999999999</v>
       </c>
       <c r="N11">
-        <v>67.65788839999999</v>
+        <v>67.219876</v>
       </c>
       <c r="O11">
-        <v>23.68026094</v>
+        <v>23.5269566</v>
       </c>
       <c r="P11">
-        <v>43.97762745999999</v>
+        <v>43.6929194</v>
       </c>
       <c r="Q11">
-        <v>58.17762746</v>
+        <v>57.8929194</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09253230405932969</v>
+        <v>0.0928807925310622</v>
       </c>
       <c r="T11">
-        <v>0.8559185605539221</v>
+        <v>0.8623012492977993</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.16285464876235</v>
+        <v>16.34656918388612</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08686221327795597</v>
+        <v>0.08657747986192195</v>
       </c>
       <c r="C12">
-        <v>817.7010525403811</v>
+        <v>815.207447008932</v>
       </c>
       <c r="D12">
-        <v>889.9810525403811</v>
+        <v>896.1954470089321</v>
       </c>
       <c r="E12">
-        <v>28.68</v>
+        <v>37.388</v>
       </c>
       <c r="F12">
-        <v>87.08</v>
+        <v>95.788</v>
       </c>
       <c r="G12">
         <v>14.8</v>
@@ -2271,28 +2271,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M12">
-        <v>4.380123999999999</v>
+        <v>4.818136399999999</v>
       </c>
       <c r="N12">
-        <v>67.219876</v>
+        <v>66.78186359999999</v>
       </c>
       <c r="O12">
-        <v>23.5269566</v>
+        <v>23.37365226</v>
       </c>
       <c r="P12">
-        <v>43.6929194</v>
+        <v>43.40821133999999</v>
       </c>
       <c r="Q12">
-        <v>57.8929194</v>
+        <v>57.60821134</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0928807925310622</v>
+        <v>0.09323711220440668</v>
       </c>
       <c r="T12">
-        <v>0.8623012492977993</v>
+        <v>0.8688273692494041</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.34656918388612</v>
+        <v>14.86051743989647</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08657747986192195</v>
+        <v>0.08629274644588789</v>
       </c>
       <c r="C13">
-        <v>815.207447008932</v>
+        <v>812.8012371678691</v>
       </c>
       <c r="D13">
-        <v>896.1954470089321</v>
+        <v>902.4972371678691</v>
       </c>
       <c r="E13">
-        <v>37.388</v>
+        <v>46.096</v>
       </c>
       <c r="F13">
-        <v>95.788</v>
+        <v>104.496</v>
       </c>
       <c r="G13">
         <v>14.8</v>
@@ -2353,28 +2353,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M13">
-        <v>4.818136399999999</v>
+        <v>5.256148799999999</v>
       </c>
       <c r="N13">
-        <v>66.78186359999999</v>
+        <v>66.34385119999999</v>
       </c>
       <c r="O13">
-        <v>23.37365226</v>
+        <v>23.22034791999999</v>
       </c>
       <c r="P13">
-        <v>43.40821133999999</v>
+        <v>43.12350327999999</v>
       </c>
       <c r="Q13">
-        <v>57.60821134</v>
+        <v>57.32350328</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09323711220440668</v>
+        <v>0.09360153005214533</v>
       </c>
       <c r="T13">
-        <v>0.8688273692494041</v>
+        <v>0.8755018101089996</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.86051743989647</v>
+        <v>13.62214098657176</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08629274644588789</v>
+        <v>0.08613476302985386</v>
       </c>
       <c r="C14">
-        <v>812.8012371678691</v>
+        <v>807.6281431838912</v>
       </c>
       <c r="D14">
-        <v>902.4972371678691</v>
+        <v>906.0321431838912</v>
       </c>
       <c r="E14">
-        <v>46.096</v>
+        <v>54.80399999999999</v>
       </c>
       <c r="F14">
-        <v>104.496</v>
+        <v>113.204</v>
       </c>
       <c r="G14">
         <v>14.8</v>
@@ -2435,45 +2435,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M14">
-        <v>5.256148799999999</v>
+        <v>5.863967199999999</v>
       </c>
       <c r="N14">
-        <v>66.34385119999999</v>
+        <v>65.73603279999999</v>
       </c>
       <c r="O14">
-        <v>23.22034791999999</v>
+        <v>23.00761147999999</v>
       </c>
       <c r="P14">
-        <v>43.12350327999999</v>
+        <v>42.72842132</v>
       </c>
       <c r="Q14">
-        <v>57.32350328</v>
+        <v>56.92842132</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09360153005214533</v>
+        <v>0.0939743253216711</v>
       </c>
       <c r="T14">
-        <v>0.8755018101089996</v>
+        <v>0.882329686390655</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.35</v>
       </c>
       <c r="W14">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.62214098657176</v>
+        <v>12.21016379491345</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08613476302985386</v>
+        <v>0.08585977961381984</v>
       </c>
       <c r="C15">
-        <v>807.6281431838912</v>
+        <v>805.139443843333</v>
       </c>
       <c r="D15">
-        <v>906.0321431838912</v>
+        <v>912.251443843333</v>
       </c>
       <c r="E15">
-        <v>54.80399999999999</v>
+        <v>63.51200000000001</v>
       </c>
       <c r="F15">
-        <v>113.204</v>
+        <v>121.912</v>
       </c>
       <c r="G15">
         <v>14.8</v>
@@ -2517,28 +2517,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M15">
-        <v>5.863967199999999</v>
+        <v>6.3150416</v>
       </c>
       <c r="N15">
-        <v>65.73603279999999</v>
+        <v>65.28495839999999</v>
       </c>
       <c r="O15">
-        <v>23.00761147999999</v>
+        <v>22.84973544</v>
       </c>
       <c r="P15">
-        <v>42.72842132</v>
+        <v>42.43522296</v>
       </c>
       <c r="Q15">
-        <v>56.92842132</v>
+        <v>56.63522295999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0939743253216711</v>
+        <v>0.09435579024862772</v>
       </c>
       <c r="T15">
-        <v>0.882329686390655</v>
+        <v>0.8893163504928142</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.21016379491345</v>
+        <v>11.33800923813392</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08585977961381984</v>
+        <v>0.08558479619778578</v>
       </c>
       <c r="C16">
-        <v>805.139443843333</v>
+        <v>802.7367172714775</v>
       </c>
       <c r="D16">
-        <v>912.251443843333</v>
+        <v>918.5567172714775</v>
       </c>
       <c r="E16">
-        <v>63.51200000000001</v>
+        <v>72.22</v>
       </c>
       <c r="F16">
-        <v>121.912</v>
+        <v>130.62</v>
       </c>
       <c r="G16">
         <v>14.8</v>
@@ -2599,28 +2599,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M16">
-        <v>6.3150416</v>
+        <v>6.766116</v>
       </c>
       <c r="N16">
-        <v>65.28495839999999</v>
+        <v>64.833884</v>
       </c>
       <c r="O16">
-        <v>22.84973544</v>
+        <v>22.6918594</v>
       </c>
       <c r="P16">
-        <v>42.43522296</v>
+        <v>42.1420246</v>
       </c>
       <c r="Q16">
-        <v>56.63522295999999</v>
+        <v>56.3420246</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09435579024862772</v>
+        <v>0.09474623082092445</v>
       </c>
       <c r="T16">
-        <v>0.8893163504928142</v>
+        <v>0.8964674066914945</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.33800923813392</v>
+        <v>10.58214195559166</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08558479619778578</v>
+        <v>0.08530981278175175</v>
       </c>
       <c r="C17">
-        <v>802.7367172714775</v>
+        <v>800.421758547871</v>
       </c>
       <c r="D17">
-        <v>918.5567172714775</v>
+        <v>924.9497585478711</v>
       </c>
       <c r="E17">
-        <v>72.21999999999997</v>
+        <v>80.928</v>
       </c>
       <c r="F17">
-        <v>130.62</v>
+        <v>139.328</v>
       </c>
       <c r="G17">
         <v>14.8</v>
@@ -2681,28 +2681,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M17">
-        <v>6.766115999999998</v>
+        <v>7.2171904</v>
       </c>
       <c r="N17">
-        <v>64.833884</v>
+        <v>64.3828096</v>
       </c>
       <c r="O17">
-        <v>22.6918594</v>
+        <v>22.53398336</v>
       </c>
       <c r="P17">
-        <v>42.1420246</v>
+        <v>41.84882624</v>
       </c>
       <c r="Q17">
-        <v>56.3420246</v>
+        <v>56.04882624</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09474623082092445</v>
+        <v>0.09514596759732352</v>
       </c>
       <c r="T17">
-        <v>0.8964674066914945</v>
+        <v>0.9037887261330005</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.58214195559166</v>
+        <v>9.920758083367179</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08530981278175175</v>
+        <v>0.08522267936571773</v>
       </c>
       <c r="C18">
-        <v>800.421758547871</v>
+        <v>793.7581155885089</v>
       </c>
       <c r="D18">
-        <v>924.9497585478711</v>
+        <v>926.994115588509</v>
       </c>
       <c r="E18">
-        <v>80.928</v>
+        <v>89.636</v>
       </c>
       <c r="F18">
-        <v>139.328</v>
+        <v>148.036</v>
       </c>
       <c r="G18">
         <v>14.8</v>
@@ -2763,45 +2763,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M18">
-        <v>7.2171904</v>
+        <v>7.919926</v>
       </c>
       <c r="N18">
-        <v>64.3828096</v>
+        <v>63.68007399999999</v>
       </c>
       <c r="O18">
-        <v>22.53398336</v>
+        <v>22.28802589999999</v>
       </c>
       <c r="P18">
-        <v>41.84882624</v>
+        <v>41.3920481</v>
       </c>
       <c r="Q18">
-        <v>56.04882624</v>
+        <v>55.5920481</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09514596759732352</v>
+        <v>0.09555533658520207</v>
       </c>
       <c r="T18">
-        <v>0.9037887261330005</v>
+        <v>0.9112864629104467</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.35</v>
       </c>
       <c r="W18">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.920758083367179</v>
+        <v>9.04048850961486</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08522267936571773</v>
+        <v>0.08495874594968367</v>
       </c>
       <c r="C19">
-        <v>793.7581155885089</v>
+        <v>791.2981380324637</v>
       </c>
       <c r="D19">
-        <v>926.994115588509</v>
+        <v>933.2421380324638</v>
       </c>
       <c r="E19">
-        <v>89.636</v>
+        <v>98.34399999999999</v>
       </c>
       <c r="F19">
-        <v>148.036</v>
+        <v>156.744</v>
       </c>
       <c r="G19">
         <v>14.8</v>
@@ -2845,28 +2845,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M19">
-        <v>7.919926</v>
+        <v>8.385804</v>
       </c>
       <c r="N19">
-        <v>63.68007399999999</v>
+        <v>63.21419599999999</v>
       </c>
       <c r="O19">
-        <v>22.28802589999999</v>
+        <v>22.1249686</v>
       </c>
       <c r="P19">
-        <v>41.3920481</v>
+        <v>41.0892274</v>
       </c>
       <c r="Q19">
-        <v>55.5920481</v>
+        <v>55.2892274</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09555533658520207</v>
+        <v>0.09597469018254107</v>
       </c>
       <c r="T19">
-        <v>0.9112864629104467</v>
+        <v>0.9189670713166107</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.04048850961486</v>
+        <v>8.538239147969591</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08495874594968368</v>
+        <v>0.08469481253364966</v>
       </c>
       <c r="C20">
-        <v>791.2981380324635</v>
+        <v>788.9229564581777</v>
       </c>
       <c r="D20">
-        <v>933.2421380324636</v>
+        <v>939.5749564581778</v>
       </c>
       <c r="E20">
-        <v>98.34399999999999</v>
+        <v>107.052</v>
       </c>
       <c r="F20">
-        <v>156.744</v>
+        <v>165.452</v>
       </c>
       <c r="G20">
         <v>14.8</v>
@@ -2927,28 +2927,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M20">
-        <v>8.385804</v>
+        <v>8.851682</v>
       </c>
       <c r="N20">
-        <v>63.21419599999999</v>
+        <v>62.748318</v>
       </c>
       <c r="O20">
-        <v>22.1249686</v>
+        <v>21.9619113</v>
       </c>
       <c r="P20">
-        <v>41.0892274</v>
+        <v>40.7864067</v>
       </c>
       <c r="Q20">
-        <v>55.2892274</v>
+        <v>54.9864067</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09597469018254107</v>
+        <v>0.09640439818969093</v>
       </c>
       <c r="T20">
-        <v>0.9189670713166107</v>
+        <v>0.9268373243747792</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.538239147969591</v>
+        <v>8.088858140181719</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08469481253364966</v>
+        <v>0.08443087911761561</v>
       </c>
       <c r="C21">
-        <v>788.9229564581777</v>
+        <v>786.6343088918367</v>
       </c>
       <c r="D21">
-        <v>939.5749564581778</v>
+        <v>945.9943088918367</v>
       </c>
       <c r="E21">
-        <v>107.052</v>
+        <v>115.76</v>
       </c>
       <c r="F21">
-        <v>165.452</v>
+        <v>174.16</v>
       </c>
       <c r="G21">
         <v>14.8</v>
@@ -3009,28 +3009,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M21">
-        <v>8.851682</v>
+        <v>9.31756</v>
       </c>
       <c r="N21">
-        <v>62.748318</v>
+        <v>62.28243999999999</v>
       </c>
       <c r="O21">
-        <v>21.9619113</v>
+        <v>21.798854</v>
       </c>
       <c r="P21">
-        <v>40.7864067</v>
+        <v>40.483586</v>
       </c>
       <c r="Q21">
-        <v>54.9864067</v>
+        <v>54.68358600000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09640439818969093</v>
+        <v>0.09684484889701951</v>
       </c>
       <c r="T21">
-        <v>0.9268373243747792</v>
+        <v>0.9349043337594016</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.088858140181719</v>
+        <v>7.684415233172633</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08443087911761561</v>
+        <v>0.08427614570158158</v>
       </c>
       <c r="C22">
-        <v>786.6343088918367</v>
+        <v>781.7306642474607</v>
       </c>
       <c r="D22">
-        <v>945.9943088918367</v>
+        <v>949.7986642474608</v>
       </c>
       <c r="E22">
-        <v>115.76</v>
+        <v>124.468</v>
       </c>
       <c r="F22">
-        <v>174.16</v>
+        <v>182.868</v>
       </c>
       <c r="G22">
         <v>14.8</v>
@@ -3091,45 +3091,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M22">
-        <v>9.31756</v>
+        <v>9.929732400000001</v>
       </c>
       <c r="N22">
-        <v>62.28243999999999</v>
+        <v>61.6702676</v>
       </c>
       <c r="O22">
-        <v>21.798854</v>
+        <v>21.58459366</v>
       </c>
       <c r="P22">
-        <v>40.483586</v>
+        <v>40.08567394</v>
       </c>
       <c r="Q22">
-        <v>54.68358600000001</v>
+        <v>54.28567394</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09684484889701951</v>
+        <v>0.09729645025516655</v>
       </c>
       <c r="T22">
-        <v>0.9349043337594016</v>
+        <v>0.9431755712297107</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.684415233172633</v>
+        <v>7.210667630881975</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08427614570158158</v>
+        <v>0.08401741228554754</v>
       </c>
       <c r="C23">
-        <v>781.7306642474607</v>
+        <v>779.4528393495633</v>
       </c>
       <c r="D23">
-        <v>949.7986642474608</v>
+        <v>956.2288393495634</v>
       </c>
       <c r="E23">
-        <v>124.468</v>
+        <v>133.176</v>
       </c>
       <c r="F23">
-        <v>182.868</v>
+        <v>191.576</v>
       </c>
       <c r="G23">
         <v>14.8</v>
@@ -3173,28 +3173,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M23">
-        <v>9.929732400000001</v>
+        <v>10.4025768</v>
       </c>
       <c r="N23">
-        <v>61.6702676</v>
+        <v>61.1974232</v>
       </c>
       <c r="O23">
-        <v>21.58459366</v>
+        <v>21.41909812</v>
       </c>
       <c r="P23">
-        <v>40.08567394</v>
+        <v>39.77832508</v>
       </c>
       <c r="Q23">
-        <v>54.28567394</v>
+        <v>53.97832508</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09729645025516655</v>
+        <v>0.09775963113531735</v>
       </c>
       <c r="T23">
-        <v>0.9431755712297107</v>
+        <v>0.951658891712079</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.210667630881975</v>
+        <v>6.882910011296431</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08401741228554754</v>
+        <v>0.08375867886951349</v>
       </c>
       <c r="C24">
-        <v>779.4528393495633</v>
+        <v>777.2626729908677</v>
       </c>
       <c r="D24">
-        <v>956.2288393495634</v>
+        <v>962.7466729908678</v>
       </c>
       <c r="E24">
-        <v>133.176</v>
+        <v>141.884</v>
       </c>
       <c r="F24">
-        <v>191.576</v>
+        <v>200.284</v>
       </c>
       <c r="G24">
         <v>14.8</v>
@@ -3255,28 +3255,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M24">
-        <v>10.4025768</v>
+        <v>10.8754212</v>
       </c>
       <c r="N24">
-        <v>61.1974232</v>
+        <v>60.7245788</v>
       </c>
       <c r="O24">
-        <v>21.41909812</v>
+        <v>21.25360258</v>
       </c>
       <c r="P24">
-        <v>39.77832508</v>
+        <v>39.47097622</v>
       </c>
       <c r="Q24">
-        <v>53.97832508</v>
+        <v>53.67097622</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09775963113531735</v>
+        <v>0.09823484268767986</v>
       </c>
       <c r="T24">
-        <v>0.951658891712079</v>
+        <v>0.9603625581810024</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.882910011296431</v>
+        <v>6.583653054283543</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08375867886951349</v>
+        <v>0.08349994545347945</v>
       </c>
       <c r="C25">
-        <v>777.2626729908677</v>
+        <v>775.161969963902</v>
       </c>
       <c r="D25">
-        <v>962.7466729908678</v>
+        <v>969.353969963902</v>
       </c>
       <c r="E25">
-        <v>141.884</v>
+        <v>150.592</v>
       </c>
       <c r="F25">
-        <v>200.284</v>
+        <v>208.992</v>
       </c>
       <c r="G25">
         <v>14.8</v>
@@ -3337,28 +3337,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M25">
-        <v>10.8754212</v>
+        <v>11.3482656</v>
       </c>
       <c r="N25">
-        <v>60.7245788</v>
+        <v>60.25173439999999</v>
       </c>
       <c r="O25">
-        <v>21.25360258</v>
+        <v>21.08810703999999</v>
       </c>
       <c r="P25">
-        <v>39.47097622</v>
+        <v>39.16362735999999</v>
       </c>
       <c r="Q25">
-        <v>53.67097622</v>
+        <v>53.36362736</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09823484268767986</v>
+        <v>0.09872255980720981</v>
       </c>
       <c r="T25">
-        <v>0.9603625581810024</v>
+        <v>0.969295268504371</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.583653054283543</v>
+        <v>6.309334177021728</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08349994545347945</v>
+        <v>0.08340371203744543</v>
       </c>
       <c r="C26">
-        <v>775.161969963902</v>
+        <v>768.9346889892706</v>
       </c>
       <c r="D26">
-        <v>969.353969963902</v>
+        <v>971.8346889892706</v>
       </c>
       <c r="E26">
-        <v>150.592</v>
+        <v>159.3</v>
       </c>
       <c r="F26">
-        <v>208.992</v>
+        <v>217.7</v>
       </c>
       <c r="G26">
         <v>14.8</v>
@@ -3419,45 +3419,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M26">
-        <v>11.3482656</v>
+        <v>12.03881</v>
       </c>
       <c r="N26">
-        <v>60.2517344</v>
+        <v>59.56119</v>
       </c>
       <c r="O26">
-        <v>21.08810704</v>
+        <v>20.8464165</v>
       </c>
       <c r="P26">
-        <v>39.16362736</v>
+        <v>38.7147735</v>
       </c>
       <c r="Q26">
-        <v>53.36362736</v>
+        <v>52.9147735</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09872255980720981</v>
+        <v>0.09922328271659389</v>
       </c>
       <c r="T26">
-        <v>0.969295268504371</v>
+        <v>0.978466184436363</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.35</v>
       </c>
       <c r="W26">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.309334177021729</v>
+        <v>5.9474316813705</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08340371203744543</v>
+        <v>0.08315147862141138</v>
       </c>
       <c r="C27">
-        <v>768.9346889892706</v>
+        <v>766.7894595266498</v>
       </c>
       <c r="D27">
-        <v>971.8346889892706</v>
+        <v>978.3974595266499</v>
       </c>
       <c r="E27">
-        <v>159.3</v>
+        <v>168.008</v>
       </c>
       <c r="F27">
-        <v>217.7</v>
+        <v>226.408</v>
       </c>
       <c r="G27">
         <v>14.8</v>
@@ -3501,28 +3501,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M27">
-        <v>12.03881</v>
+        <v>12.5203624</v>
       </c>
       <c r="N27">
-        <v>59.56119</v>
+        <v>59.0796376</v>
       </c>
       <c r="O27">
-        <v>20.8464165</v>
+        <v>20.67787316</v>
       </c>
       <c r="P27">
-        <v>38.7147735</v>
+        <v>38.40176444</v>
       </c>
       <c r="Q27">
-        <v>52.9147735</v>
+        <v>52.60176444</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09922328271659389</v>
+        <v>0.09973753867758295</v>
       </c>
       <c r="T27">
-        <v>0.978466184436363</v>
+        <v>0.9878849629611113</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.9474316813705</v>
+        <v>5.718684309010097</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08315147862141138</v>
+        <v>0.08289924520537734</v>
       </c>
       <c r="C28">
-        <v>766.7894595266498</v>
+        <v>764.7334690780373</v>
       </c>
       <c r="D28">
-        <v>978.3974595266499</v>
+        <v>985.0494690780373</v>
       </c>
       <c r="E28">
-        <v>168.008</v>
+        <v>176.716</v>
       </c>
       <c r="F28">
-        <v>226.408</v>
+        <v>235.116</v>
       </c>
       <c r="G28">
         <v>14.8</v>
@@ -3583,28 +3583,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M28">
-        <v>12.5203624</v>
+        <v>13.0019148</v>
       </c>
       <c r="N28">
-        <v>59.0796376</v>
+        <v>58.59808519999999</v>
       </c>
       <c r="O28">
-        <v>20.67787316</v>
+        <v>20.50932982</v>
       </c>
       <c r="P28">
-        <v>38.40176444</v>
+        <v>38.08875537999999</v>
       </c>
       <c r="Q28">
-        <v>52.60176444</v>
+        <v>52.28875538</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09973753867758295</v>
+        <v>0.1002658838429827</v>
       </c>
       <c r="T28">
-        <v>0.9878849629611113</v>
+        <v>0.9975617902125652</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.718684309010097</v>
+        <v>5.506881186454167</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08289924520537734</v>
+        <v>0.08264701178934331</v>
       </c>
       <c r="C29">
-        <v>764.7334690780373</v>
+        <v>762.7685502800773</v>
       </c>
       <c r="D29">
-        <v>985.0494690780373</v>
+        <v>991.7925502800773</v>
       </c>
       <c r="E29">
-        <v>176.716</v>
+        <v>185.424</v>
       </c>
       <c r="F29">
-        <v>235.116</v>
+        <v>243.824</v>
       </c>
       <c r="G29">
         <v>14.8</v>
@@ -3665,28 +3665,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M29">
-        <v>13.0019148</v>
+        <v>13.4834672</v>
       </c>
       <c r="N29">
-        <v>58.59808519999999</v>
+        <v>58.11653279999999</v>
       </c>
       <c r="O29">
-        <v>20.50932982</v>
+        <v>20.34078648</v>
       </c>
       <c r="P29">
-        <v>38.08875537999999</v>
+        <v>37.77574632</v>
       </c>
       <c r="Q29">
-        <v>52.28875538</v>
+        <v>51.97574632</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1002658838429827</v>
+        <v>0.1008089052629768</v>
       </c>
       <c r="T29">
-        <v>0.9975617902125652</v>
+        <v>1.007507418221004</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.506881186454167</v>
+        <v>5.310206858366517</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08264701178934331</v>
+        <v>0.08239477837330927</v>
       </c>
       <c r="C30">
-        <v>762.7685502800773</v>
+        <v>760.8965862959889</v>
       </c>
       <c r="D30">
-        <v>991.7925502800773</v>
+        <v>998.628586295989</v>
       </c>
       <c r="E30">
-        <v>185.424</v>
+        <v>194.132</v>
       </c>
       <c r="F30">
-        <v>243.824</v>
+        <v>252.532</v>
       </c>
       <c r="G30">
         <v>14.8</v>
@@ -3747,28 +3747,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M30">
-        <v>13.4834672</v>
+        <v>13.9650196</v>
       </c>
       <c r="N30">
-        <v>58.11653279999999</v>
+        <v>57.63498039999999</v>
       </c>
       <c r="O30">
-        <v>20.34078648</v>
+        <v>20.17224314</v>
       </c>
       <c r="P30">
-        <v>37.77574632</v>
+        <v>37.46273726</v>
       </c>
       <c r="Q30">
-        <v>51.97574632</v>
+        <v>51.66273726</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1008089052629768</v>
+        <v>0.101367223060999</v>
       </c>
       <c r="T30">
-        <v>1.007507418221004</v>
+        <v>1.017733204764891</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.310206858366517</v>
+        <v>5.127096277043534</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08239477837330927</v>
+        <v>0.08214254495727523</v>
       </c>
       <c r="C31">
-        <v>760.896586295989</v>
+        <v>759.119512568951</v>
       </c>
       <c r="D31">
-        <v>998.628586295989</v>
+        <v>1005.559512568951</v>
       </c>
       <c r="E31">
-        <v>194.132</v>
+        <v>202.8399999999999</v>
       </c>
       <c r="F31">
-        <v>252.532</v>
+        <v>261.24</v>
       </c>
       <c r="G31">
         <v>14.8</v>
@@ -3829,28 +3829,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M31">
-        <v>13.9650196</v>
+        <v>14.446572</v>
       </c>
       <c r="N31">
-        <v>57.6349804</v>
+        <v>57.153428</v>
       </c>
       <c r="O31">
-        <v>20.17224314</v>
+        <v>20.0036998</v>
       </c>
       <c r="P31">
-        <v>37.46273726</v>
+        <v>37.1497282</v>
       </c>
       <c r="Q31">
-        <v>51.66273726</v>
+        <v>51.3497282</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.101367223060999</v>
+        <v>0.1019414927961075</v>
       </c>
       <c r="T31">
-        <v>1.017733204764891</v>
+        <v>1.028251156638604</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.127096277043535</v>
+        <v>4.956193067808751</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08214254495727523</v>
+        <v>0.08189031154124118</v>
       </c>
       <c r="C32">
-        <v>759.119512568951</v>
+        <v>757.4393186490112</v>
       </c>
       <c r="D32">
-        <v>1005.559512568951</v>
+        <v>1012.587318649011</v>
       </c>
       <c r="E32">
-        <v>202.8399999999999</v>
+        <v>211.548</v>
       </c>
       <c r="F32">
-        <v>261.24</v>
+        <v>269.948</v>
       </c>
       <c r="G32">
         <v>14.8</v>
@@ -3911,28 +3911,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M32">
-        <v>14.446572</v>
+        <v>14.9281244</v>
       </c>
       <c r="N32">
-        <v>57.153428</v>
+        <v>56.67187559999999</v>
       </c>
       <c r="O32">
-        <v>20.0036998</v>
+        <v>19.83515646</v>
       </c>
       <c r="P32">
-        <v>37.1497282</v>
+        <v>36.83671914</v>
       </c>
       <c r="Q32">
-        <v>51.3497282</v>
+        <v>51.03671914</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1019414927961075</v>
+        <v>0.1025324080307843</v>
       </c>
       <c r="T32">
-        <v>1.028251156638604</v>
+        <v>1.03907397668257</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.956193067808751</v>
+        <v>4.796315872072984</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08189031154124118</v>
+        <v>0.08163807812520715</v>
       </c>
       <c r="C33">
-        <v>757.4393186490112</v>
+        <v>755.8580500971448</v>
       </c>
       <c r="D33">
-        <v>1012.587318649011</v>
+        <v>1019.714050097145</v>
       </c>
       <c r="E33">
-        <v>211.548</v>
+        <v>220.256</v>
       </c>
       <c r="F33">
-        <v>269.948</v>
+        <v>278.656</v>
       </c>
       <c r="G33">
         <v>14.8</v>
@@ -3993,28 +3993,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M33">
-        <v>14.9281244</v>
+        <v>15.4096768</v>
       </c>
       <c r="N33">
-        <v>56.67187559999999</v>
+        <v>56.19032319999999</v>
       </c>
       <c r="O33">
-        <v>19.83515646</v>
+        <v>19.66661312</v>
       </c>
       <c r="P33">
-        <v>36.83671914</v>
+        <v>36.52371008</v>
       </c>
       <c r="Q33">
-        <v>51.03671914</v>
+        <v>50.72371008</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1025324080307843</v>
+        <v>0.1031407031253047</v>
       </c>
       <c r="T33">
-        <v>1.03907397668257</v>
+        <v>1.050215114963123</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.796315872072984</v>
+        <v>4.646431001070703</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08163807812520715</v>
+        <v>0.08138584470917312</v>
       </c>
       <c r="C34">
-        <v>755.8580500971448</v>
+        <v>754.377810470291</v>
       </c>
       <c r="D34">
-        <v>1019.714050097145</v>
+        <v>1026.941810470291</v>
       </c>
       <c r="E34">
-        <v>220.256</v>
+        <v>228.964</v>
       </c>
       <c r="F34">
-        <v>278.656</v>
+        <v>287.364</v>
       </c>
       <c r="G34">
         <v>14.8</v>
@@ -4075,28 +4075,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M34">
-        <v>15.4096768</v>
+        <v>15.8912292</v>
       </c>
       <c r="N34">
-        <v>56.19032319999999</v>
+        <v>55.7087708</v>
       </c>
       <c r="O34">
-        <v>19.66661312</v>
+        <v>19.49806978</v>
       </c>
       <c r="P34">
-        <v>36.52371008</v>
+        <v>36.21070102</v>
       </c>
       <c r="Q34">
-        <v>50.72371008</v>
+        <v>50.41070102</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1031407031253047</v>
+        <v>0.1037671562823479</v>
       </c>
       <c r="T34">
-        <v>1.050215114963123</v>
+        <v>1.061688824535632</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.646431001070703</v>
+        <v>4.505630061644318</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08138584470917312</v>
+        <v>0.08168611129313907</v>
       </c>
       <c r="C35">
-        <v>754.377810470291</v>
+        <v>737.0771739808455</v>
       </c>
       <c r="D35">
-        <v>1026.941810470291</v>
+        <v>1018.349173980845</v>
       </c>
       <c r="E35">
-        <v>228.964</v>
+        <v>237.672</v>
       </c>
       <c r="F35">
-        <v>287.364</v>
+        <v>296.072</v>
       </c>
       <c r="G35">
         <v>14.8</v>
@@ -4157,45 +4157,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M35">
-        <v>15.8912292</v>
+        <v>17.1129616</v>
       </c>
       <c r="N35">
-        <v>55.7087708</v>
+        <v>54.48703839999999</v>
       </c>
       <c r="O35">
-        <v>19.49806978</v>
+        <v>19.07046343999999</v>
       </c>
       <c r="P35">
-        <v>36.21070102</v>
+        <v>35.41657495999999</v>
       </c>
       <c r="Q35">
-        <v>50.41070102</v>
+        <v>49.61657495999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1037671562823479</v>
+        <v>0.1044125928683926</v>
       </c>
       <c r="T35">
-        <v>1.061688824535632</v>
+        <v>1.073510222277006</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.35</v>
       </c>
       <c r="W35">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.505630061644318</v>
+        <v>4.183963107823486</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08168611129313907</v>
+        <v>0.08145012787710505</v>
       </c>
       <c r="C36">
-        <v>737.0771739808455</v>
+        <v>735.1100619131371</v>
       </c>
       <c r="D36">
-        <v>1018.349173980845</v>
+        <v>1025.090061913137</v>
       </c>
       <c r="E36">
-        <v>237.672</v>
+        <v>246.38</v>
       </c>
       <c r="F36">
-        <v>296.072</v>
+        <v>304.78</v>
       </c>
       <c r="G36">
         <v>14.8</v>
@@ -4239,28 +4239,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M36">
-        <v>17.1129616</v>
+        <v>17.616284</v>
       </c>
       <c r="N36">
-        <v>54.48703839999999</v>
+        <v>53.98371599999999</v>
       </c>
       <c r="O36">
-        <v>19.07046343999999</v>
+        <v>18.89430059999999</v>
       </c>
       <c r="P36">
-        <v>35.41657495999999</v>
+        <v>35.08941539999999</v>
       </c>
       <c r="Q36">
-        <v>49.61657495999999</v>
+        <v>49.2894154</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1044125928683926</v>
+        <v>0.1050778890417001</v>
       </c>
       <c r="T36">
-        <v>1.073510222277006</v>
+        <v>1.085695355333499</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.183963107823486</v>
+        <v>4.064421304742815</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08145012787710505</v>
+        <v>0.082033144461071</v>
       </c>
       <c r="C37">
-        <v>735.1100619131371</v>
+        <v>709.9076473365562</v>
       </c>
       <c r="D37">
-        <v>1025.090061913137</v>
+        <v>1008.595647336556</v>
       </c>
       <c r="E37">
-        <v>246.38</v>
+        <v>255.088</v>
       </c>
       <c r="F37">
-        <v>304.78</v>
+        <v>313.488</v>
       </c>
       <c r="G37">
         <v>14.8</v>
@@ -4321,45 +4321,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M37">
-        <v>17.616284</v>
+        <v>19.2168144</v>
       </c>
       <c r="N37">
-        <v>53.98371599999999</v>
+        <v>52.38318559999999</v>
       </c>
       <c r="O37">
-        <v>18.89430059999999</v>
+        <v>18.33411495999999</v>
       </c>
       <c r="P37">
-        <v>35.08941539999999</v>
+        <v>34.04907064</v>
       </c>
       <c r="Q37">
-        <v>49.2894154</v>
+        <v>48.24907064</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1050778890417001</v>
+        <v>0.1057639757204235</v>
       </c>
       <c r="T37">
-        <v>1.085695355333499</v>
+        <v>1.098261273798007</v>
       </c>
       <c r="U37">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.064421304742815</v>
+        <v>3.725903706495703</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08203314446107102</v>
+        <v>0.08181991104503697</v>
       </c>
       <c r="C38">
-        <v>709.9076473365558</v>
+        <v>707.1704087581968</v>
       </c>
       <c r="D38">
-        <v>1008.595647336556</v>
+        <v>1014.566408758197</v>
       </c>
       <c r="E38">
-        <v>255.088</v>
+        <v>263.796</v>
       </c>
       <c r="F38">
-        <v>313.488</v>
+        <v>322.196</v>
       </c>
       <c r="G38">
         <v>14.8</v>
@@ -4403,28 +4403,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M38">
-        <v>19.2168144</v>
+        <v>19.7506148</v>
       </c>
       <c r="N38">
-        <v>52.38318559999999</v>
+        <v>51.8493852</v>
       </c>
       <c r="O38">
-        <v>18.33411495999999</v>
+        <v>18.14728482</v>
       </c>
       <c r="P38">
-        <v>34.04907064</v>
+        <v>33.70210038</v>
       </c>
       <c r="Q38">
-        <v>48.24907064</v>
+        <v>47.90210038000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1057639757204235</v>
+        <v>0.1064718429286301</v>
       </c>
       <c r="T38">
-        <v>1.098261273798007</v>
+        <v>1.111226110309007</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.725903706495703</v>
+        <v>3.625203606320144</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08181991104503697</v>
+        <v>0.08160667762900294</v>
       </c>
       <c r="C39">
-        <v>707.1704087581968</v>
+        <v>704.5042834993949</v>
       </c>
       <c r="D39">
-        <v>1014.566408758197</v>
+        <v>1020.608283499395</v>
       </c>
       <c r="E39">
-        <v>263.796</v>
+        <v>272.504</v>
       </c>
       <c r="F39">
-        <v>322.196</v>
+        <v>330.904</v>
       </c>
       <c r="G39">
         <v>14.8</v>
@@ -4485,28 +4485,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M39">
-        <v>19.7506148</v>
+        <v>20.2844152</v>
       </c>
       <c r="N39">
-        <v>51.8493852</v>
+        <v>51.3155848</v>
       </c>
       <c r="O39">
-        <v>18.14728482</v>
+        <v>17.96045468</v>
       </c>
       <c r="P39">
-        <v>33.70210038</v>
+        <v>33.35513012</v>
       </c>
       <c r="Q39">
-        <v>47.90210038000001</v>
+        <v>47.55513012</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1064718429286301</v>
+        <v>0.107202544562908</v>
       </c>
       <c r="T39">
-        <v>1.111226110309007</v>
+        <v>1.12460916735262</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.625203606320144</v>
+        <v>3.529803511416981</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08160667762900294</v>
+        <v>0.08210324421296891</v>
       </c>
       <c r="C40">
-        <v>704.5042834993949</v>
+        <v>681.8360995022956</v>
       </c>
       <c r="D40">
-        <v>1020.608283499395</v>
+        <v>1006.648099502296</v>
       </c>
       <c r="E40">
-        <v>272.504</v>
+        <v>281.212</v>
       </c>
       <c r="F40">
-        <v>330.904</v>
+        <v>339.612</v>
       </c>
       <c r="G40">
         <v>14.8</v>
@@ -4567,45 +4567,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M40">
-        <v>20.2844152</v>
+        <v>21.7691292</v>
       </c>
       <c r="N40">
-        <v>51.3155848</v>
+        <v>49.8308708</v>
       </c>
       <c r="O40">
-        <v>17.96045468</v>
+        <v>17.44080478</v>
       </c>
       <c r="P40">
-        <v>33.35513012</v>
+        <v>32.39006602000001</v>
       </c>
       <c r="Q40">
-        <v>47.55513012</v>
+        <v>46.59006602000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.107202544562908</v>
+        <v>0.1079572036278179</v>
       </c>
       <c r="T40">
-        <v>1.12460916735262</v>
+        <v>1.138431013151762</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.35</v>
       </c>
       <c r="W40">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.529803511416981</v>
+        <v>3.289061282249177</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08210324421296891</v>
+        <v>0.08190821079693486</v>
       </c>
       <c r="C41">
-        <v>681.8360995022956</v>
+        <v>678.5653674603852</v>
       </c>
       <c r="D41">
-        <v>1006.648099502296</v>
+        <v>1012.085367460385</v>
       </c>
       <c r="E41">
-        <v>281.212</v>
+        <v>289.92</v>
       </c>
       <c r="F41">
-        <v>339.612</v>
+        <v>348.32</v>
       </c>
       <c r="G41">
         <v>14.8</v>
@@ -4649,28 +4649,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M41">
-        <v>21.7691292</v>
+        <v>22.327312</v>
       </c>
       <c r="N41">
-        <v>49.8308708</v>
+        <v>49.27268799999999</v>
       </c>
       <c r="O41">
-        <v>17.44080478</v>
+        <v>17.24544079999999</v>
       </c>
       <c r="P41">
-        <v>32.39006602000001</v>
+        <v>32.02724719999999</v>
       </c>
       <c r="Q41">
-        <v>46.59006602000001</v>
+        <v>46.22724719999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1079572036278179</v>
+        <v>0.1087370179948914</v>
       </c>
       <c r="T41">
-        <v>1.138431013151762</v>
+        <v>1.152713587144208</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.289061282249177</v>
+        <v>3.206834750192947</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08190821079693486</v>
+        <v>0.08171317738090082</v>
       </c>
       <c r="C42">
-        <v>678.5653674603852</v>
+        <v>675.3536916769899</v>
       </c>
       <c r="D42">
-        <v>1012.085367460385</v>
+        <v>1017.58169167699</v>
       </c>
       <c r="E42">
-        <v>289.92</v>
+        <v>298.628</v>
       </c>
       <c r="F42">
-        <v>348.32</v>
+        <v>357.028</v>
       </c>
       <c r="G42">
         <v>14.8</v>
@@ -4731,28 +4731,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M42">
-        <v>22.327312</v>
+        <v>22.8854948</v>
       </c>
       <c r="N42">
-        <v>49.27268799999999</v>
+        <v>48.71450519999999</v>
       </c>
       <c r="O42">
-        <v>17.24544079999999</v>
+        <v>17.05007681999999</v>
       </c>
       <c r="P42">
-        <v>32.02724719999999</v>
+        <v>31.66442838</v>
       </c>
       <c r="Q42">
-        <v>46.22724719999999</v>
+        <v>45.86442837999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1087370179948914</v>
+        <v>0.1095432667472895</v>
       </c>
       <c r="T42">
-        <v>1.152713587144208</v>
+        <v>1.167480316187246</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.206834750192947</v>
+        <v>3.128619268480924</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08171317738090082</v>
+        <v>0.0815181439648668</v>
       </c>
       <c r="C43">
-        <v>675.3536916769899</v>
+        <v>672.2020395548824</v>
       </c>
       <c r="D43">
-        <v>1017.58169167699</v>
+        <v>1023.138039554882</v>
       </c>
       <c r="E43">
-        <v>298.628</v>
+        <v>307.336</v>
       </c>
       <c r="F43">
-        <v>357.028</v>
+        <v>365.736</v>
       </c>
       <c r="G43">
         <v>14.8</v>
@@ -4813,28 +4813,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M43">
-        <v>22.8854948</v>
+        <v>23.4436776</v>
       </c>
       <c r="N43">
-        <v>48.71450519999999</v>
+        <v>48.15632239999999</v>
       </c>
       <c r="O43">
-        <v>17.05007681999999</v>
+        <v>16.85471284</v>
       </c>
       <c r="P43">
-        <v>31.66442838</v>
+        <v>31.30160956</v>
       </c>
       <c r="Q43">
-        <v>45.86442837999999</v>
+        <v>45.50160955999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1095432667472895</v>
+        <v>0.1103773171808048</v>
       </c>
       <c r="T43">
-        <v>1.167480316187246</v>
+        <v>1.182756242783492</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.128619268480924</v>
+        <v>3.054128333517093</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08151814396486681</v>
+        <v>0.08350321054883277</v>
       </c>
       <c r="C44">
-        <v>672.2020395548819</v>
+        <v>609.626023979012</v>
       </c>
       <c r="D44">
-        <v>1023.138039554882</v>
+        <v>969.270023979012</v>
       </c>
       <c r="E44">
-        <v>307.336</v>
+        <v>316.044</v>
       </c>
       <c r="F44">
-        <v>365.736</v>
+        <v>374.444</v>
       </c>
       <c r="G44">
         <v>14.8</v>
@@ -4895,45 +4895,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M44">
-        <v>23.4436776</v>
+        <v>26.9225236</v>
       </c>
       <c r="N44">
-        <v>48.15632239999999</v>
+        <v>44.6774764</v>
       </c>
       <c r="O44">
-        <v>16.85471284</v>
+        <v>15.63711674</v>
       </c>
       <c r="P44">
-        <v>31.30160956</v>
+        <v>29.04035966</v>
       </c>
       <c r="Q44">
-        <v>45.50160955999999</v>
+        <v>43.24035966</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1103773171808048</v>
+        <v>0.1112406325418119</v>
       </c>
       <c r="T44">
-        <v>1.182756242783492</v>
+        <v>1.198568166804168</v>
       </c>
       <c r="U44">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V44">
         <v>0.35</v>
       </c>
       <c r="W44">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.054128333517093</v>
+        <v>2.659483229127896</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08350321054883277</v>
+        <v>0.08335887713279871</v>
       </c>
       <c r="C45">
-        <v>609.626023979012</v>
+        <v>604.6427906467068</v>
       </c>
       <c r="D45">
-        <v>969.270023979012</v>
+        <v>972.9947906467067</v>
       </c>
       <c r="E45">
-        <v>316.044</v>
+        <v>324.752</v>
       </c>
       <c r="F45">
-        <v>374.444</v>
+        <v>383.152</v>
       </c>
       <c r="G45">
         <v>14.8</v>
@@ -4977,28 +4977,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M45">
-        <v>26.9225236</v>
+        <v>27.5486288</v>
       </c>
       <c r="N45">
-        <v>44.6774764</v>
+        <v>44.05137119999999</v>
       </c>
       <c r="O45">
-        <v>15.63711674</v>
+        <v>15.41797992</v>
       </c>
       <c r="P45">
-        <v>29.04035966</v>
+        <v>28.63339128</v>
       </c>
       <c r="Q45">
-        <v>43.24035966</v>
+        <v>42.83339128</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1112406325418119</v>
+        <v>0.1121347805942834</v>
       </c>
       <c r="T45">
-        <v>1.198568166804168</v>
+        <v>1.21494480239701</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.659483229127896</v>
+        <v>2.599040428465899</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08335887713279871</v>
+        <v>0.08321454371676469</v>
       </c>
       <c r="C46">
-        <v>604.6427906467068</v>
+        <v>599.6882952458934</v>
       </c>
       <c r="D46">
-        <v>972.9947906467067</v>
+        <v>976.7482952458935</v>
       </c>
       <c r="E46">
-        <v>324.752</v>
+        <v>333.46</v>
       </c>
       <c r="F46">
-        <v>383.152</v>
+        <v>391.86</v>
       </c>
       <c r="G46">
         <v>14.8</v>
@@ -5059,28 +5059,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M46">
-        <v>27.5486288</v>
+        <v>28.174734</v>
       </c>
       <c r="N46">
-        <v>44.05137119999999</v>
+        <v>43.42526599999999</v>
       </c>
       <c r="O46">
-        <v>15.41797992</v>
+        <v>15.1988431</v>
       </c>
       <c r="P46">
-        <v>28.63339128</v>
+        <v>28.2264229</v>
       </c>
       <c r="Q46">
-        <v>42.83339128</v>
+        <v>42.42642289999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1121347805942834</v>
+        <v>0.1130614431213903</v>
       </c>
       <c r="T46">
-        <v>1.21494480239701</v>
+        <v>1.231916952011411</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.599040428465899</v>
+        <v>2.54128397449999</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08321454371676469</v>
+        <v>0.08423631030073066</v>
       </c>
       <c r="C47">
-        <v>599.6882952458934</v>
+        <v>565.0150358019087</v>
       </c>
       <c r="D47">
-        <v>976.7482952458935</v>
+        <v>950.7830358019087</v>
       </c>
       <c r="E47">
-        <v>333.46</v>
+        <v>342.168</v>
       </c>
       <c r="F47">
-        <v>391.86</v>
+        <v>400.568</v>
       </c>
       <c r="G47">
         <v>14.8</v>
@@ -5141,45 +5141,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M47">
-        <v>28.174734</v>
+        <v>30.3630544</v>
       </c>
       <c r="N47">
-        <v>43.42526599999999</v>
+        <v>41.23694559999999</v>
       </c>
       <c r="O47">
-        <v>15.1988431</v>
+        <v>14.43293096</v>
       </c>
       <c r="P47">
-        <v>28.2264229</v>
+        <v>26.80401463999999</v>
       </c>
       <c r="Q47">
-        <v>42.42642289999999</v>
+        <v>41.00401463999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1130614431213903</v>
+        <v>0.1140224264828345</v>
       </c>
       <c r="T47">
-        <v>1.231916952011411</v>
+        <v>1.249517699759678</v>
       </c>
       <c r="U47">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.54128397449999</v>
+        <v>2.358129029337707</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08423631030073066</v>
+        <v>0.08411732688469661</v>
       </c>
       <c r="C48">
-        <v>565.0150358019087</v>
+        <v>559.2594185150178</v>
       </c>
       <c r="D48">
-        <v>950.7830358019087</v>
+        <v>953.7354185150178</v>
       </c>
       <c r="E48">
-        <v>342.168</v>
+        <v>350.876</v>
       </c>
       <c r="F48">
-        <v>400.568</v>
+        <v>409.276</v>
       </c>
       <c r="G48">
         <v>14.8</v>
@@ -5223,28 +5223,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M48">
-        <v>30.3630544</v>
+        <v>31.0231208</v>
       </c>
       <c r="N48">
-        <v>41.23694559999999</v>
+        <v>40.57687919999999</v>
       </c>
       <c r="O48">
-        <v>14.43293096</v>
+        <v>14.20190772</v>
       </c>
       <c r="P48">
-        <v>26.80401463999999</v>
+        <v>26.37497148</v>
       </c>
       <c r="Q48">
-        <v>41.00401463999999</v>
+        <v>40.57497148</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1140224264828345</v>
+        <v>0.1150196733673521</v>
       </c>
       <c r="T48">
-        <v>1.249517699759678</v>
+        <v>1.267782626668257</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.358129029337707</v>
+        <v>2.307956071266692</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08411732688469661</v>
+        <v>0.08399834346866257</v>
       </c>
       <c r="C49">
-        <v>559.2594185150178</v>
+        <v>553.52219388858</v>
       </c>
       <c r="D49">
-        <v>953.7354185150178</v>
+        <v>956.7061938885801</v>
       </c>
       <c r="E49">
-        <v>350.876</v>
+        <v>359.5840000000001</v>
       </c>
       <c r="F49">
-        <v>409.276</v>
+        <v>417.984</v>
       </c>
       <c r="G49">
         <v>14.8</v>
@@ -5305,28 +5305,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M49">
-        <v>31.0231208</v>
+        <v>31.68318720000001</v>
       </c>
       <c r="N49">
-        <v>40.57687919999999</v>
+        <v>39.91681279999999</v>
       </c>
       <c r="O49">
-        <v>14.20190772</v>
+        <v>13.97088448</v>
       </c>
       <c r="P49">
-        <v>26.37497148</v>
+        <v>25.94592831999999</v>
       </c>
       <c r="Q49">
-        <v>40.57497148</v>
+        <v>40.14592832</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1150196733673521</v>
+        <v>0.1160552759012742</v>
       </c>
       <c r="T49">
-        <v>1.267782626668257</v>
+        <v>1.286750050765628</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.307956071266692</v>
+        <v>2.259873653115302</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08399834346866257</v>
+        <v>0.08387936005262853</v>
       </c>
       <c r="C50">
-        <v>553.52219388858</v>
+        <v>547.8035343326544</v>
       </c>
       <c r="D50">
-        <v>956.7061938885801</v>
+        <v>959.6955343326545</v>
       </c>
       <c r="E50">
-        <v>359.584</v>
+        <v>368.292</v>
       </c>
       <c r="F50">
-        <v>417.984</v>
+        <v>426.692</v>
       </c>
       <c r="G50">
         <v>14.8</v>
@@ -5387,28 +5387,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M50">
-        <v>31.6831872</v>
+        <v>32.3432536</v>
       </c>
       <c r="N50">
-        <v>39.91681279999999</v>
+        <v>39.2567464</v>
       </c>
       <c r="O50">
-        <v>13.97088448</v>
+        <v>13.73986124</v>
       </c>
       <c r="P50">
-        <v>25.94592831999999</v>
+        <v>25.51688516</v>
       </c>
       <c r="Q50">
-        <v>40.14592832</v>
+        <v>39.71688516</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1160552759012742</v>
+        <v>0.1171314902992716</v>
       </c>
       <c r="T50">
-        <v>1.286750050765628</v>
+        <v>1.306461295415837</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.259873653115302</v>
+        <v>2.213753782643562</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08387936005262853</v>
+        <v>0.0837603766365945</v>
       </c>
       <c r="C51">
-        <v>547.8035343326544</v>
+        <v>542.1036144189152</v>
       </c>
       <c r="D51">
-        <v>959.6955343326545</v>
+        <v>962.7036144189152</v>
       </c>
       <c r="E51">
-        <v>368.292</v>
+        <v>377</v>
       </c>
       <c r="F51">
-        <v>426.692</v>
+        <v>435.4</v>
       </c>
       <c r="G51">
         <v>14.8</v>
@@ -5469,28 +5469,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M51">
-        <v>32.3432536</v>
+        <v>33.00332</v>
       </c>
       <c r="N51">
-        <v>39.2567464</v>
+        <v>38.59667999999999</v>
       </c>
       <c r="O51">
-        <v>13.73986124</v>
+        <v>13.508838</v>
       </c>
       <c r="P51">
-        <v>25.51688516</v>
+        <v>25.08784199999999</v>
       </c>
       <c r="Q51">
-        <v>39.71688516</v>
+        <v>39.287842</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1171314902992716</v>
+        <v>0.118250753273189</v>
       </c>
       <c r="T51">
-        <v>1.306461295415837</v>
+        <v>1.326960989852054</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.213753782643562</v>
+        <v>2.16947870699069</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0837603766365945</v>
+        <v>0.08364139322056045</v>
       </c>
       <c r="C52">
-        <v>542.1036144189152</v>
+        <v>536.4226109146373</v>
       </c>
       <c r="D52">
-        <v>962.7036144189152</v>
+        <v>965.7306109146374</v>
       </c>
       <c r="E52">
-        <v>377</v>
+        <v>385.708</v>
       </c>
       <c r="F52">
-        <v>435.4</v>
+        <v>444.108</v>
       </c>
       <c r="G52">
         <v>14.8</v>
@@ -5551,28 +5551,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M52">
-        <v>33.00332</v>
+        <v>33.6633864</v>
       </c>
       <c r="N52">
-        <v>38.59667999999999</v>
+        <v>37.93661359999999</v>
       </c>
       <c r="O52">
-        <v>13.508838</v>
+        <v>13.27781476</v>
       </c>
       <c r="P52">
-        <v>25.08784199999999</v>
+        <v>24.65879884</v>
       </c>
       <c r="Q52">
-        <v>39.287842</v>
+        <v>38.85879883999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.118250753273189</v>
+        <v>0.1194157004501234</v>
       </c>
       <c r="T52">
-        <v>1.326960989852054</v>
+        <v>1.348297406510157</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.16947870699069</v>
+        <v>2.126939908814403</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08364139322056045</v>
+        <v>0.08352240980452642</v>
       </c>
       <c r="C53">
-        <v>536.4226109146373</v>
+        <v>530.7607028173202</v>
       </c>
       <c r="D53">
-        <v>965.7306109146374</v>
+        <v>968.7767028173203</v>
       </c>
       <c r="E53">
-        <v>385.708</v>
+        <v>394.416</v>
       </c>
       <c r="F53">
-        <v>444.108</v>
+        <v>452.816</v>
       </c>
       <c r="G53">
         <v>14.8</v>
@@ -5633,28 +5633,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M53">
-        <v>33.6633864</v>
+        <v>34.3234528</v>
       </c>
       <c r="N53">
-        <v>37.93661359999999</v>
+        <v>37.2765472</v>
       </c>
       <c r="O53">
-        <v>13.27781476</v>
+        <v>13.04679152</v>
       </c>
       <c r="P53">
-        <v>24.65879884</v>
+        <v>24.22975568</v>
       </c>
       <c r="Q53">
-        <v>38.85879883999999</v>
+        <v>38.42975568</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1194157004501234</v>
+        <v>0.1206291870927634</v>
       </c>
       <c r="T53">
-        <v>1.348297406510157</v>
+        <v>1.370522840529015</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.126939908814403</v>
+        <v>2.086037218260279</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08352240980452642</v>
+        <v>0.08340342638849239</v>
       </c>
       <c r="C54">
-        <v>530.7607028173202</v>
+        <v>525.1180713899743</v>
       </c>
       <c r="D54">
-        <v>968.7767028173203</v>
+        <v>971.8420713899743</v>
       </c>
       <c r="E54">
-        <v>394.416</v>
+        <v>403.124</v>
       </c>
       <c r="F54">
-        <v>452.816</v>
+        <v>461.524</v>
       </c>
       <c r="G54">
         <v>14.8</v>
@@ -5715,28 +5715,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M54">
-        <v>34.3234528</v>
+        <v>34.9835192</v>
       </c>
       <c r="N54">
-        <v>37.2765472</v>
+        <v>36.61648079999999</v>
       </c>
       <c r="O54">
-        <v>13.04679152</v>
+        <v>12.81576828</v>
       </c>
       <c r="P54">
-        <v>24.22975568</v>
+        <v>23.80071251999999</v>
       </c>
       <c r="Q54">
-        <v>38.42975568</v>
+        <v>38.00071251999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1206291870927634</v>
+        <v>0.1218943114648774</v>
       </c>
       <c r="T54">
-        <v>1.370522840529015</v>
+        <v>1.393694037697612</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.086037218260279</v>
+        <v>2.046678025462915</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08340342638849239</v>
+        <v>0.08328444297245835</v>
       </c>
       <c r="C55">
-        <v>525.1180713899743</v>
+        <v>519.4949001970754</v>
       </c>
       <c r="D55">
-        <v>971.8420713899743</v>
+        <v>974.9269001970755</v>
       </c>
       <c r="E55">
-        <v>403.124</v>
+        <v>411.8320000000001</v>
       </c>
       <c r="F55">
-        <v>461.524</v>
+        <v>470.232</v>
       </c>
       <c r="G55">
         <v>14.8</v>
@@ -5797,28 +5797,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M55">
-        <v>34.9835192</v>
+        <v>35.6435856</v>
       </c>
       <c r="N55">
-        <v>36.61648079999999</v>
+        <v>35.95641439999999</v>
       </c>
       <c r="O55">
-        <v>12.81576828</v>
+        <v>12.58474504</v>
       </c>
       <c r="P55">
-        <v>23.80071251999999</v>
+        <v>23.37166936</v>
       </c>
       <c r="Q55">
-        <v>38.00071251999999</v>
+        <v>37.57166936</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1218943114648774</v>
+        <v>0.1232144412444747</v>
       </c>
       <c r="T55">
-        <v>1.393694037697612</v>
+        <v>1.417872678221365</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.046678025462915</v>
+        <v>2.008776580546936</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08328444297245835</v>
+        <v>0.0882419595564243</v>
       </c>
       <c r="C56">
-        <v>519.4949001970754</v>
+        <v>396.9086456019731</v>
       </c>
       <c r="D56">
-        <v>974.9269001970755</v>
+        <v>861.0486456019731</v>
       </c>
       <c r="E56">
-        <v>411.8320000000001</v>
+        <v>420.54</v>
       </c>
       <c r="F56">
-        <v>470.232</v>
+        <v>478.94</v>
       </c>
       <c r="G56">
         <v>14.8</v>
@@ -5879,45 +5879,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M56">
-        <v>35.6435856</v>
+        <v>43.1046</v>
       </c>
       <c r="N56">
-        <v>35.95641439999999</v>
+        <v>28.4954</v>
       </c>
       <c r="O56">
-        <v>12.58474504</v>
+        <v>9.973389999999998</v>
       </c>
       <c r="P56">
-        <v>23.37166936</v>
+        <v>18.52201</v>
       </c>
       <c r="Q56">
-        <v>37.57166936</v>
+        <v>32.72201</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1232144412444747</v>
+        <v>0.1245932434587207</v>
       </c>
       <c r="T56">
-        <v>1.417872678221365</v>
+        <v>1.443125924990618</v>
       </c>
       <c r="U56">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V56">
         <v>0.35</v>
       </c>
       <c r="W56">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.008776580546936</v>
+        <v>1.661075616059539</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0882419595564243</v>
+        <v>0.08821527614039026</v>
       </c>
       <c r="C57">
-        <v>396.9086456019731</v>
+        <v>388.742330610933</v>
       </c>
       <c r="D57">
-        <v>861.0486456019731</v>
+        <v>861.5903306109331</v>
       </c>
       <c r="E57">
-        <v>420.54</v>
+        <v>429.248</v>
       </c>
       <c r="F57">
-        <v>478.94</v>
+        <v>487.648</v>
       </c>
       <c r="G57">
         <v>14.8</v>
@@ -5961,28 +5961,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M57">
-        <v>43.1046</v>
+        <v>43.88832</v>
       </c>
       <c r="N57">
-        <v>28.4954</v>
+        <v>27.71167999999999</v>
       </c>
       <c r="O57">
-        <v>9.973389999999998</v>
+        <v>9.699087999999998</v>
       </c>
       <c r="P57">
-        <v>18.52201</v>
+        <v>18.012592</v>
       </c>
       <c r="Q57">
-        <v>32.72201</v>
+        <v>32.212592</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1245932434587207</v>
+        <v>0.126034718500887</v>
       </c>
       <c r="T57">
-        <v>1.443125924990618</v>
+        <v>1.469527046613018</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.661075616059539</v>
+        <v>1.631413551487047</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08821527614039026</v>
+        <v>0.08818859272435622</v>
       </c>
       <c r="C58">
-        <v>388.742330610933</v>
+        <v>380.5766975961288</v>
       </c>
       <c r="D58">
-        <v>861.5903306109331</v>
+        <v>862.1326975961289</v>
       </c>
       <c r="E58">
-        <v>429.248</v>
+        <v>437.9560000000001</v>
       </c>
       <c r="F58">
-        <v>487.648</v>
+        <v>496.3560000000001</v>
       </c>
       <c r="G58">
         <v>14.8</v>
@@ -6043,28 +6043,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M58">
-        <v>43.88832</v>
+        <v>44.67204</v>
       </c>
       <c r="N58">
-        <v>27.71167999999999</v>
+        <v>26.92795999999999</v>
       </c>
       <c r="O58">
-        <v>9.699087999999998</v>
+        <v>9.424785999999996</v>
       </c>
       <c r="P58">
-        <v>18.012592</v>
+        <v>17.50317399999999</v>
       </c>
       <c r="Q58">
-        <v>32.212592</v>
+        <v>31.70317399999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.126034718500887</v>
+        <v>0.1275432388938517</v>
       </c>
       <c r="T58">
-        <v>1.469527046613018</v>
+        <v>1.497156127380647</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.631413551487047</v>
+        <v>1.602792261110081</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08818859272435622</v>
+        <v>0.0881619093083222</v>
       </c>
       <c r="C59">
-        <v>380.5766975961288</v>
+        <v>372.4117478462735</v>
       </c>
       <c r="D59">
-        <v>862.1326975961289</v>
+        <v>862.6757478462736</v>
       </c>
       <c r="E59">
-        <v>437.9560000000001</v>
+        <v>446.664</v>
       </c>
       <c r="F59">
-        <v>496.3560000000001</v>
+        <v>505.064</v>
       </c>
       <c r="G59">
         <v>14.8</v>
@@ -6125,28 +6125,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M59">
-        <v>44.67204</v>
+        <v>45.45576</v>
       </c>
       <c r="N59">
-        <v>26.92795999999999</v>
+        <v>26.14424</v>
       </c>
       <c r="O59">
-        <v>9.424785999999996</v>
+        <v>9.150483999999999</v>
       </c>
       <c r="P59">
-        <v>17.50317399999999</v>
+        <v>16.993756</v>
       </c>
       <c r="Q59">
-        <v>31.70317399999999</v>
+        <v>31.193756</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1275432388938517</v>
+        <v>0.1291235935912433</v>
       </c>
       <c r="T59">
-        <v>1.497156127380647</v>
+        <v>1.52610087866102</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.602792261110081</v>
+        <v>1.575157911780597</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08816190930832218</v>
+        <v>0.08813522589228814</v>
       </c>
       <c r="C60">
-        <v>372.4117478462739</v>
+        <v>364.2474826533308</v>
       </c>
       <c r="D60">
-        <v>862.6757478462739</v>
+        <v>863.2194826533308</v>
       </c>
       <c r="E60">
-        <v>446.664</v>
+        <v>455.372</v>
       </c>
       <c r="F60">
-        <v>505.064</v>
+        <v>513.7719999999999</v>
       </c>
       <c r="G60">
         <v>14.8</v>
@@ -6207,28 +6207,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M60">
-        <v>45.45576</v>
+        <v>46.23947999999999</v>
       </c>
       <c r="N60">
-        <v>26.14424</v>
+        <v>25.36052</v>
       </c>
       <c r="O60">
-        <v>9.150483999999999</v>
+        <v>8.876182</v>
       </c>
       <c r="P60">
-        <v>16.993756</v>
+        <v>16.484338</v>
       </c>
       <c r="Q60">
-        <v>31.193756</v>
+        <v>30.684338</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1291235935912433</v>
+        <v>0.1307810387616784</v>
       </c>
       <c r="T60">
-        <v>1.52610087866102</v>
+        <v>1.55645756902824</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.575157911780597</v>
+        <v>1.548460320055502</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08813522589228814</v>
+        <v>0.08810854247625412</v>
       </c>
       <c r="C61">
-        <v>364.2474826533308</v>
+        <v>356.0839033125216</v>
       </c>
       <c r="D61">
-        <v>863.2194826533308</v>
+        <v>863.7639033125215</v>
       </c>
       <c r="E61">
-        <v>455.372</v>
+        <v>464.0799999999999</v>
       </c>
       <c r="F61">
-        <v>513.7719999999999</v>
+        <v>522.4799999999999</v>
       </c>
       <c r="G61">
         <v>14.8</v>
@@ -6289,28 +6289,28 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M61">
-        <v>46.23947999999999</v>
+        <v>47.02319999999999</v>
       </c>
       <c r="N61">
-        <v>25.36052</v>
+        <v>24.57680000000001</v>
       </c>
       <c r="O61">
-        <v>8.876182</v>
+        <v>8.601880000000001</v>
       </c>
       <c r="P61">
-        <v>16.484338</v>
+        <v>15.97492</v>
       </c>
       <c r="Q61">
-        <v>30.684338</v>
+        <v>30.17492</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1307810387616784</v>
+        <v>0.1325213561906353</v>
       </c>
       <c r="T61">
-        <v>1.55645756902824</v>
+        <v>1.588332093913822</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.548460320055502</v>
+        <v>1.522652648054577</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08810854247625412</v>
+        <v>0.1139335453186342</v>
       </c>
       <c r="C62">
-        <v>356.0839033125216</v>
+        <v>19.97909526633271</v>
       </c>
       <c r="D62">
-        <v>863.7639033125215</v>
+        <v>536.3670952663327</v>
       </c>
       <c r="E62">
-        <v>464.0799999999999</v>
+        <v>472.788</v>
       </c>
       <c r="F62">
-        <v>522.4799999999999</v>
+        <v>531.188</v>
       </c>
       <c r="G62">
         <v>14.8</v>
@@ -6371,45 +6371,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M62">
-        <v>47.02319999999999</v>
+        <v>77.9783984</v>
       </c>
       <c r="N62">
-        <v>24.57680000000001</v>
+        <v>-6.378398400000009</v>
       </c>
       <c r="O62">
-        <v>8.601880000000001</v>
+        <v>-2.232439440000003</v>
       </c>
       <c r="P62">
-        <v>15.97492</v>
+        <v>-4.145958960000006</v>
       </c>
       <c r="Q62">
-        <v>30.17492</v>
+        <v>10.05404103999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1325213561906353</v>
+        <v>0.1363171291458095</v>
       </c>
       <c r="T62">
-        <v>1.588332093913822</v>
+        <v>1.657853008608239</v>
       </c>
       <c r="U62">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.35</v>
+        <v>0.3213710529350907</v>
       </c>
       <c r="W62">
-        <v>0.0585</v>
+        <v>0.0996227294291287</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.522652648054577</v>
+        <v>0.9182030083859736</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1139335453186342</v>
+        <v>0.1149435453186342</v>
       </c>
       <c r="C63">
-        <v>19.97909526633271</v>
+        <v>3.436224148247447</v>
       </c>
       <c r="D63">
-        <v>536.3670952663327</v>
+        <v>528.5322241482475</v>
       </c>
       <c r="E63">
-        <v>472.788</v>
+        <v>481.496</v>
       </c>
       <c r="F63">
-        <v>531.188</v>
+        <v>539.896</v>
       </c>
       <c r="G63">
         <v>14.8</v>
@@ -6453,37 +6453,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M63">
-        <v>77.9783984</v>
+        <v>79.25673279999999</v>
       </c>
       <c r="N63">
-        <v>-6.378398400000009</v>
+        <v>-7.6567328</v>
       </c>
       <c r="O63">
-        <v>-2.232439440000003</v>
+        <v>-2.67985648</v>
       </c>
       <c r="P63">
-        <v>-4.145958960000006</v>
+        <v>-4.976876320000001</v>
       </c>
       <c r="Q63">
-        <v>10.05404103999999</v>
+        <v>9.223123679999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1363171291458095</v>
+        <v>0.1386991588601729</v>
       </c>
       <c r="T63">
-        <v>1.657853008608239</v>
+        <v>1.701480719361087</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.3213710529350907</v>
+        <v>0.3161876488554926</v>
       </c>
       <c r="W63">
-        <v>0.0996227294291287</v>
+        <v>0.1003836531480137</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.9182030083859736</v>
+        <v>0.9033932824442644</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1149435453186342</v>
+        <v>0.1159535453186342</v>
       </c>
       <c r="C64">
-        <v>3.436224148247447</v>
+        <v>-12.88104982308448</v>
       </c>
       <c r="D64">
-        <v>528.5322241482475</v>
+        <v>520.9229501769155</v>
       </c>
       <c r="E64">
-        <v>481.496</v>
+        <v>490.204</v>
       </c>
       <c r="F64">
-        <v>539.896</v>
+        <v>548.6039999999999</v>
       </c>
       <c r="G64">
         <v>14.8</v>
@@ -6535,37 +6535,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M64">
-        <v>79.25673279999999</v>
+        <v>80.5350672</v>
       </c>
       <c r="N64">
-        <v>-7.6567328</v>
+        <v>-8.935067200000006</v>
       </c>
       <c r="O64">
-        <v>-2.67985648</v>
+        <v>-3.127273520000002</v>
       </c>
       <c r="P64">
-        <v>-4.976876320000001</v>
+        <v>-5.807793680000004</v>
       </c>
       <c r="Q64">
-        <v>9.223123679999999</v>
+        <v>8.392206319999996</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1386991588601729</v>
+        <v>0.1412099469374749</v>
       </c>
       <c r="T64">
-        <v>1.701480719361087</v>
+        <v>1.747466684749225</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.3161876488554926</v>
+        <v>0.3111687972863577</v>
       </c>
       <c r="W64">
-        <v>0.1003836531480137</v>
+        <v>0.1011204205583627</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9033932824442644</v>
+        <v>0.8890537065324506</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1159535453186342</v>
+        <v>0.1169635453186342</v>
       </c>
       <c r="C65">
-        <v>-12.88104982308448</v>
+        <v>-28.98233211843569</v>
       </c>
       <c r="D65">
-        <v>520.9229501769155</v>
+        <v>513.5296678815644</v>
       </c>
       <c r="E65">
-        <v>490.204</v>
+        <v>498.912</v>
       </c>
       <c r="F65">
-        <v>548.6039999999999</v>
+        <v>557.312</v>
       </c>
       <c r="G65">
         <v>14.8</v>
@@ -6617,37 +6617,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M65">
-        <v>80.5350672</v>
+        <v>81.81340160000001</v>
       </c>
       <c r="N65">
-        <v>-8.935067200000006</v>
+        <v>-10.21340160000001</v>
       </c>
       <c r="O65">
-        <v>-3.127273520000002</v>
+        <v>-3.574690560000004</v>
       </c>
       <c r="P65">
-        <v>-5.807793680000004</v>
+        <v>-6.638711040000008</v>
       </c>
       <c r="Q65">
-        <v>8.392206319999996</v>
+        <v>7.561288959999992</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1412099469374749</v>
+        <v>0.1438602232412936</v>
       </c>
       <c r="T65">
-        <v>1.747466684749225</v>
+        <v>1.796007425992258</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.3111687972863577</v>
+        <v>0.3063067848287583</v>
       </c>
       <c r="W65">
-        <v>0.1011204205583627</v>
+        <v>0.1018341639871383</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8890537065324506</v>
+        <v>0.8751622423678811</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1169635453186342</v>
+        <v>0.1179735453186342</v>
       </c>
       <c r="C66">
-        <v>-28.98233211843569</v>
+        <v>-44.87669053093396</v>
       </c>
       <c r="D66">
-        <v>513.5296678815644</v>
+        <v>506.343309469066</v>
       </c>
       <c r="E66">
-        <v>498.912</v>
+        <v>507.62</v>
       </c>
       <c r="F66">
-        <v>557.312</v>
+        <v>566.02</v>
       </c>
       <c r="G66">
         <v>14.8</v>
@@ -6699,37 +6699,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M66">
-        <v>81.81340160000001</v>
+        <v>83.09173600000001</v>
       </c>
       <c r="N66">
-        <v>-10.21340160000001</v>
+        <v>-11.49173600000002</v>
       </c>
       <c r="O66">
-        <v>-3.574690560000004</v>
+        <v>-4.022107600000006</v>
       </c>
       <c r="P66">
-        <v>-6.638711040000008</v>
+        <v>-7.469628400000011</v>
       </c>
       <c r="Q66">
-        <v>7.561288959999992</v>
+        <v>6.730371599999988</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1438602232412936</v>
+        <v>0.1466619439053306</v>
       </c>
       <c r="T66">
-        <v>1.796007425992258</v>
+        <v>1.847321923877752</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.3063067848287583</v>
+        <v>0.3015943727544697</v>
       </c>
       <c r="W66">
-        <v>0.1018341639871383</v>
+        <v>0.1025259460796439</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8751622423678811</v>
+        <v>0.8616982078699136</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1179735453186342</v>
+        <v>0.1189835453186342</v>
       </c>
       <c r="C67">
-        <v>-44.87669053093396</v>
+        <v>-60.57269227828215</v>
       </c>
       <c r="D67">
-        <v>506.343309469066</v>
+        <v>499.3553077217178</v>
       </c>
       <c r="E67">
-        <v>507.62</v>
+        <v>516.328</v>
       </c>
       <c r="F67">
-        <v>566.02</v>
+        <v>574.728</v>
       </c>
       <c r="G67">
         <v>14.8</v>
@@ -6781,37 +6781,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M67">
-        <v>83.09173600000001</v>
+        <v>84.3700704</v>
       </c>
       <c r="N67">
-        <v>-11.49173600000002</v>
+        <v>-12.77007040000001</v>
       </c>
       <c r="O67">
-        <v>-4.022107600000006</v>
+        <v>-4.469524640000003</v>
       </c>
       <c r="P67">
-        <v>-7.469628400000011</v>
+        <v>-8.300545760000006</v>
       </c>
       <c r="Q67">
-        <v>6.730371599999988</v>
+        <v>5.899454239999994</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1466619439053306</v>
+        <v>0.149628471667252</v>
       </c>
       <c r="T67">
-        <v>1.847321923877752</v>
+        <v>1.901654921638862</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.3015943727544697</v>
+        <v>0.2970247610460687</v>
       </c>
       <c r="W67">
-        <v>0.1025259460796439</v>
+        <v>0.1031967650784371</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8616982078699136</v>
+        <v>0.8486421744173392</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1189835453186342</v>
+        <v>0.1199935453186342</v>
       </c>
       <c r="C68">
-        <v>-60.57269227828215</v>
+        <v>-76.07843807453634</v>
       </c>
       <c r="D68">
-        <v>499.3553077217178</v>
+        <v>492.5575619254637</v>
       </c>
       <c r="E68">
-        <v>516.328</v>
+        <v>525.0360000000001</v>
       </c>
       <c r="F68">
-        <v>574.728</v>
+        <v>583.436</v>
       </c>
       <c r="G68">
         <v>14.8</v>
@@ -6863,37 +6863,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M68">
-        <v>84.3700704</v>
+        <v>85.64840480000001</v>
       </c>
       <c r="N68">
-        <v>-12.77007040000001</v>
+        <v>-14.04840480000001</v>
       </c>
       <c r="O68">
-        <v>-4.469524640000003</v>
+        <v>-4.916941680000004</v>
       </c>
       <c r="P68">
-        <v>-8.300545760000006</v>
+        <v>-9.13146312000001</v>
       </c>
       <c r="Q68">
-        <v>5.899454239999994</v>
+        <v>5.068536879999989</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.149628471667252</v>
+        <v>0.1527747889905021</v>
       </c>
       <c r="T68">
-        <v>1.901654921638862</v>
+        <v>1.959280828355191</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2970247610460687</v>
+        <v>0.2925915556573214</v>
       </c>
       <c r="W68">
-        <v>0.1031967650784371</v>
+        <v>0.1038475596295052</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8486421744173392</v>
+        <v>0.8359758733066327</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1199935453186342</v>
+        <v>0.1210035453186342</v>
       </c>
       <c r="C69">
-        <v>-76.07843807453634</v>
+        <v>-91.40159345633248</v>
       </c>
       <c r="D69">
-        <v>492.5575619254637</v>
+        <v>485.9424065436675</v>
       </c>
       <c r="E69">
-        <v>525.0360000000001</v>
+        <v>533.744</v>
       </c>
       <c r="F69">
-        <v>583.436</v>
+        <v>592.144</v>
       </c>
       <c r="G69">
         <v>14.8</v>
@@ -6945,37 +6945,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M69">
-        <v>85.64840480000001</v>
+        <v>86.92673920000001</v>
       </c>
       <c r="N69">
-        <v>-14.04840480000001</v>
+        <v>-15.32673920000002</v>
       </c>
       <c r="O69">
-        <v>-4.916941680000004</v>
+        <v>-5.364358720000006</v>
       </c>
       <c r="P69">
-        <v>-9.13146312000001</v>
+        <v>-9.962380480000014</v>
       </c>
       <c r="Q69">
-        <v>5.068536879999989</v>
+        <v>4.237619519999985</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1527747889905021</v>
+        <v>0.1561177511464553</v>
       </c>
       <c r="T69">
-        <v>1.959280828355191</v>
+        <v>2.020508354241291</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2925915556573214</v>
+        <v>0.2882887386623608</v>
       </c>
       <c r="W69">
-        <v>0.1038475596295052</v>
+        <v>0.1044792131643655</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8359758733066327</v>
+        <v>0.823682110463888</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1210035453186342</v>
+        <v>0.1220135453186342</v>
       </c>
       <c r="C70">
-        <v>-91.40159345633248</v>
+        <v>-106.5494176182601</v>
       </c>
       <c r="D70">
-        <v>485.9424065436675</v>
+        <v>479.5025823817399</v>
       </c>
       <c r="E70">
-        <v>533.744</v>
+        <v>542.452</v>
       </c>
       <c r="F70">
-        <v>592.144</v>
+        <v>600.852</v>
       </c>
       <c r="G70">
         <v>14.8</v>
@@ -7027,37 +7027,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M70">
-        <v>86.92673920000001</v>
+        <v>88.20507360000001</v>
       </c>
       <c r="N70">
-        <v>-15.32673920000002</v>
+        <v>-16.60507360000001</v>
       </c>
       <c r="O70">
-        <v>-5.364358720000006</v>
+        <v>-5.811775760000003</v>
       </c>
       <c r="P70">
-        <v>-9.962380480000014</v>
+        <v>-10.79329784000001</v>
       </c>
       <c r="Q70">
-        <v>4.237619519999985</v>
+        <v>3.406702159999991</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1561177511464553</v>
+        <v>0.1596763882802119</v>
       </c>
       <c r="T70">
-        <v>2.020508354241291</v>
+        <v>2.085686043087784</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2882887386623608</v>
+        <v>0.2841106410005875</v>
       </c>
       <c r="W70">
-        <v>0.1044792131643655</v>
+        <v>0.1050925579011138</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.823682110463888</v>
+        <v>0.8117446885731071</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1220135453186342</v>
+        <v>0.1230235453186342</v>
       </c>
       <c r="C71">
-        <v>-106.5494176182601</v>
+        <v>-121.5287899854221</v>
       </c>
       <c r="D71">
-        <v>479.5025823817399</v>
+        <v>473.231210014578</v>
       </c>
       <c r="E71">
-        <v>542.452</v>
+        <v>551.1600000000001</v>
       </c>
       <c r="F71">
-        <v>600.852</v>
+        <v>609.5600000000001</v>
       </c>
       <c r="G71">
         <v>14.8</v>
@@ -7109,37 +7109,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M71">
-        <v>88.20507360000001</v>
+        <v>89.48340800000001</v>
       </c>
       <c r="N71">
-        <v>-16.60507360000001</v>
+        <v>-17.88340800000002</v>
       </c>
       <c r="O71">
-        <v>-5.811775760000003</v>
+        <v>-6.259192800000005</v>
       </c>
       <c r="P71">
-        <v>-10.79329784000001</v>
+        <v>-11.62421520000001</v>
       </c>
       <c r="Q71">
-        <v>3.406702159999991</v>
+        <v>2.575784799999987</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1596763882802119</v>
+        <v>0.1634722678895524</v>
       </c>
       <c r="T71">
-        <v>2.085686043087784</v>
+        <v>2.15520891119071</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2841106410005875</v>
+        <v>0.2800519175577219</v>
       </c>
       <c r="W71">
-        <v>0.1050925579011138</v>
+        <v>0.1056883785025264</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8117446885731071</v>
+        <v>0.8001483358792055</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1230235453186342</v>
+        <v>0.1646884099693177</v>
       </c>
       <c r="C72">
-        <v>-121.5287899854221</v>
+        <v>-296.0823448113727</v>
       </c>
       <c r="D72">
-        <v>473.231210014578</v>
+        <v>307.3856551886273</v>
       </c>
       <c r="E72">
-        <v>551.1600000000001</v>
+        <v>559.8680000000001</v>
       </c>
       <c r="F72">
-        <v>609.5600000000001</v>
+        <v>618.268</v>
       </c>
       <c r="G72">
         <v>14.8</v>
@@ -7191,45 +7191,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M72">
-        <v>89.48340800000001</v>
+        <v>124.1482144</v>
       </c>
       <c r="N72">
-        <v>-17.88340800000002</v>
+        <v>-52.54821440000002</v>
       </c>
       <c r="O72">
-        <v>-6.259192800000005</v>
+        <v>-18.39187504000001</v>
       </c>
       <c r="P72">
-        <v>-11.62421520000001</v>
+        <v>-34.15633936000002</v>
       </c>
       <c r="Q72">
-        <v>2.575784799999987</v>
+        <v>-19.95633936000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1634722678895524</v>
+        <v>0.1755122241984457</v>
       </c>
       <c r="T72">
-        <v>2.15520891119071</v>
+        <v>2.3757249392461</v>
       </c>
       <c r="U72">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.2800519175577219</v>
+        <v>0.2018555008713842</v>
       </c>
       <c r="W72">
-        <v>0.1056883785025264</v>
+        <v>0.160267415425026</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.8001483358792055</v>
+        <v>0.5767300024896692</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1646884099693177</v>
+        <v>0.1662384099693177</v>
       </c>
       <c r="C73">
-        <v>-296.0823448113725</v>
+        <v>-308.7462901419673</v>
       </c>
       <c r="D73">
-        <v>307.3856551886274</v>
+        <v>303.4297098580327</v>
       </c>
       <c r="E73">
-        <v>559.8679999999999</v>
+        <v>568.576</v>
       </c>
       <c r="F73">
-        <v>618.2679999999999</v>
+        <v>626.976</v>
       </c>
       <c r="G73">
         <v>14.8</v>
@@ -7273,37 +7273,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M73">
-        <v>124.1482144</v>
+        <v>125.8967808</v>
       </c>
       <c r="N73">
-        <v>-52.54821439999999</v>
+        <v>-54.29678080000001</v>
       </c>
       <c r="O73">
-        <v>-18.39187504</v>
+        <v>-19.00387328</v>
       </c>
       <c r="P73">
-        <v>-34.15633936</v>
+        <v>-35.29290752000001</v>
       </c>
       <c r="Q73">
-        <v>-19.95633936</v>
+        <v>-21.09290752000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1755122241984456</v>
+        <v>0.1801448036341044</v>
       </c>
       <c r="T73">
-        <v>2.375724939246099</v>
+        <v>2.460572258504888</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.2018555008713843</v>
+        <v>0.1990519522481706</v>
       </c>
       <c r="W73">
-        <v>0.160267415425026</v>
+        <v>0.1608303679885673</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5767300024896693</v>
+        <v>0.5687198635662016</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1662384099693177</v>
+        <v>0.1677884099693177</v>
       </c>
       <c r="C74">
-        <v>-308.7462901419673</v>
+        <v>-321.3097059999021</v>
       </c>
       <c r="D74">
-        <v>303.4297098580327</v>
+        <v>299.5742940000979</v>
       </c>
       <c r="E74">
-        <v>568.576</v>
+        <v>577.284</v>
       </c>
       <c r="F74">
-        <v>626.976</v>
+        <v>635.684</v>
       </c>
       <c r="G74">
         <v>14.8</v>
@@ -7355,37 +7355,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M74">
-        <v>125.8967808</v>
+        <v>127.6453472</v>
       </c>
       <c r="N74">
-        <v>-54.29678080000001</v>
+        <v>-56.04534720000001</v>
       </c>
       <c r="O74">
-        <v>-19.00387328</v>
+        <v>-19.61587152</v>
       </c>
       <c r="P74">
-        <v>-35.29290752000001</v>
+        <v>-36.42947568000001</v>
       </c>
       <c r="Q74">
-        <v>-21.09290752000001</v>
+        <v>-22.22947568000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1801448036341044</v>
+        <v>0.1851205371020342</v>
       </c>
       <c r="T74">
-        <v>2.460572258504888</v>
+        <v>2.551704564375439</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1990519522481706</v>
+        <v>0.1963252131762778</v>
       </c>
       <c r="W74">
-        <v>0.1608303679885673</v>
+        <v>0.1613778971942034</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5687198635662016</v>
+        <v>0.5609291805036509</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1677884099693177</v>
+        <v>0.1693384099693177</v>
       </c>
       <c r="C75">
-        <v>-321.3097059999021</v>
+        <v>-333.7763763261227</v>
       </c>
       <c r="D75">
-        <v>299.5742940000979</v>
+        <v>295.8156236738773</v>
       </c>
       <c r="E75">
-        <v>577.284</v>
+        <v>585.992</v>
       </c>
       <c r="F75">
-        <v>635.684</v>
+        <v>644.3919999999999</v>
       </c>
       <c r="G75">
         <v>14.8</v>
@@ -7437,37 +7437,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M75">
-        <v>127.6453472</v>
+        <v>129.3939136</v>
       </c>
       <c r="N75">
-        <v>-56.04534720000001</v>
+        <v>-57.7939136</v>
       </c>
       <c r="O75">
-        <v>-19.61587152</v>
+        <v>-20.22786976</v>
       </c>
       <c r="P75">
-        <v>-36.42947568000001</v>
+        <v>-37.56604384</v>
       </c>
       <c r="Q75">
-        <v>-22.22947568000001</v>
+        <v>-23.36604384</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1851205371020342</v>
+        <v>0.1904790192982663</v>
       </c>
       <c r="T75">
-        <v>2.551704564375439</v>
+        <v>2.649847047620648</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1963252131762778</v>
+        <v>0.1936721697549768</v>
       </c>
       <c r="W75">
-        <v>0.1613778971942034</v>
+        <v>0.1619106283132007</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5609291805036509</v>
+        <v>0.5533490564427908</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1693384099693177</v>
+        <v>0.1708884099693178</v>
       </c>
       <c r="C76">
-        <v>-333.7763763261227</v>
+        <v>-346.149897510755</v>
       </c>
       <c r="D76">
-        <v>295.8156236738773</v>
+        <v>292.1501024892449</v>
       </c>
       <c r="E76">
-        <v>585.992</v>
+        <v>594.6999999999999</v>
       </c>
       <c r="F76">
-        <v>644.3919999999999</v>
+        <v>653.0999999999999</v>
       </c>
       <c r="G76">
         <v>14.8</v>
@@ -7519,37 +7519,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M76">
-        <v>129.3939136</v>
+        <v>131.14248</v>
       </c>
       <c r="N76">
-        <v>-57.7939136</v>
+        <v>-59.54247999999998</v>
       </c>
       <c r="O76">
-        <v>-20.22786976</v>
+        <v>-20.83986799999999</v>
       </c>
       <c r="P76">
-        <v>-37.56604384</v>
+        <v>-38.70261199999999</v>
       </c>
       <c r="Q76">
-        <v>-23.36604384</v>
+        <v>-24.50261199999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1904790192982663</v>
+        <v>0.196266180070197</v>
       </c>
       <c r="T76">
-        <v>2.649847047620648</v>
+        <v>2.755840929525474</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1936721697549768</v>
+        <v>0.1910898741582438</v>
       </c>
       <c r="W76">
-        <v>0.1619106283132007</v>
+        <v>0.1624291532690247</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5533490564427908</v>
+        <v>0.5459710690235537</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1708884099693178</v>
+        <v>0.1724384099693177</v>
       </c>
       <c r="C77">
-        <v>-346.149897510755</v>
+        <v>-358.4336898708142</v>
       </c>
       <c r="D77">
-        <v>292.1501024892449</v>
+        <v>288.5743101291858</v>
       </c>
       <c r="E77">
-        <v>594.6999999999999</v>
+        <v>603.408</v>
       </c>
       <c r="F77">
-        <v>653.0999999999999</v>
+        <v>661.808</v>
       </c>
       <c r="G77">
         <v>14.8</v>
@@ -7601,37 +7601,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M77">
-        <v>131.14248</v>
+        <v>132.8910464</v>
       </c>
       <c r="N77">
-        <v>-59.54247999999998</v>
+        <v>-61.2910464</v>
       </c>
       <c r="O77">
-        <v>-20.83986799999999</v>
+        <v>-21.45186624</v>
       </c>
       <c r="P77">
-        <v>-38.70261199999999</v>
+        <v>-39.83918016</v>
       </c>
       <c r="Q77">
-        <v>-24.50261199999999</v>
+        <v>-25.63918016</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.196266180070197</v>
+        <v>0.2025356042397885</v>
       </c>
       <c r="T77">
-        <v>2.755840929525474</v>
+        <v>2.870667634922369</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1910898741582438</v>
+        <v>0.1885755337087932</v>
       </c>
       <c r="W77">
-        <v>0.1624291532690247</v>
+        <v>0.1629340328312743</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5459710690235537</v>
+        <v>0.5387872391679805</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1724384099693177</v>
+        <v>0.1739884099693177</v>
       </c>
       <c r="C78">
-        <v>-358.4336898708142</v>
+        <v>-370.6310082952123</v>
       </c>
       <c r="D78">
-        <v>288.5743101291858</v>
+        <v>285.0849917047877</v>
       </c>
       <c r="E78">
-        <v>603.408</v>
+        <v>612.116</v>
       </c>
       <c r="F78">
-        <v>661.808</v>
+        <v>670.516</v>
       </c>
       <c r="G78">
         <v>14.8</v>
@@ -7683,37 +7683,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M78">
-        <v>132.8910464</v>
+        <v>134.6396128</v>
       </c>
       <c r="N78">
-        <v>-61.2910464</v>
+        <v>-63.03961280000001</v>
       </c>
       <c r="O78">
-        <v>-21.45186624</v>
+        <v>-22.06386448</v>
       </c>
       <c r="P78">
-        <v>-39.83918016</v>
+        <v>-40.97574832000001</v>
       </c>
       <c r="Q78">
-        <v>-25.63918016</v>
+        <v>-26.77574832000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2025356042397885</v>
+        <v>0.209350195728475</v>
       </c>
       <c r="T78">
-        <v>2.870667634922369</v>
+        <v>2.995479271223342</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1885755337087932</v>
+        <v>0.1861265008034842</v>
       </c>
       <c r="W78">
-        <v>0.1629340328312743</v>
+        <v>0.1634257986386604</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5387872391679805</v>
+        <v>0.531790002295669</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1739884099693177</v>
+        <v>0.1755384099693177</v>
       </c>
       <c r="C79">
-        <v>-370.6310082952123</v>
+        <v>-382.7449521267031</v>
       </c>
       <c r="D79">
-        <v>285.0849917047877</v>
+        <v>281.6790478732968</v>
       </c>
       <c r="E79">
-        <v>612.116</v>
+        <v>620.824</v>
       </c>
       <c r="F79">
-        <v>670.516</v>
+        <v>679.2239999999999</v>
       </c>
       <c r="G79">
         <v>14.8</v>
@@ -7765,37 +7765,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M79">
-        <v>134.6396128</v>
+        <v>136.3881792</v>
       </c>
       <c r="N79">
-        <v>-63.03961280000001</v>
+        <v>-64.7881792</v>
       </c>
       <c r="O79">
-        <v>-22.06386448</v>
+        <v>-22.67586272</v>
       </c>
       <c r="P79">
-        <v>-40.97574832000001</v>
+        <v>-42.11231648</v>
       </c>
       <c r="Q79">
-        <v>-26.77574832000001</v>
+        <v>-27.91231648</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.209350195728475</v>
+        <v>0.2167842955343147</v>
       </c>
       <c r="T79">
-        <v>2.995479271223342</v>
+        <v>3.131637419915312</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1861265008034842</v>
+        <v>0.1837402636136959</v>
       </c>
       <c r="W79">
-        <v>0.1634257986386604</v>
+        <v>0.1639049550663699</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.531790002295669</v>
+        <v>0.524972181753417</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1755384099693177</v>
+        <v>0.1770884099693177</v>
       </c>
       <c r="C80">
-        <v>-382.7449521267031</v>
+        <v>-394.7784743438253</v>
       </c>
       <c r="D80">
-        <v>281.6790478732968</v>
+        <v>278.3535256561747</v>
       </c>
       <c r="E80">
-        <v>620.824</v>
+        <v>629.532</v>
       </c>
       <c r="F80">
-        <v>679.2239999999999</v>
+        <v>687.932</v>
       </c>
       <c r="G80">
         <v>14.8</v>
@@ -7847,37 +7847,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M80">
-        <v>136.3881792</v>
+        <v>138.1367456</v>
       </c>
       <c r="N80">
-        <v>-64.7881792</v>
+        <v>-66.53674560000002</v>
       </c>
       <c r="O80">
-        <v>-22.67586272</v>
+        <v>-23.28786096</v>
       </c>
       <c r="P80">
-        <v>-42.11231648</v>
+        <v>-43.24888464000001</v>
       </c>
       <c r="Q80">
-        <v>-27.91231648</v>
+        <v>-29.04888464000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2167842955343147</v>
+        <v>0.2249264048454726</v>
       </c>
       <c r="T80">
-        <v>3.131637419915312</v>
+        <v>3.280763011339851</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1837402636136959</v>
+        <v>0.1814144374920035</v>
       </c>
       <c r="W80">
-        <v>0.1639049550663699</v>
+        <v>0.1643719809516057</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.524972181753417</v>
+        <v>0.5183269642628673</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1770884099693177</v>
+        <v>0.1786384099693178</v>
       </c>
       <c r="C81">
-        <v>-394.7784743438253</v>
+        <v>-406.7343901000191</v>
       </c>
       <c r="D81">
-        <v>278.3535256561747</v>
+        <v>275.1056098999808</v>
       </c>
       <c r="E81">
-        <v>629.532</v>
+        <v>638.24</v>
       </c>
       <c r="F81">
-        <v>687.932</v>
+        <v>696.64</v>
       </c>
       <c r="G81">
         <v>14.8</v>
@@ -7929,37 +7929,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M81">
-        <v>138.1367456</v>
+        <v>139.885312</v>
       </c>
       <c r="N81">
-        <v>-66.53674560000002</v>
+        <v>-68.285312</v>
       </c>
       <c r="O81">
-        <v>-23.28786096</v>
+        <v>-23.8998592</v>
       </c>
       <c r="P81">
-        <v>-43.24888464000001</v>
+        <v>-44.3854528</v>
       </c>
       <c r="Q81">
-        <v>-29.04888464000001</v>
+        <v>-30.1854528</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2249264048454726</v>
+        <v>0.2338827250877462</v>
       </c>
       <c r="T81">
-        <v>3.280763011339851</v>
+        <v>3.444801161906844</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1814144374920035</v>
+        <v>0.1791467570233535</v>
       </c>
       <c r="W81">
-        <v>0.1643719809516057</v>
+        <v>0.1648273311897106</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5183269642628673</v>
+        <v>0.5118478772095815</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1786384099693178</v>
+        <v>0.1801884099693177</v>
       </c>
       <c r="C82">
-        <v>-406.7343901000191</v>
+        <v>-418.6153846718153</v>
       </c>
       <c r="D82">
-        <v>275.1056098999808</v>
+        <v>271.9326153281847</v>
       </c>
       <c r="E82">
-        <v>638.24</v>
+        <v>646.948</v>
       </c>
       <c r="F82">
-        <v>696.64</v>
+        <v>705.348</v>
       </c>
       <c r="G82">
         <v>14.8</v>
@@ -8011,37 +8011,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M82">
-        <v>139.885312</v>
+        <v>141.6338784</v>
       </c>
       <c r="N82">
-        <v>-68.285312</v>
+        <v>-70.03387839999999</v>
       </c>
       <c r="O82">
-        <v>-23.8998592</v>
+        <v>-24.51185744</v>
       </c>
       <c r="P82">
-        <v>-44.3854528</v>
+        <v>-45.52202095999999</v>
       </c>
       <c r="Q82">
-        <v>-30.1854528</v>
+        <v>-31.32202095999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2338827250877462</v>
+        <v>0.2437818158818382</v>
       </c>
       <c r="T82">
-        <v>3.444801161906844</v>
+        <v>3.626106486217731</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1791467570233535</v>
+        <v>0.1769350686650405</v>
       </c>
       <c r="W82">
-        <v>0.1648273311897106</v>
+        <v>0.1652714382120599</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5118478772095815</v>
+        <v>0.5055287676144016</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1801884099693177</v>
+        <v>0.2113724858163328</v>
       </c>
       <c r="C83">
-        <v>-418.6153846718153</v>
+        <v>-478.5394261527531</v>
       </c>
       <c r="D83">
-        <v>271.9326153281847</v>
+        <v>220.716573847247</v>
       </c>
       <c r="E83">
-        <v>646.948</v>
+        <v>655.6560000000001</v>
       </c>
       <c r="F83">
-        <v>705.348</v>
+        <v>714.056</v>
       </c>
       <c r="G83">
         <v>14.8</v>
@@ -8093,45 +8093,45 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M83">
-        <v>141.6338784</v>
+        <v>168.3744048</v>
       </c>
       <c r="N83">
-        <v>-70.03387839999999</v>
+        <v>-96.77440480000001</v>
       </c>
       <c r="O83">
-        <v>-24.51185744</v>
+        <v>-33.87104168</v>
       </c>
       <c r="P83">
-        <v>-45.52202095999999</v>
+        <v>-62.90336312000001</v>
       </c>
       <c r="Q83">
-        <v>-31.32202095999999</v>
+        <v>-48.70336312000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2437818158818382</v>
+        <v>0.2599701159142461</v>
       </c>
       <c r="T83">
-        <v>3.626106486217731</v>
+        <v>3.92260088640743</v>
       </c>
       <c r="U83">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1769350686650405</v>
+        <v>0.1488349730457369</v>
       </c>
       <c r="W83">
-        <v>0.1652714382120599</v>
+        <v>0.2007047133558152</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.5055287676144016</v>
+        <v>0.425242780130677</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2113724858163328</v>
+        <v>0.2132724858163328</v>
       </c>
       <c r="C84">
-        <v>-478.5394261527531</v>
+        <v>-489.7514881678692</v>
       </c>
       <c r="D84">
-        <v>220.716573847247</v>
+        <v>218.2125118321308</v>
       </c>
       <c r="E84">
-        <v>655.6560000000001</v>
+        <v>664.364</v>
       </c>
       <c r="F84">
-        <v>714.056</v>
+        <v>722.764</v>
       </c>
       <c r="G84">
         <v>14.8</v>
@@ -8175,37 +8175,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M84">
-        <v>168.3744048</v>
+        <v>170.4277512</v>
       </c>
       <c r="N84">
-        <v>-96.77440480000001</v>
+        <v>-98.82775120000002</v>
       </c>
       <c r="O84">
-        <v>-33.87104168</v>
+        <v>-34.58971292</v>
       </c>
       <c r="P84">
-        <v>-62.90336312000001</v>
+        <v>-64.23803828000001</v>
       </c>
       <c r="Q84">
-        <v>-48.70336312000001</v>
+        <v>-50.03803828000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2599701159142461</v>
+        <v>0.2725683580268488</v>
       </c>
       <c r="T84">
-        <v>3.92260088640743</v>
+        <v>4.153342115019632</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1488349730457369</v>
+        <v>0.1470417805994027</v>
       </c>
       <c r="W84">
-        <v>0.2007047133558152</v>
+        <v>0.2011275481346608</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.425242780130677</v>
+        <v>0.4201193731411507</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2132724858163328</v>
+        <v>0.2151724858163328</v>
       </c>
       <c r="C85">
-        <v>-489.7514881678692</v>
+        <v>-500.9073696551295</v>
       </c>
       <c r="D85">
-        <v>218.2125118321308</v>
+        <v>215.7646303448705</v>
       </c>
       <c r="E85">
-        <v>664.364</v>
+        <v>673.072</v>
       </c>
       <c r="F85">
-        <v>722.764</v>
+        <v>731.472</v>
       </c>
       <c r="G85">
         <v>14.8</v>
@@ -8257,37 +8257,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M85">
-        <v>170.4277512</v>
+        <v>172.4810976</v>
       </c>
       <c r="N85">
-        <v>-98.82775120000002</v>
+        <v>-100.8810976</v>
       </c>
       <c r="O85">
-        <v>-34.58971292</v>
+        <v>-35.30838416</v>
       </c>
       <c r="P85">
-        <v>-64.23803828000001</v>
+        <v>-65.57271344</v>
       </c>
       <c r="Q85">
-        <v>-50.03803828000001</v>
+        <v>-51.37271344</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2725683580268488</v>
+        <v>0.2867413804035269</v>
       </c>
       <c r="T85">
-        <v>4.153342115019632</v>
+        <v>4.41292599720836</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1470417805994027</v>
+        <v>0.1452912832113146</v>
       </c>
       <c r="W85">
-        <v>0.2011275481346608</v>
+        <v>0.201540315418772</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4201193731411507</v>
+        <v>0.4151179520323275</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2151724858163328</v>
+        <v>0.2170724858163328</v>
       </c>
       <c r="C86">
-        <v>-500.9073696551295</v>
+        <v>-512.0089403194502</v>
       </c>
       <c r="D86">
-        <v>215.7646303448705</v>
+        <v>213.3710596805498</v>
       </c>
       <c r="E86">
-        <v>673.072</v>
+        <v>681.78</v>
       </c>
       <c r="F86">
-        <v>731.472</v>
+        <v>740.1799999999999</v>
       </c>
       <c r="G86">
         <v>14.8</v>
@@ -8339,37 +8339,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M86">
-        <v>172.4810976</v>
+        <v>174.534444</v>
       </c>
       <c r="N86">
-        <v>-100.8810976</v>
+        <v>-102.934444</v>
       </c>
       <c r="O86">
-        <v>-35.30838416</v>
+        <v>-36.0270554</v>
       </c>
       <c r="P86">
-        <v>-65.57271344</v>
+        <v>-66.90738860000002</v>
       </c>
       <c r="Q86">
-        <v>-51.37271344</v>
+        <v>-52.70738860000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2867413804035268</v>
+        <v>0.3028041390970952</v>
       </c>
       <c r="T86">
-        <v>4.412925997208357</v>
+        <v>4.707121063688914</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1452912832113146</v>
+        <v>0.1435819739970638</v>
       </c>
       <c r="W86">
-        <v>0.201540315418772</v>
+        <v>0.2019433705314924</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4151179520323275</v>
+        <v>0.4102342114201825</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2170724858163328</v>
+        <v>0.2189724858163328</v>
       </c>
       <c r="C87">
-        <v>-512.0089403194502</v>
+        <v>-523.0579878102335</v>
       </c>
       <c r="D87">
-        <v>213.3710596805498</v>
+        <v>211.0300121897665</v>
       </c>
       <c r="E87">
-        <v>681.78</v>
+        <v>690.4879999999999</v>
       </c>
       <c r="F87">
-        <v>740.1799999999999</v>
+        <v>748.8879999999999</v>
       </c>
       <c r="G87">
         <v>14.8</v>
@@ -8421,37 +8421,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M87">
-        <v>174.534444</v>
+        <v>176.5877904</v>
       </c>
       <c r="N87">
-        <v>-102.934444</v>
+        <v>-104.9877904</v>
       </c>
       <c r="O87">
-        <v>-36.0270554</v>
+        <v>-36.74572663999999</v>
       </c>
       <c r="P87">
-        <v>-66.90738860000002</v>
+        <v>-68.24206376000001</v>
       </c>
       <c r="Q87">
-        <v>-52.70738860000002</v>
+        <v>-54.04206376</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3028041390970952</v>
+        <v>0.3211615776040306</v>
       </c>
       <c r="T87">
-        <v>4.707121063688914</v>
+        <v>5.043343996809551</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1435819739970638</v>
+        <v>0.1419124161598887</v>
       </c>
       <c r="W87">
-        <v>0.2019433705314924</v>
+        <v>0.2023370522694982</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4102342114201825</v>
+        <v>0.4054640461711105</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2189724858163328</v>
+        <v>0.2208724858163328</v>
       </c>
       <c r="C88">
-        <v>-523.0579878102335</v>
+        <v>-534.0562221739656</v>
       </c>
       <c r="D88">
-        <v>211.0300121897665</v>
+        <v>208.7397778260345</v>
       </c>
       <c r="E88">
-        <v>690.4879999999999</v>
+        <v>699.196</v>
       </c>
       <c r="F88">
-        <v>748.8879999999999</v>
+        <v>757.596</v>
       </c>
       <c r="G88">
         <v>14.8</v>
@@ -8503,37 +8503,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M88">
-        <v>176.5877904</v>
+        <v>178.6411368</v>
       </c>
       <c r="N88">
-        <v>-104.9877904</v>
+        <v>-107.0411368</v>
       </c>
       <c r="O88">
-        <v>-36.74572663999999</v>
+        <v>-37.46439788</v>
       </c>
       <c r="P88">
-        <v>-68.24206376000001</v>
+        <v>-69.57673892</v>
       </c>
       <c r="Q88">
-        <v>-54.04206376</v>
+        <v>-55.37673891999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3211615776040306</v>
+        <v>0.3423432374197252</v>
       </c>
       <c r="T88">
-        <v>5.043343996809551</v>
+        <v>5.43129353502567</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1419124161598887</v>
+        <v>0.1402812389626486</v>
       </c>
       <c r="W88">
-        <v>0.2023370522694982</v>
+        <v>0.2027216838526074</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4054640461711105</v>
+        <v>0.4008035398932817</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2208724858163328</v>
+        <v>0.2227724858163328</v>
       </c>
       <c r="C89">
-        <v>-534.0562221739656</v>
+        <v>-545.0052800199919</v>
       </c>
       <c r="D89">
-        <v>208.7397778260345</v>
+        <v>206.4987199800081</v>
       </c>
       <c r="E89">
-        <v>699.196</v>
+        <v>707.904</v>
       </c>
       <c r="F89">
-        <v>757.596</v>
+        <v>766.304</v>
       </c>
       <c r="G89">
         <v>14.8</v>
@@ -8585,37 +8585,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M89">
-        <v>178.6411368</v>
+        <v>180.6944832</v>
       </c>
       <c r="N89">
-        <v>-107.0411368</v>
+        <v>-109.0944832</v>
       </c>
       <c r="O89">
-        <v>-37.46439788</v>
+        <v>-38.18306912</v>
       </c>
       <c r="P89">
-        <v>-69.57673892</v>
+        <v>-70.91141408000001</v>
       </c>
       <c r="Q89">
-        <v>-55.37673891999999</v>
+        <v>-56.71141408000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3423432374197252</v>
+        <v>0.3670551738713691</v>
       </c>
       <c r="T89">
-        <v>5.43129353502567</v>
+        <v>5.883901329611144</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1402812389626486</v>
+        <v>0.1386871339744367</v>
       </c>
       <c r="W89">
-        <v>0.2027216838526074</v>
+        <v>0.2030975738088278</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4008035398932817</v>
+        <v>0.3962489542126763</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2227724858163328</v>
+        <v>0.2246724858163328</v>
       </c>
       <c r="C90">
-        <v>-545.0052800199919</v>
+        <v>-555.9067284207978</v>
       </c>
       <c r="D90">
-        <v>206.4987199800081</v>
+        <v>204.3052715792022</v>
       </c>
       <c r="E90">
-        <v>707.904</v>
+        <v>716.612</v>
       </c>
       <c r="F90">
-        <v>766.304</v>
+        <v>775.0119999999999</v>
       </c>
       <c r="G90">
         <v>14.8</v>
@@ -8667,37 +8667,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M90">
-        <v>180.6944832</v>
+        <v>182.7478296</v>
       </c>
       <c r="N90">
-        <v>-109.0944832</v>
+        <v>-111.1478296</v>
       </c>
       <c r="O90">
-        <v>-38.18306912</v>
+        <v>-38.90174036</v>
       </c>
       <c r="P90">
-        <v>-70.91141408000001</v>
+        <v>-72.24608924</v>
       </c>
       <c r="Q90">
-        <v>-56.71141408000001</v>
+        <v>-58.04608924</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3670551738713691</v>
+        <v>0.3962601896778572</v>
       </c>
       <c r="T90">
-        <v>5.883901329611144</v>
+        <v>6.418801450484884</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1386871339744367</v>
+        <v>0.1371288515702295</v>
       </c>
       <c r="W90">
-        <v>0.2030975738088278</v>
+        <v>0.2034650167997399</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3962489542126763</v>
+        <v>0.3917967187720844</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2246724858163328</v>
+        <v>0.2265724858163328</v>
       </c>
       <c r="C91">
-        <v>-555.9067284207978</v>
+        <v>-566.7620685663269</v>
       </c>
       <c r="D91">
-        <v>204.3052715792022</v>
+        <v>202.1579314336731</v>
       </c>
       <c r="E91">
-        <v>716.612</v>
+        <v>725.3200000000001</v>
       </c>
       <c r="F91">
-        <v>775.0119999999999</v>
+        <v>783.72</v>
       </c>
       <c r="G91">
         <v>14.8</v>
@@ -8749,37 +8749,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M91">
-        <v>182.7478296</v>
+        <v>184.801176</v>
       </c>
       <c r="N91">
-        <v>-111.1478296</v>
+        <v>-113.201176</v>
       </c>
       <c r="O91">
-        <v>-38.90174036</v>
+        <v>-39.62041160000001</v>
       </c>
       <c r="P91">
-        <v>-72.24608924</v>
+        <v>-73.58076440000002</v>
       </c>
       <c r="Q91">
-        <v>-58.04608924</v>
+        <v>-59.38076440000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3962601896778572</v>
+        <v>0.431306208645643</v>
       </c>
       <c r="T91">
-        <v>6.418801450484884</v>
+        <v>7.060681595533373</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1371288515702295</v>
+        <v>0.1356051976638936</v>
       </c>
       <c r="W91">
-        <v>0.2034650167997399</v>
+        <v>0.2038242943908539</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3917967187720844</v>
+        <v>0.3874434218968389</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2265724858163328</v>
+        <v>0.2284724858163328</v>
       </c>
       <c r="C92">
-        <v>-566.7620685663269</v>
+        <v>-577.5727391902442</v>
       </c>
       <c r="D92">
-        <v>202.1579314336731</v>
+        <v>200.0552608097558</v>
       </c>
       <c r="E92">
-        <v>725.3200000000001</v>
+        <v>734.028</v>
       </c>
       <c r="F92">
-        <v>783.72</v>
+        <v>792.428</v>
       </c>
       <c r="G92">
         <v>14.8</v>
@@ -8831,37 +8831,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M92">
-        <v>184.801176</v>
+        <v>186.8545224</v>
       </c>
       <c r="N92">
-        <v>-113.201176</v>
+        <v>-115.2545224</v>
       </c>
       <c r="O92">
-        <v>-39.62041160000001</v>
+        <v>-40.33908284</v>
       </c>
       <c r="P92">
-        <v>-73.58076440000002</v>
+        <v>-74.91543956000001</v>
       </c>
       <c r="Q92">
-        <v>-59.38076440000002</v>
+        <v>-60.71543956000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.431306208645643</v>
+        <v>0.4741402318284922</v>
       </c>
       <c r="T92">
-        <v>7.060681595533373</v>
+        <v>7.84520177281486</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1356051976638936</v>
+        <v>0.1341150306565981</v>
       </c>
       <c r="W92">
-        <v>0.2038242943908539</v>
+        <v>0.2041756757711742</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3874434218968389</v>
+        <v>0.3831858018759946</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2284724858163328</v>
+        <v>0.2303724858163328</v>
       </c>
       <c r="C93">
-        <v>-577.5727391902442</v>
+        <v>-588.3401197845803</v>
       </c>
       <c r="D93">
-        <v>200.0552608097558</v>
+        <v>197.9958802154196</v>
       </c>
       <c r="E93">
-        <v>734.028</v>
+        <v>742.736</v>
       </c>
       <c r="F93">
-        <v>792.428</v>
+        <v>801.136</v>
       </c>
       <c r="G93">
         <v>14.8</v>
@@ -8913,37 +8913,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M93">
-        <v>186.8545224</v>
+        <v>188.9078688</v>
       </c>
       <c r="N93">
-        <v>-115.2545224</v>
+        <v>-117.3078688</v>
       </c>
       <c r="O93">
-        <v>-40.33908284</v>
+        <v>-41.05775408</v>
       </c>
       <c r="P93">
-        <v>-74.91543956000001</v>
+        <v>-76.25011472</v>
       </c>
       <c r="Q93">
-        <v>-60.71543956000001</v>
+        <v>-62.05011472</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4741402318284922</v>
+        <v>0.5276827608070538</v>
       </c>
       <c r="T93">
-        <v>7.84520177281486</v>
+        <v>8.82585199441672</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1341150306565981</v>
+        <v>0.1326572585842438</v>
       </c>
       <c r="W93">
-        <v>0.2041756757711742</v>
+        <v>0.2045194184258353</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3831858018759946</v>
+        <v>0.3790207388121251</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2303724858163328</v>
+        <v>0.2322724858163328</v>
       </c>
       <c r="C94">
-        <v>-588.3401197845803</v>
+        <v>-599.0655336178461</v>
       </c>
       <c r="D94">
-        <v>197.9958802154196</v>
+        <v>195.978466382154</v>
       </c>
       <c r="E94">
-        <v>742.736</v>
+        <v>751.4440000000001</v>
       </c>
       <c r="F94">
-        <v>801.136</v>
+        <v>809.8440000000001</v>
       </c>
       <c r="G94">
         <v>14.8</v>
@@ -8995,37 +8995,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M94">
-        <v>188.9078688</v>
+        <v>190.9612152</v>
       </c>
       <c r="N94">
-        <v>-117.3078688</v>
+        <v>-119.3612152</v>
       </c>
       <c r="O94">
-        <v>-41.05775408</v>
+        <v>-41.77642532000001</v>
       </c>
       <c r="P94">
-        <v>-76.25011472</v>
+        <v>-77.58478988000002</v>
       </c>
       <c r="Q94">
-        <v>-62.05011472</v>
+        <v>-63.38478988000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5276827608070538</v>
+        <v>0.5965231552080615</v>
       </c>
       <c r="T94">
-        <v>8.82585199441672</v>
+        <v>10.08668799361911</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1326572585842438</v>
+        <v>0.1312308364489293</v>
       </c>
       <c r="W94">
-        <v>0.2045194184258353</v>
+        <v>0.2048557687653425</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3790207388121251</v>
+        <v>0.3749452469969409</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2322724858163328</v>
+        <v>0.2341724858163328</v>
       </c>
       <c r="C95">
-        <v>-599.0655336178461</v>
+        <v>-609.7502505704966</v>
       </c>
       <c r="D95">
-        <v>195.978466382154</v>
+        <v>194.0017494295034</v>
       </c>
       <c r="E95">
-        <v>751.4440000000001</v>
+        <v>760.152</v>
       </c>
       <c r="F95">
-        <v>809.8440000000001</v>
+        <v>818.552</v>
       </c>
       <c r="G95">
         <v>14.8</v>
@@ -9077,37 +9077,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M95">
-        <v>190.9612152</v>
+        <v>193.0145616</v>
       </c>
       <c r="N95">
-        <v>-119.3612152</v>
+        <v>-121.4145616</v>
       </c>
       <c r="O95">
-        <v>-41.77642532000001</v>
+        <v>-42.49509656</v>
       </c>
       <c r="P95">
-        <v>-77.58478988000002</v>
+        <v>-78.91946504000001</v>
       </c>
       <c r="Q95">
-        <v>-63.38478988000001</v>
+        <v>-64.71946504</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5965231552080615</v>
+        <v>0.6883103477427387</v>
       </c>
       <c r="T95">
-        <v>10.08668799361911</v>
+        <v>11.7678026592223</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1312308364489293</v>
+        <v>0.1298347637207492</v>
       </c>
       <c r="W95">
-        <v>0.2048557687653425</v>
+        <v>0.2051849627146473</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3749452469969409</v>
+        <v>0.3709564677735693</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2341724858163328</v>
+        <v>0.2360724858163328</v>
       </c>
       <c r="C96">
-        <v>-609.7502505704966</v>
+        <v>-620.3954898005127</v>
       </c>
       <c r="D96">
-        <v>194.0017494295034</v>
+        <v>192.0645101994874</v>
       </c>
       <c r="E96">
-        <v>760.152</v>
+        <v>768.86</v>
       </c>
       <c r="F96">
-        <v>818.552</v>
+        <v>827.26</v>
       </c>
       <c r="G96">
         <v>14.8</v>
@@ -9159,37 +9159,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M96">
-        <v>193.0145616</v>
+        <v>195.067908</v>
       </c>
       <c r="N96">
-        <v>-121.4145616</v>
+        <v>-123.467908</v>
       </c>
       <c r="O96">
-        <v>-42.49509656</v>
+        <v>-43.21376780000001</v>
       </c>
       <c r="P96">
-        <v>-78.91946504000001</v>
+        <v>-80.25414020000002</v>
       </c>
       <c r="Q96">
-        <v>-64.71946504</v>
+        <v>-66.05414020000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6883103477427387</v>
+        <v>0.8168124172912867</v>
       </c>
       <c r="T96">
-        <v>11.7678026592223</v>
+        <v>14.12136319106676</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1298347637207492</v>
+        <v>0.1284680819973729</v>
       </c>
       <c r="W96">
-        <v>0.2051849627146473</v>
+        <v>0.2055072262650195</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3709564677735693</v>
+        <v>0.3670516628496369</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2360724858163328</v>
+        <v>0.2379724858163328</v>
       </c>
       <c r="C97">
-        <v>-620.3954898005127</v>
+        <v>-631.0024222508522</v>
       </c>
       <c r="D97">
-        <v>192.0645101994874</v>
+        <v>190.1655777491479</v>
       </c>
       <c r="E97">
-        <v>768.86</v>
+        <v>777.5680000000001</v>
       </c>
       <c r="F97">
-        <v>827.26</v>
+        <v>835.9680000000001</v>
       </c>
       <c r="G97">
         <v>14.8</v>
@@ -9241,37 +9241,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M97">
-        <v>195.067908</v>
+        <v>197.1212544</v>
       </c>
       <c r="N97">
-        <v>-123.467908</v>
+        <v>-125.5212544</v>
       </c>
       <c r="O97">
-        <v>-43.21376780000001</v>
+        <v>-43.93243904000001</v>
       </c>
       <c r="P97">
-        <v>-80.25414020000002</v>
+        <v>-81.58881536000003</v>
       </c>
       <c r="Q97">
-        <v>-66.05414020000002</v>
+        <v>-67.38881536000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8168124172912867</v>
+        <v>1.009565521614109</v>
       </c>
       <c r="T97">
-        <v>14.12136319106676</v>
+        <v>17.65170398883346</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1284680819973729</v>
+        <v>0.1271298728099003</v>
       </c>
       <c r="W97">
-        <v>0.2055072262650195</v>
+        <v>0.2058227759914255</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3670516628496369</v>
+        <v>0.3632282080282865</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2379724858163328</v>
+        <v>0.2398724858163328</v>
       </c>
       <c r="C98">
-        <v>-631.002422250852</v>
+        <v>-641.5721730096138</v>
       </c>
       <c r="D98">
-        <v>190.165577749148</v>
+        <v>188.303826990386</v>
       </c>
       <c r="E98">
-        <v>777.568</v>
+        <v>786.276</v>
       </c>
       <c r="F98">
-        <v>835.968</v>
+        <v>844.6759999999999</v>
       </c>
       <c r="G98">
         <v>14.8</v>
@@ -9323,37 +9323,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M98">
-        <v>197.1212544</v>
+        <v>199.1746008</v>
       </c>
       <c r="N98">
-        <v>-125.5212544</v>
+        <v>-127.5746008</v>
       </c>
       <c r="O98">
-        <v>-43.93243904</v>
+        <v>-44.65111027999999</v>
       </c>
       <c r="P98">
-        <v>-81.58881536000001</v>
+        <v>-82.92349052</v>
       </c>
       <c r="Q98">
-        <v>-67.38881536000001</v>
+        <v>-68.72349052</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.009565521614106</v>
+        <v>1.330820695485475</v>
       </c>
       <c r="T98">
-        <v>17.65170398883342</v>
+        <v>23.53560531844456</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1271298728099003</v>
+        <v>0.1258192555644374</v>
       </c>
       <c r="W98">
-        <v>0.2058227759914255</v>
+        <v>0.2061318195379057</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3632282080282866</v>
+        <v>0.3594835873269641</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2398724858163328</v>
+        <v>0.2417724858163328</v>
       </c>
       <c r="C99">
-        <v>-641.5721730096138</v>
+        <v>-652.1058235329076</v>
       </c>
       <c r="D99">
-        <v>188.303826990386</v>
+        <v>186.4781764670923</v>
       </c>
       <c r="E99">
-        <v>786.276</v>
+        <v>794.9839999999999</v>
       </c>
       <c r="F99">
-        <v>844.6759999999999</v>
+        <v>853.3839999999999</v>
       </c>
       <c r="G99">
         <v>14.8</v>
@@ -9405,37 +9405,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M99">
-        <v>199.1746008</v>
+        <v>201.2279472</v>
       </c>
       <c r="N99">
-        <v>-127.5746008</v>
+        <v>-129.6279472</v>
       </c>
       <c r="O99">
-        <v>-44.65111027999999</v>
+        <v>-45.36978152</v>
       </c>
       <c r="P99">
-        <v>-82.92349052</v>
+        <v>-84.25816567999999</v>
       </c>
       <c r="Q99">
-        <v>-68.72349052</v>
+        <v>-70.05816567999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.330820695485475</v>
+        <v>1.973331043228213</v>
       </c>
       <c r="T99">
-        <v>23.53560531844456</v>
+        <v>35.30340797766684</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1258192555644374</v>
+        <v>0.1245353856096982</v>
       </c>
       <c r="W99">
-        <v>0.2061318195379057</v>
+        <v>0.2064345560732332</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3594835873269641</v>
+        <v>0.3558153874562807</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2417724858163328</v>
+        <v>0.2436724858163328</v>
       </c>
       <c r="C100">
-        <v>-652.1058235329076</v>
+        <v>-662.6044137396549</v>
       </c>
       <c r="D100">
-        <v>186.4781764670923</v>
+        <v>184.6875862603451</v>
       </c>
       <c r="E100">
-        <v>794.9839999999999</v>
+        <v>803.692</v>
       </c>
       <c r="F100">
-        <v>853.3839999999999</v>
+        <v>862.092</v>
       </c>
       <c r="G100">
         <v>14.8</v>
@@ -9487,37 +9487,37 @@
         <v>71.59999999999999</v>
       </c>
       <c r="M100">
-        <v>201.2279472</v>
+        <v>203.2812936</v>
       </c>
       <c r="N100">
-        <v>-129.6279472</v>
+        <v>-131.6812936</v>
       </c>
       <c r="O100">
-        <v>-45.36978152</v>
+        <v>-46.08845276</v>
       </c>
       <c r="P100">
-        <v>-84.25816567999999</v>
+        <v>-85.59284084000001</v>
       </c>
       <c r="Q100">
-        <v>-70.05816567999999</v>
+        <v>-71.39284084000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.973331043228213</v>
+        <v>3.900862086456425</v>
       </c>
       <c r="T100">
-        <v>35.30340797766684</v>
+        <v>70.60681595533366</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1245353856096982</v>
+        <v>0.1232774524217215</v>
       </c>
       <c r="W100">
-        <v>0.2064345560732332</v>
+        <v>0.2067311767189581</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3558153874562807</v>
+        <v>0.35222129263349</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2436724858163328</v>
-      </c>
-      <c r="C101">
-        <v>-662.6044137396549</v>
-      </c>
-      <c r="D101">
-        <v>184.6875862603451</v>
-      </c>
-      <c r="E101">
-        <v>803.692</v>
-      </c>
-      <c r="F101">
-        <v>862.092</v>
-      </c>
-      <c r="G101">
-        <v>14.8</v>
-      </c>
-      <c r="H101">
-        <v>812.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>85.8</v>
-      </c>
-      <c r="K101">
-        <v>14.2</v>
-      </c>
-      <c r="L101">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="M101">
-        <v>203.2812936</v>
-      </c>
-      <c r="N101">
-        <v>-131.6812936</v>
-      </c>
-      <c r="O101">
-        <v>-46.08845276</v>
-      </c>
-      <c r="P101">
-        <v>-85.59284084000001</v>
-      </c>
-      <c r="Q101">
-        <v>-71.39284084000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.900862086456425</v>
-      </c>
-      <c r="T101">
-        <v>70.60681595533366</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1232774524217215</v>
-      </c>
-      <c r="W101">
-        <v>0.2067311767189581</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.35222129263349</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
